--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
   <si>
     <t>id</t>
   </si>
@@ -155,16 +155,37 @@
     <t>远程攻击-攻击</t>
   </si>
   <si>
+    <t>AttackMode_RangedFireBall</t>
+  </si>
+  <si>
+    <t>1000500001:0.5</t>
+  </si>
+  <si>
+    <t>远程攻击-火球直线攻击</t>
+  </si>
+  <si>
+    <t>AttackMode_RangedWaterBall</t>
+  </si>
+  <si>
+    <t>1000600001:0.5</t>
+  </si>
+  <si>
+    <t>远程攻击-水球直线攻击</t>
+  </si>
+  <si>
+    <t>AttackMode_RangedIceBall</t>
+  </si>
+  <si>
+    <t>1000700001:0.5</t>
+  </si>
+  <si>
+    <t>远程攻击-冰球直线攻击</t>
+  </si>
+  <si>
     <t>AttackModeRangedArea</t>
   </si>
   <si>
-    <t>AttackMode_RangedFireBall</t>
-  </si>
-  <si>
     <t>远程攻击-火球直线攻击-范围伤害</t>
-  </si>
-  <si>
-    <t>AttackMode_RangedIceBall</t>
   </si>
   <si>
     <t>远程攻击-冰球直线攻击-范围伤害</t>
@@ -1219,7 +1240,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -1481,28 +1502,22 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" ht="12" customHeight="1" spans="1:14">
+    <row r="8" spans="1:14">
       <c r="A8">
-        <v>201001</v>
+        <v>200002</v>
       </c>
       <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>43</v>
       </c>
       <c r="F8">
         <v>0.1</v>
       </c>
-      <c r="G8">
-        <v>11</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>100001</v>
-      </c>
       <c r="K8">
         <v>1</v>
       </c>
@@ -1518,27 +1533,20 @@
     </row>
     <row r="9" customFormat="1" spans="1:14">
       <c r="A9">
-        <v>201002</v>
+        <v>200003</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
       </c>
-      <c r="D9"/>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
       <c r="F9">
         <v>0.1</v>
       </c>
-      <c r="G9">
-        <v>11</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>200001</v>
-      </c>
       <c r="K9">
         <v>1</v>
       </c>
@@ -1549,28 +1557,25 @@
         <v>200001</v>
       </c>
       <c r="N9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:14">
       <c r="A10">
-        <v>202001</v>
+        <v>200004</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
       </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
       <c r="F10">
         <v>0.1</v>
       </c>
-      <c r="G10">
-        <v>30</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
       <c r="K10">
         <v>1</v>
       </c>
@@ -1581,27 +1586,31 @@
         <v>200001</v>
       </c>
       <c r="N10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" ht="12" customHeight="1" spans="1:14">
       <c r="A11">
-        <v>203001</v>
+        <v>201001</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11">
+        <v>42</v>
+      </c>
+      <c r="F11">
+        <v>0.1</v>
+      </c>
+      <c r="G11">
         <v>11</v>
       </c>
-      <c r="F11">
-        <v>0.25</v>
-      </c>
-      <c r="G11"/>
-      <c r="H11"/>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>100001</v>
+      </c>
       <c r="K11">
         <v>1</v>
       </c>
@@ -1612,22 +1621,32 @@
         <v>200001</v>
       </c>
       <c r="N11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:14">
+      <c r="A12">
+        <v>201002</v>
+      </c>
+      <c r="B12" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="12" customFormat="1" ht="15" customHeight="1" spans="1:14">
-      <c r="A12">
-        <v>204001</v>
-      </c>
-      <c r="B12" t="s">
-        <v>52</v>
-      </c>
       <c r="C12" t="s">
-        <v>40</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D12"/>
       <c r="F12">
         <v>0.1</v>
       </c>
+      <c r="G12">
+        <v>11</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>200001</v>
+      </c>
       <c r="K12">
         <v>1</v>
       </c>
@@ -1641,19 +1660,25 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" customFormat="1" ht="15" customHeight="1" spans="1:14">
+    <row r="13" customFormat="1" spans="1:14">
       <c r="A13">
-        <v>204002</v>
+        <v>202001</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F13">
         <v>0.1</v>
       </c>
+      <c r="G13">
+        <v>30</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
       <c r="K13">
         <v>1</v>
       </c>
@@ -1664,22 +1689,27 @@
         <v>200001</v>
       </c>
       <c r="N13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" ht="15" customHeight="1" spans="1:14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:14">
       <c r="A14">
-        <v>204003</v>
+        <v>203001</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="E14">
+        <v>11</v>
       </c>
       <c r="F14">
-        <v>0.1</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="G14"/>
+      <c r="H14"/>
       <c r="K14">
         <v>1</v>
       </c>
@@ -1690,15 +1720,15 @@
         <v>200001</v>
       </c>
       <c r="N14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A15">
-        <v>205001</v>
+        <v>204001</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
         <v>40</v>
@@ -1716,18 +1746,18 @@
         <v>200001</v>
       </c>
       <c r="N15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A16">
-        <v>205002</v>
+        <v>204002</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16">
         <v>0.1</v>
@@ -1742,18 +1772,18 @@
         <v>200001</v>
       </c>
       <c r="N16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A17">
-        <v>205003</v>
+        <v>204003</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F17">
         <v>0.1</v>
@@ -1768,30 +1798,24 @@
         <v>200001</v>
       </c>
       <c r="N17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A18">
-        <v>300001</v>
+        <v>205001</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
       </c>
       <c r="F18">
-        <v>1.5</v>
-      </c>
-      <c r="G18">
-        <v>11</v>
-      </c>
-      <c r="H18">
-        <v>1.5</v>
-      </c>
-      <c r="I18">
-        <v>300001</v>
+        <v>0.1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>100001</v>
@@ -1800,30 +1824,24 @@
         <v>200001</v>
       </c>
       <c r="N18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A19">
-        <v>400001</v>
+        <v>205002</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
       </c>
       <c r="F19">
-        <v>0.5</v>
-      </c>
-      <c r="G19">
-        <v>11</v>
-      </c>
-      <c r="H19">
-        <v>0.5</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>100001</v>
@@ -1832,30 +1850,24 @@
         <v>200001</v>
       </c>
       <c r="N19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" ht="15" customHeight="1" spans="1:14">
+      <c r="A20">
+        <v>205003</v>
+      </c>
+      <c r="B20" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20">
-        <v>400002</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
+      <c r="C20" t="s">
+        <v>48</v>
       </c>
       <c r="F20">
-        <v>0.5</v>
-      </c>
-      <c r="G20">
-        <v>11</v>
-      </c>
-      <c r="H20">
-        <v>0.5</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <v>100001</v>
@@ -1864,27 +1876,30 @@
         <v>200001</v>
       </c>
       <c r="N20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21">
-        <v>500001</v>
+        <v>300001</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G21">
         <v>11</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I21">
-        <v>500001</v>
+        <v>300001</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
       </c>
       <c r="L21">
         <v>100001</v>
@@ -1893,27 +1908,30 @@
         <v>200001</v>
       </c>
       <c r="N21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22">
-        <v>500002</v>
+        <v>400001</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G22">
         <v>11</v>
       </c>
       <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>500002</v>
+        <v>0.5</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
       </c>
       <c r="L22">
         <v>100001</v>
@@ -1922,21 +1940,30 @@
         <v>200001</v>
       </c>
       <c r="N22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23">
-        <v>600001</v>
+        <v>400002</v>
       </c>
       <c r="B23" t="s">
         <v>69</v>
       </c>
+      <c r="F23">
+        <v>0.5</v>
+      </c>
+      <c r="G23">
+        <v>11</v>
+      </c>
       <c r="H23">
+        <v>0.5</v>
+      </c>
+      <c r="J23">
         <v>0</v>
       </c>
-      <c r="I23">
-        <v>600001</v>
+      <c r="K23">
+        <v>0</v>
       </c>
       <c r="L23">
         <v>100001</v>
@@ -1945,15 +1972,18 @@
         <v>200001</v>
       </c>
       <c r="N23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24">
-        <v>700001</v>
+        <v>500001</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
       </c>
       <c r="G24">
         <v>11</v>
@@ -1962,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>800001</v>
+        <v>500001</v>
       </c>
       <c r="L24">
         <v>100001</v>
@@ -1971,15 +2001,18 @@
         <v>200001</v>
       </c>
       <c r="N24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:14">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25">
-        <v>700002</v>
+        <v>500002</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
       </c>
       <c r="G25">
         <v>11</v>
@@ -1988,35 +2021,110 @@
         <v>1</v>
       </c>
       <c r="I25">
+        <v>500002</v>
+      </c>
+      <c r="L25">
+        <v>100001</v>
+      </c>
+      <c r="M25">
+        <v>200001</v>
+      </c>
+      <c r="N25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26">
+        <v>600001</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>600001</v>
+      </c>
+      <c r="L26">
+        <v>100001</v>
+      </c>
+      <c r="M26">
+        <v>200001</v>
+      </c>
+      <c r="N26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:14">
+      <c r="A27">
+        <v>700001</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G27">
+        <v>11</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>800001</v>
+      </c>
+      <c r="L27">
+        <v>100001</v>
+      </c>
+      <c r="M27">
+        <v>200001</v>
+      </c>
+      <c r="N27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:14">
+      <c r="A28">
+        <v>700002</v>
+      </c>
+      <c r="B28" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28">
+        <v>11</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
         <v>800002</v>
       </c>
-      <c r="L25">
-        <v>100001</v>
-      </c>
-      <c r="M25">
-        <v>200001</v>
-      </c>
-      <c r="N25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1"/>
-    <row r="27" ht="15" customHeight="1"/>
-    <row r="28" ht="15" customHeight="1"/>
+      <c r="L28">
+        <v>100001</v>
+      </c>
+      <c r="M28">
+        <v>200001</v>
+      </c>
+      <c r="N28" t="s">
+        <v>80</v>
+      </c>
+    </row>
     <row r="29" ht="15" customHeight="1"/>
     <row r="30" ht="15" customHeight="1"/>
     <row r="31" ht="15" customHeight="1"/>
     <row r="32" ht="15" customHeight="1"/>
     <row r="33" ht="15" customHeight="1"/>
-    <row r="65" ht="12" customHeight="1"/>
-    <row r="66" ht="12" customHeight="1"/>
-    <row r="67" ht="12" customHeight="1"/>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="15" customHeight="1"/>
     <row r="68" ht="12" customHeight="1"/>
     <row r="69" ht="12" customHeight="1"/>
     <row r="70" ht="12" customHeight="1"/>
     <row r="71" ht="12" customHeight="1"/>
     <row r="72" ht="12" customHeight="1"/>
     <row r="73" ht="12" customHeight="1"/>
+    <row r="74" ht="12" customHeight="1"/>
+    <row r="75" ht="12" customHeight="1"/>
+    <row r="76" ht="12" customHeight="1"/>
   </sheetData>
   <sortState ref="A4:O88">
     <sortCondition ref="A4"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25620" windowHeight="8235"/>
   </bookViews>
   <sheets>
     <sheet name="AttackModeInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
   <si>
     <t>id</t>
   </si>
@@ -270,6 +270,15 @@
   </si>
   <si>
     <t>普通近战-捶地冰锥</t>
+  </si>
+  <si>
+    <t>AttackModeFalluponChain</t>
+  </si>
+  <si>
+    <t>AttackMode_Thunder_1</t>
+  </si>
+  <si>
+    <t>远程攻击-下落雷击</t>
   </si>
 </sst>
 </file>
@@ -2108,7 +2117,32 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1"/>
+    <row r="29" ht="15" customHeight="1" spans="1:14">
+      <c r="A29">
+        <v>800001</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29">
+        <v>11</v>
+      </c>
+      <c r="H29">
+        <v>1.5</v>
+      </c>
+      <c r="L29">
+        <v>100001</v>
+      </c>
+      <c r="M29">
+        <v>200001</v>
+      </c>
+      <c r="N29" t="s">
+        <v>83</v>
+      </c>
+    </row>
     <row r="30" ht="15" customHeight="1"/>
     <row r="31" ht="15" customHeight="1"/>
     <row r="32" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25620" windowHeight="8235"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="AttackModeInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="87">
   <si>
     <t>id</t>
   </si>
@@ -107,7 +107,7 @@
     <t>碰撞范围检测（用于范围）</t>
   </si>
   <si>
-    <t>打击之后的特效</t>
+    <t>打击之后的特效(用&amp;分隔)</t>
   </si>
   <si>
     <t>受伤特效（默认不填，0为关闭）</t>
@@ -146,6 +146,12 @@
     <t>普通近战范围-捶地攻击</t>
   </si>
   <si>
+    <t>普通近战-捶地火锥</t>
+  </si>
+  <si>
+    <t>普通近战-捶地冰锥</t>
+  </si>
+  <si>
     <t>AttackModeRanged</t>
   </si>
   <si>
@@ -266,19 +272,22 @@
     <t>AttackModeFalluponArea</t>
   </si>
   <si>
-    <t>普通近战-捶地火锥</t>
-  </si>
-  <si>
-    <t>普通近战-捶地冰锥</t>
+    <t>下落范围攻击-火球</t>
+  </si>
+  <si>
+    <t>下落范围攻击-水球</t>
+  </si>
+  <si>
+    <t>下落范围攻击-冰球</t>
   </si>
   <si>
     <t>AttackModeFalluponChain</t>
   </si>
   <si>
-    <t>AttackMode_Thunder_1</t>
-  </si>
-  <si>
-    <t>远程攻击-下落雷击</t>
+    <t>900001&amp;900002</t>
+  </si>
+  <si>
+    <t>下落攻击-雷击</t>
   </si>
 </sst>
 </file>
@@ -894,11 +903,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1249,7 +1261,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -1259,7 +1271,7 @@
     <col min="6" max="6" width="27.875" customWidth="1"/>
     <col min="7" max="7" width="42.125" customWidth="1"/>
     <col min="8" max="8" width="25.375" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="9" max="9" width="25.125" customWidth="1"/>
     <col min="10" max="10" width="30.75" customWidth="1"/>
     <col min="11" max="13" width="11.5" customWidth="1"/>
     <col min="14" max="14" width="42.875" customWidth="1"/>
@@ -1336,7 +1348,7 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -1414,6 +1426,7 @@
       <c r="H4">
         <v>0</v>
       </c>
+      <c r="I4" s="2"/>
       <c r="K4">
         <v>1</v>
       </c>
@@ -1443,7 +1456,7 @@
       <c r="H5" t="s">
         <v>36</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>400001</v>
       </c>
       <c r="L5">
@@ -1472,7 +1485,7 @@
       <c r="H6">
         <v>1.5</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>700001</v>
       </c>
       <c r="L6">
@@ -1485,77 +1498,72 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" customFormat="1" spans="1:14">
       <c r="A7">
-        <v>200001</v>
+        <v>101003</v>
       </c>
       <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>800001</v>
+      </c>
+      <c r="L7">
+        <v>100001</v>
+      </c>
+      <c r="M7">
+        <v>200001</v>
+      </c>
+      <c r="N7" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" customFormat="1" spans="1:14">
+      <c r="A8">
+        <v>101004</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>800002</v>
+      </c>
+      <c r="L8">
+        <v>100001</v>
+      </c>
+      <c r="M8">
+        <v>200001</v>
+      </c>
+      <c r="N8" t="s">
         <v>40</v>
       </c>
-      <c r="F7">
-        <v>0.1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>100001</v>
-      </c>
-      <c r="M7">
-        <v>200001</v>
-      </c>
-      <c r="N7" t="s">
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9">
+        <v>200001</v>
+      </c>
+      <c r="B9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8">
-        <v>200002</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8">
-        <v>0.1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>100001</v>
-      </c>
-      <c r="M8">
-        <v>200001</v>
-      </c>
-      <c r="N8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:14">
-      <c r="A9">
-        <v>200003</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
       </c>
       <c r="F9">
         <v>0.1</v>
       </c>
+      <c r="I9" s="2"/>
       <c r="K9">
         <v>1</v>
       </c>
@@ -1566,25 +1574,26 @@
         <v>200001</v>
       </c>
       <c r="N9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
-        <v>200004</v>
+        <v>200002</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>0.1</v>
       </c>
+      <c r="I10" s="2"/>
       <c r="K10">
         <v>1</v>
       </c>
@@ -1595,31 +1604,26 @@
         <v>200001</v>
       </c>
       <c r="N10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" ht="12" customHeight="1" spans="1:14">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:14">
       <c r="A11">
-        <v>201001</v>
+        <v>200003</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
       </c>
       <c r="F11">
         <v>0.1</v>
       </c>
-      <c r="G11">
-        <v>11</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>100001</v>
-      </c>
+      <c r="I11" s="2"/>
       <c r="K11">
         <v>1</v>
       </c>
@@ -1630,32 +1634,26 @@
         <v>200001</v>
       </c>
       <c r="N11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:14">
       <c r="A12">
-        <v>201002</v>
+        <v>200004</v>
       </c>
       <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
         <v>51</v>
       </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12"/>
       <c r="F12">
         <v>0.1</v>
       </c>
-      <c r="G12">
-        <v>11</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>200001</v>
-      </c>
+      <c r="I12" s="2"/>
       <c r="K12">
         <v>1</v>
       </c>
@@ -1666,27 +1664,30 @@
         <v>200001</v>
       </c>
       <c r="N12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" ht="12" customHeight="1" spans="1:14">
+      <c r="A13">
+        <v>201001</v>
+      </c>
+      <c r="B13" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:14">
-      <c r="A13">
-        <v>202001</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F13">
         <v>0.1</v>
       </c>
       <c r="G13">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>100001</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1698,53 +1699,65 @@
         <v>200001</v>
       </c>
       <c r="N13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:14">
       <c r="A14">
-        <v>203001</v>
+        <v>201002</v>
       </c>
       <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14"/>
+      <c r="F14">
+        <v>0.1</v>
+      </c>
+      <c r="G14">
+        <v>11</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>200001</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>100001</v>
+      </c>
+      <c r="M14">
+        <v>200001</v>
+      </c>
+      <c r="N14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:14">
+      <c r="A15">
+        <v>202001</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
         <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14">
-        <v>11</v>
-      </c>
-      <c r="F14">
-        <v>0.25</v>
-      </c>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>100001</v>
-      </c>
-      <c r="M14">
-        <v>200001</v>
-      </c>
-      <c r="N14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" ht="15" customHeight="1" spans="1:14">
-      <c r="A15">
-        <v>204001</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
       </c>
       <c r="F15">
         <v>0.1</v>
       </c>
+      <c r="G15">
+        <v>30</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2"/>
       <c r="K15">
         <v>1</v>
       </c>
@@ -1755,12 +1768,12 @@
         <v>200001</v>
       </c>
       <c r="N15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" ht="15" customHeight="1" spans="1:14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:14">
       <c r="A16">
-        <v>204002</v>
+        <v>203001</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
@@ -1768,9 +1781,15 @@
       <c r="C16" t="s">
         <v>42</v>
       </c>
+      <c r="E16">
+        <v>11</v>
+      </c>
       <c r="F16">
-        <v>0.1</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16" s="2"/>
       <c r="K16">
         <v>1</v>
       </c>
@@ -1781,22 +1800,23 @@
         <v>200001</v>
       </c>
       <c r="N16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A17">
-        <v>204003</v>
+        <v>204001</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F17">
         <v>0.1</v>
       </c>
+      <c r="I17" s="2"/>
       <c r="K17">
         <v>1</v>
       </c>
@@ -1812,17 +1832,18 @@
     </row>
     <row r="18" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A18">
-        <v>205001</v>
+        <v>204002</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F18">
         <v>0.1</v>
       </c>
+      <c r="I18" s="2"/>
       <c r="K18">
         <v>1</v>
       </c>
@@ -1833,22 +1854,23 @@
         <v>200001</v>
       </c>
       <c r="N18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A19">
-        <v>205002</v>
+        <v>204003</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F19">
         <v>0.1</v>
       </c>
+      <c r="I19" s="2"/>
       <c r="K19">
         <v>1</v>
       </c>
@@ -1859,22 +1881,23 @@
         <v>200001</v>
       </c>
       <c r="N19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A20">
-        <v>205003</v>
+        <v>205001</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F20">
         <v>0.1</v>
       </c>
+      <c r="I20" s="2"/>
       <c r="K20">
         <v>1</v>
       </c>
@@ -1888,88 +1911,78 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A21">
-        <v>300001</v>
+        <v>205002</v>
       </c>
       <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21">
+        <v>0.1</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>100001</v>
+      </c>
+      <c r="M21">
+        <v>200001</v>
+      </c>
+      <c r="N21" t="s">
         <v>67</v>
       </c>
-      <c r="F21">
-        <v>1.5</v>
-      </c>
-      <c r="G21">
-        <v>11</v>
-      </c>
-      <c r="H21">
-        <v>1.5</v>
-      </c>
-      <c r="I21">
-        <v>300001</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>100001</v>
-      </c>
-      <c r="M21">
-        <v>200001</v>
-      </c>
-      <c r="N21" t="s">
+    </row>
+    <row r="22" customFormat="1" ht="15" customHeight="1" spans="1:14">
+      <c r="A22">
+        <v>205003</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22">
+        <v>0.1</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>100001</v>
+      </c>
+      <c r="M22">
+        <v>200001</v>
+      </c>
+      <c r="N22" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22">
-        <v>400001</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22">
-        <v>0.5</v>
-      </c>
-      <c r="G22">
-        <v>11</v>
-      </c>
-      <c r="H22">
-        <v>0.5</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>100001</v>
-      </c>
-      <c r="M22">
-        <v>200001</v>
-      </c>
-      <c r="N22" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23">
-        <v>400002</v>
+        <v>300001</v>
       </c>
       <c r="B23" t="s">
         <v>69</v>
       </c>
       <c r="F23">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G23">
         <v>11</v>
       </c>
       <c r="H23">
-        <v>0.5</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
+        <v>1.5</v>
+      </c>
+      <c r="I23" s="2">
+        <v>300001</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1981,27 +1994,31 @@
         <v>200001</v>
       </c>
       <c r="N23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24">
-        <v>500001</v>
+        <v>400001</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G24">
         <v>11</v>
       </c>
       <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>500001</v>
+        <v>0.5</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
       </c>
       <c r="L24">
         <v>100001</v>
@@ -2010,27 +2027,31 @@
         <v>200001</v>
       </c>
       <c r="N24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25">
-        <v>500002</v>
+        <v>400002</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G25">
         <v>11</v>
       </c>
       <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>500002</v>
+        <v>0.5</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
       </c>
       <c r="L25">
         <v>100001</v>
@@ -2039,38 +2060,47 @@
         <v>200001</v>
       </c>
       <c r="N25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26">
-        <v>600001</v>
+        <v>500001</v>
       </c>
       <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>11</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2">
+        <v>500001</v>
+      </c>
+      <c r="L26">
+        <v>100001</v>
+      </c>
+      <c r="M26">
+        <v>200001</v>
+      </c>
+      <c r="N26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27">
+        <v>500002</v>
+      </c>
+      <c r="B27" t="s">
         <v>76</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>600001</v>
-      </c>
-      <c r="L26">
-        <v>100001</v>
-      </c>
-      <c r="M26">
-        <v>200001</v>
-      </c>
-      <c r="N26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:14">
-      <c r="A27">
-        <v>700001</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
+      <c r="F27">
+        <v>1</v>
       </c>
       <c r="G27">
         <v>11</v>
@@ -2078,8 +2108,8 @@
       <c r="H27">
         <v>1</v>
       </c>
-      <c r="I27">
-        <v>800001</v>
+      <c r="I27" s="2">
+        <v>500002</v>
       </c>
       <c r="L27">
         <v>100001</v>
@@ -2088,24 +2118,21 @@
         <v>200001</v>
       </c>
       <c r="N27" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:14">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28">
-        <v>700002</v>
+        <v>600001</v>
       </c>
       <c r="B28" t="s">
         <v>78</v>
       </c>
-      <c r="G28">
-        <v>11</v>
-      </c>
       <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28">
-        <v>800002</v>
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>600001</v>
       </c>
       <c r="L28">
         <v>100001</v>
@@ -2114,51 +2141,132 @@
         <v>200001</v>
       </c>
       <c r="N28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:14">
+      <c r="A29">
+        <v>700001</v>
+      </c>
+      <c r="B29" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:14">
-      <c r="A29">
-        <v>800001</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="G29">
         <v>11</v>
       </c>
       <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="L29">
+        <v>100001</v>
+      </c>
+      <c r="M29">
+        <v>200001</v>
+      </c>
+      <c r="N29" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:14">
+      <c r="A30">
+        <v>700002</v>
+      </c>
+      <c r="B30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30">
+        <v>11</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="L30">
+        <v>100001</v>
+      </c>
+      <c r="M30">
+        <v>200001</v>
+      </c>
+      <c r="N30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:14">
+      <c r="A31">
+        <v>700003</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31">
+        <v>11</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="L31">
+        <v>100001</v>
+      </c>
+      <c r="M31">
+        <v>200001</v>
+      </c>
+      <c r="N31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:14">
+      <c r="A32">
+        <v>800001</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32">
+        <v>11</v>
+      </c>
+      <c r="H32">
         <v>1.5</v>
       </c>
-      <c r="L29">
-        <v>100001</v>
-      </c>
-      <c r="M29">
-        <v>200001</v>
-      </c>
-      <c r="N29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1"/>
-    <row r="31" ht="15" customHeight="1"/>
-    <row r="32" ht="15" customHeight="1"/>
+      <c r="I32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L32">
+        <v>100001</v>
+      </c>
+      <c r="M32">
+        <v>200001</v>
+      </c>
+      <c r="N32" t="s">
+        <v>86</v>
+      </c>
+    </row>
     <row r="33" ht="15" customHeight="1"/>
     <row r="34" ht="15" customHeight="1"/>
     <row r="35" ht="15" customHeight="1"/>
     <row r="36" ht="15" customHeight="1"/>
-    <row r="68" ht="12" customHeight="1"/>
-    <row r="69" ht="12" customHeight="1"/>
-    <row r="70" ht="12" customHeight="1"/>
+    <row r="37" ht="15" customHeight="1"/>
+    <row r="38" ht="15" customHeight="1"/>
+    <row r="39" ht="15" customHeight="1"/>
     <row r="71" ht="12" customHeight="1"/>
     <row r="72" ht="12" customHeight="1"/>
     <row r="73" ht="12" customHeight="1"/>
     <row r="74" ht="12" customHeight="1"/>
     <row r="75" ht="12" customHeight="1"/>
     <row r="76" ht="12" customHeight="1"/>
+    <row r="77" ht="12" customHeight="1"/>
+    <row r="78" ht="12" customHeight="1"/>
+    <row r="79" ht="12" customHeight="1"/>
   </sheetData>
   <sortState ref="A4:O88">
     <sortCondition ref="A4"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
   <si>
     <t>id</t>
   </si>
@@ -1273,7 +1273,8 @@
     <col min="8" max="8" width="25.375" customWidth="1"/>
     <col min="9" max="9" width="25.125" customWidth="1"/>
     <col min="10" max="10" width="30.75" customWidth="1"/>
-    <col min="11" max="13" width="11.5" customWidth="1"/>
+    <col min="11" max="11" width="23.875" customWidth="1"/>
+    <col min="12" max="13" width="11.5" customWidth="1"/>
     <col min="14" max="14" width="42.875" customWidth="1"/>
     <col min="15" max="15" width="25.125" customWidth="1"/>
   </cols>
@@ -2154,13 +2155,19 @@
       <c r="C29" t="s">
         <v>44</v>
       </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
       <c r="G29">
         <v>11</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I29" s="2"/>
+      <c r="K29">
+        <v>3</v>
+      </c>
       <c r="L29">
         <v>100001</v>
       </c>
@@ -2181,13 +2188,19 @@
       <c r="C30" t="s">
         <v>47</v>
       </c>
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
       <c r="G30">
         <v>11</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I30" s="2"/>
+      <c r="K30">
+        <v>3</v>
+      </c>
       <c r="L30">
         <v>100001</v>
       </c>
@@ -2208,13 +2221,19 @@
       <c r="C31" t="s">
         <v>50</v>
       </c>
+      <c r="D31" t="s">
+        <v>51</v>
+      </c>
       <c r="G31">
         <v>11</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I31" s="2"/>
+      <c r="K31">
+        <v>3</v>
+      </c>
       <c r="L31">
         <v>100001</v>
       </c>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="I29" s="2"/>
       <c r="K29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>100001</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="I30" s="2"/>
       <c r="K30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>100001</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="I31" s="2"/>
       <c r="K31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>100001</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="AttackModeInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -272,10 +272,19 @@
     <t>AttackModeFalluponArea</t>
   </si>
   <si>
+    <t>AttackMode_Fallupon_Meteorite_1</t>
+  </si>
+  <si>
     <t>下落范围攻击-火球</t>
   </si>
   <si>
+    <t>AttackMode_Fallupon_Water_1</t>
+  </si>
+  <si>
     <t>下落范围攻击-水球</t>
+  </si>
+  <si>
+    <t>AttackMode_Fallupon_Ice_1</t>
   </si>
   <si>
     <t>下落范围攻击-冰球</t>
@@ -2153,7 +2162,7 @@
         <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
         <v>45</v>
@@ -2164,9 +2173,11 @@
       <c r="H29">
         <v>1.5</v>
       </c>
-      <c r="I29" s="2"/>
+      <c r="I29" s="2">
+        <v>800001</v>
+      </c>
       <c r="K29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L29">
         <v>100001</v>
@@ -2175,7 +2186,7 @@
         <v>200001</v>
       </c>
       <c r="N29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:14">
@@ -2186,7 +2197,7 @@
         <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
@@ -2197,9 +2208,11 @@
       <c r="H30">
         <v>1.5</v>
       </c>
-      <c r="I30" s="2"/>
+      <c r="I30" s="2">
+        <v>800001</v>
+      </c>
       <c r="K30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L30">
         <v>100001</v>
@@ -2208,7 +2221,7 @@
         <v>200001</v>
       </c>
       <c r="N30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:14">
@@ -2219,7 +2232,7 @@
         <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
         <v>51</v>
@@ -2230,9 +2243,11 @@
       <c r="H31">
         <v>1.5</v>
       </c>
-      <c r="I31" s="2"/>
+      <c r="I31" s="2">
+        <v>800001</v>
+      </c>
       <c r="K31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L31">
         <v>100001</v>
@@ -2241,7 +2256,7 @@
         <v>200001</v>
       </c>
       <c r="N31" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:14">
@@ -2249,7 +2264,7 @@
         <v>800001</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G32">
         <v>11</v>
@@ -2258,7 +2273,7 @@
         <v>1.5</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L32">
         <v>100001</v>
@@ -2267,7 +2282,7 @@
         <v>200001</v>
       </c>
       <c r="N32" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="AttackModeInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>AttackModeMelee</t>
-  </si>
-  <si>
-    <t>AttackMode_MeleeNormal</t>
   </si>
   <si>
     <t>普通近战攻击</t>
@@ -1427,9 +1424,7 @@
       <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
+      <c r="C4"/>
       <c r="F4">
         <v>0.1</v>
       </c>
@@ -1447,7 +1442,7 @@
         <v>200001</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1455,7 +1450,7 @@
         <v>101001</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1464,7 +1459,7 @@
         <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I5" s="2">
         <v>400001</v>
@@ -1476,7 +1471,7 @@
         <v>200001</v>
       </c>
       <c r="N5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:14">
@@ -1484,7 +1479,7 @@
         <v>101002</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>0.1</v>
@@ -1505,7 +1500,7 @@
         <v>200001</v>
       </c>
       <c r="N6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:14">
@@ -1513,7 +1508,7 @@
         <v>101003</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -1531,7 +1526,7 @@
         <v>200001</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:14">
@@ -1539,7 +1534,7 @@
         <v>101004</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8">
         <v>11</v>
@@ -1557,7 +1552,7 @@
         <v>200001</v>
       </c>
       <c r="N8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1565,10 +1560,10 @@
         <v>200001</v>
       </c>
       <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
         <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
       </c>
       <c r="F9">
         <v>0.1</v>
@@ -1584,7 +1579,7 @@
         <v>200001</v>
       </c>
       <c r="N9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1592,13 +1587,13 @@
         <v>200002</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
         <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
       </c>
       <c r="F10">
         <v>0.1</v>
@@ -1614,7 +1609,7 @@
         <v>200001</v>
       </c>
       <c r="N10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:14">
@@ -1622,13 +1617,13 @@
         <v>200003</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
         <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
       </c>
       <c r="F11">
         <v>0.1</v>
@@ -1644,7 +1639,7 @@
         <v>200001</v>
       </c>
       <c r="N11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:14">
@@ -1652,13 +1647,13 @@
         <v>200004</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
         <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
       </c>
       <c r="F12">
         <v>0.1</v>
@@ -1674,7 +1669,7 @@
         <v>200001</v>
       </c>
       <c r="N12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" spans="1:14">
@@ -1682,10 +1677,10 @@
         <v>201001</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13">
         <v>0.1</v>
@@ -1709,7 +1704,7 @@
         <v>200001</v>
       </c>
       <c r="N13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:14">
@@ -1717,10 +1712,10 @@
         <v>201002</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14"/>
       <c r="F14">
@@ -1745,7 +1740,7 @@
         <v>200001</v>
       </c>
       <c r="N14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:14">
@@ -1753,10 +1748,10 @@
         <v>202001</v>
       </c>
       <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
         <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
       </c>
       <c r="F15">
         <v>0.1</v>
@@ -1778,7 +1773,7 @@
         <v>200001</v>
       </c>
       <c r="N15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:14">
@@ -1786,10 +1781,10 @@
         <v>203001</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16">
         <v>11</v>
@@ -1810,7 +1805,7 @@
         <v>200001</v>
       </c>
       <c r="N16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="15" customHeight="1" spans="1:14">
@@ -1818,10 +1813,10 @@
         <v>204001</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17">
         <v>0.1</v>
@@ -1837,7 +1832,7 @@
         <v>200001</v>
       </c>
       <c r="N17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="15" customHeight="1" spans="1:14">
@@ -1845,10 +1840,10 @@
         <v>204002</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18">
         <v>0.1</v>
@@ -1864,7 +1859,7 @@
         <v>200001</v>
       </c>
       <c r="N18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="15" customHeight="1" spans="1:14">
@@ -1872,10 +1867,10 @@
         <v>204003</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F19">
         <v>0.1</v>
@@ -1891,7 +1886,7 @@
         <v>200001</v>
       </c>
       <c r="N19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" customFormat="1" ht="15" customHeight="1" spans="1:14">
@@ -1899,10 +1894,10 @@
         <v>205001</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20">
         <v>0.1</v>
@@ -1918,7 +1913,7 @@
         <v>200001</v>
       </c>
       <c r="N20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" customFormat="1" ht="15" customHeight="1" spans="1:14">
@@ -1926,10 +1921,10 @@
         <v>205002</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F21">
         <v>0.1</v>
@@ -1945,7 +1940,7 @@
         <v>200001</v>
       </c>
       <c r="N21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" customFormat="1" ht="15" customHeight="1" spans="1:14">
@@ -1953,10 +1948,10 @@
         <v>205003</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F22">
         <v>0.1</v>
@@ -1972,7 +1967,7 @@
         <v>200001</v>
       </c>
       <c r="N22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1980,7 +1975,7 @@
         <v>300001</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F23">
         <v>1.5</v>
@@ -2004,7 +1999,7 @@
         <v>200001</v>
       </c>
       <c r="N23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2012,7 +2007,7 @@
         <v>400001</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F24">
         <v>0.5</v>
@@ -2037,7 +2032,7 @@
         <v>200001</v>
       </c>
       <c r="N24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -2045,7 +2040,7 @@
         <v>400002</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F25">
         <v>0.5</v>
@@ -2070,7 +2065,7 @@
         <v>200001</v>
       </c>
       <c r="N25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2078,7 +2073,7 @@
         <v>500001</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2099,7 +2094,7 @@
         <v>200001</v>
       </c>
       <c r="N26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2107,7 +2102,7 @@
         <v>500002</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -2128,7 +2123,7 @@
         <v>200001</v>
       </c>
       <c r="N27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2136,7 +2131,7 @@
         <v>600001</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2151,7 +2146,7 @@
         <v>200001</v>
       </c>
       <c r="N28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:14">
@@ -2159,13 +2154,13 @@
         <v>700001</v>
       </c>
       <c r="B29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s">
         <v>80</v>
       </c>
-      <c r="C29" t="s">
-        <v>81</v>
-      </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G29">
         <v>11</v>
@@ -2186,7 +2181,7 @@
         <v>200001</v>
       </c>
       <c r="N29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:14">
@@ -2194,13 +2189,13 @@
         <v>700002</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G30">
         <v>11</v>
@@ -2221,7 +2216,7 @@
         <v>200001</v>
       </c>
       <c r="N30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:14">
@@ -2229,13 +2224,13 @@
         <v>700003</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G31">
         <v>11</v>
@@ -2256,7 +2251,7 @@
         <v>200001</v>
       </c>
       <c r="N31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:14">
@@ -2264,7 +2259,7 @@
         <v>800001</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G32">
         <v>11</v>
@@ -2273,16 +2268,16 @@
         <v>1.5</v>
       </c>
       <c r="I32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L32">
+        <v>100001</v>
+      </c>
+      <c r="M32">
+        <v>200001</v>
+      </c>
+      <c r="N32" t="s">
         <v>88</v>
-      </c>
-      <c r="L32">
-        <v>100001</v>
-      </c>
-      <c r="M32">
-        <v>200001</v>
-      </c>
-      <c r="N32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="AttackModeInfo" sheetId="1" r:id="rId1"/>
@@ -909,7 +909,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -917,6 +917,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1424,7 +1427,6 @@
       <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="C4"/>
       <c r="F4">
         <v>0.1</v>
       </c>
@@ -1438,8 +1440,8 @@
       <c r="L4">
         <v>100001</v>
       </c>
-      <c r="M4">
-        <v>200001</v>
+      <c r="M4" s="3">
+        <v>200002</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
@@ -1468,7 +1470,7 @@
         <v>100001</v>
       </c>
       <c r="M5">
-        <v>200001</v>
+        <v>200007</v>
       </c>
       <c r="N5" t="s">
         <v>36</v>
@@ -1497,7 +1499,7 @@
         <v>100001</v>
       </c>
       <c r="M6">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N6" t="s">
         <v>37</v>
@@ -1522,8 +1524,8 @@
       <c r="L7">
         <v>100001</v>
       </c>
-      <c r="M7">
-        <v>200001</v>
+      <c r="M7" s="3">
+        <v>420007</v>
       </c>
       <c r="N7" t="s">
         <v>38</v>
@@ -1548,8 +1550,8 @@
       <c r="L8">
         <v>100001</v>
       </c>
-      <c r="M8">
-        <v>200001</v>
+      <c r="M8" s="3">
+        <v>420007</v>
       </c>
       <c r="N8" t="s">
         <v>39</v>
@@ -1575,8 +1577,8 @@
       <c r="L9">
         <v>100001</v>
       </c>
-      <c r="M9">
-        <v>200001</v>
+      <c r="M9" s="3">
+        <v>420011</v>
       </c>
       <c r="N9" t="s">
         <v>42</v>
@@ -1605,8 +1607,8 @@
       <c r="L10">
         <v>100001</v>
       </c>
-      <c r="M10">
-        <v>200001</v>
+      <c r="M10" s="3">
+        <v>420003</v>
       </c>
       <c r="N10" t="s">
         <v>45</v>
@@ -1635,8 +1637,8 @@
       <c r="L11">
         <v>100001</v>
       </c>
-      <c r="M11">
-        <v>200001</v>
+      <c r="M11" s="3">
+        <v>420003</v>
       </c>
       <c r="N11" t="s">
         <v>48</v>
@@ -1665,8 +1667,8 @@
       <c r="L12">
         <v>100001</v>
       </c>
-      <c r="M12">
-        <v>200001</v>
+      <c r="M12" s="3">
+        <v>420003</v>
       </c>
       <c r="N12" t="s">
         <v>51</v>
@@ -1701,7 +1703,7 @@
         <v>100001</v>
       </c>
       <c r="M13">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N13" t="s">
         <v>53</v>
@@ -1737,7 +1739,7 @@
         <v>100001</v>
       </c>
       <c r="M14">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N14" t="s">
         <v>54</v>
@@ -1770,7 +1772,7 @@
         <v>100001</v>
       </c>
       <c r="M15">
-        <v>200001</v>
+        <v>6</v>
       </c>
       <c r="N15" t="s">
         <v>57</v>
@@ -1802,7 +1804,7 @@
         <v>100001</v>
       </c>
       <c r="M16">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N16" t="s">
         <v>59</v>
@@ -1829,7 +1831,7 @@
         <v>100001</v>
       </c>
       <c r="M17">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N17" t="s">
         <v>61</v>
@@ -1856,7 +1858,7 @@
         <v>100001</v>
       </c>
       <c r="M18">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N18" t="s">
         <v>62</v>
@@ -1883,7 +1885,7 @@
         <v>100001</v>
       </c>
       <c r="M19">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N19" t="s">
         <v>63</v>
@@ -1910,7 +1912,7 @@
         <v>100001</v>
       </c>
       <c r="M20">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N20" t="s">
         <v>65</v>
@@ -1937,7 +1939,7 @@
         <v>100001</v>
       </c>
       <c r="M21">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N21" t="s">
         <v>66</v>
@@ -1964,7 +1966,7 @@
         <v>100001</v>
       </c>
       <c r="M22">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N22" t="s">
         <v>67</v>
@@ -1996,7 +1998,7 @@
         <v>100001</v>
       </c>
       <c r="M23">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N23" t="s">
         <v>69</v>
@@ -2029,7 +2031,7 @@
         <v>100001</v>
       </c>
       <c r="M24">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N24" t="s">
         <v>71</v>
@@ -2062,7 +2064,7 @@
         <v>100001</v>
       </c>
       <c r="M25">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N25" t="s">
         <v>72</v>
@@ -2090,8 +2092,8 @@
       <c r="L26">
         <v>100001</v>
       </c>
-      <c r="M26">
-        <v>200001</v>
+      <c r="M26" s="3">
+        <v>470001</v>
       </c>
       <c r="N26" t="s">
         <v>74</v>
@@ -2119,8 +2121,8 @@
       <c r="L27">
         <v>100001</v>
       </c>
-      <c r="M27">
-        <v>200001</v>
+      <c r="M27" s="3">
+        <v>470001</v>
       </c>
       <c r="N27" t="s">
         <v>76</v>
@@ -2143,7 +2145,7 @@
         <v>100001</v>
       </c>
       <c r="M28">
-        <v>200001</v>
+        <v>6</v>
       </c>
       <c r="N28" t="s">
         <v>78</v>
@@ -2178,7 +2180,7 @@
         <v>100001</v>
       </c>
       <c r="M29">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N29" t="s">
         <v>81</v>
@@ -2213,7 +2215,7 @@
         <v>100001</v>
       </c>
       <c r="M30">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N30" t="s">
         <v>83</v>
@@ -2248,7 +2250,7 @@
         <v>100001</v>
       </c>
       <c r="M31">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N31" t="s">
         <v>85</v>
@@ -2274,7 +2276,7 @@
         <v>100001</v>
       </c>
       <c r="M32">
-        <v>200001</v>
+        <v>420008</v>
       </c>
       <c r="N32" t="s">
         <v>88</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1472,11 +1472,11 @@
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>1.5,1,0.25</t>
+          <t>3,1,0.25</t>
         </is>
       </c>
       <c r="I9" s="0" t="n">
-        <v>400001</v>
+        <v>400002</v>
       </c>
       <c r="M9" s="0" t="n">
         <v>100001</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="0" t="inlineStr">
         <is>
-          <t>BOSS技能-向前挥砍攻击前方3格</t>
+          <t>BOSS技能-向前挥砍攻击前方6格</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1136,7 +1136,12 @@
           <t>sound_hit</t>
         </is>
       </c>
-      <c r="O1" s="0" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>start_pos_offset</t>
+        </is>
+      </c>
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1213,7 +1218,12 @@
           <t>long</t>
         </is>
       </c>
-      <c r="O2" s="0" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1290,7 +1300,12 @@
           <t>音效-击中</t>
         </is>
       </c>
-      <c r="O3" s="0" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>攻击起始位置偏移(x,y,z,空=0,叠加在生物攻击起始位置之上)</t>
+        </is>
+      </c>
+      <c r="P3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1321,7 +1336,7 @@
       <c r="N4" s="0" t="n">
         <v>200002</v>
       </c>
-      <c r="O4" s="0" t="inlineStr">
+      <c r="P4" s="0" t="inlineStr">
         <is>
           <t>普通近战攻击</t>
         </is>
@@ -1356,7 +1371,7 @@
       <c r="N5" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="O5" s="0" t="inlineStr">
+      <c r="P5" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-前方镰刀打击</t>
         </is>
@@ -1389,7 +1404,7 @@
       <c r="N6" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O6" s="0" t="inlineStr">
+      <c r="P6" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-捶地攻击</t>
         </is>
@@ -1419,7 +1434,7 @@
       <c r="N7" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="O7" s="0" t="inlineStr">
+      <c r="P7" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地火锥</t>
         </is>
@@ -1449,7 +1464,7 @@
       <c r="N8" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="O8" s="0" t="inlineStr">
+      <c r="P8" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地冰锥</t>
         </is>
@@ -1484,7 +1499,7 @@
       <c r="N9" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="O9" s="0" t="inlineStr">
+      <c r="P9" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-向前挥砍攻击前方6格</t>
         </is>
@@ -1520,7 +1535,7 @@
       <c r="N10" s="0" t="n">
         <v>420011</v>
       </c>
-      <c r="O10" s="0" t="inlineStr">
+      <c r="P10" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击</t>
         </is>
@@ -1558,7 +1573,7 @@
       <c r="N11" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="O11" s="0" t="inlineStr">
+      <c r="P11" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击</t>
         </is>
@@ -1596,7 +1611,7 @@
       <c r="N12" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="O12" s="0" t="inlineStr">
+      <c r="P12" s="0" t="inlineStr">
         <is>
           <t>远程攻击-水球直线攻击</t>
         </is>
@@ -1634,7 +1649,7 @@
       <c r="N13" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="O13" s="0" t="inlineStr">
+      <c r="P13" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击</t>
         </is>
@@ -1675,7 +1690,7 @@
       <c r="N14" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O14" s="0" t="inlineStr">
+      <c r="P14" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击-范围伤害</t>
         </is>
@@ -1717,7 +1732,7 @@
       <c r="N15" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O15" s="0" t="inlineStr">
+      <c r="P15" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击-范围伤害</t>
         </is>
@@ -1756,7 +1771,7 @@
       <c r="N16" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="O16" s="0" t="inlineStr">
+      <c r="P16" s="0" t="inlineStr">
         <is>
           <t>远程攻击-跟踪-爱心</t>
         </is>
@@ -1794,7 +1809,7 @@
       <c r="N17" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O17" s="0" t="inlineStr">
+      <c r="P17" s="0" t="inlineStr">
         <is>
           <t>远程攻击-抛物线-石头</t>
         </is>
@@ -1827,7 +1842,7 @@
       <c r="N18" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O18" s="0" t="inlineStr">
+      <c r="P18" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂弓箭</t>
         </is>
@@ -1860,7 +1875,7 @@
       <c r="N19" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O19" s="0" t="inlineStr">
+      <c r="P19" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂火球</t>
         </is>
@@ -1893,7 +1908,7 @@
       <c r="N20" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O20" s="0" t="inlineStr">
+      <c r="P20" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂冰球</t>
         </is>
@@ -1926,7 +1941,7 @@
       <c r="N21" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O21" s="0" t="inlineStr">
+      <c r="P21" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透</t>
         </is>
@@ -1959,7 +1974,7 @@
       <c r="N22" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O22" s="0" t="inlineStr">
+      <c r="P22" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透火锥</t>
         </is>
@@ -1992,7 +2007,7 @@
       <c r="N23" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O23" s="0" t="inlineStr">
+      <c r="P23" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透冰锥</t>
         </is>
@@ -2028,7 +2043,7 @@
       <c r="N24" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O24" s="0" t="inlineStr">
+      <c r="P24" s="0" t="inlineStr">
         <is>
           <t>爆炸范围攻击-火焰</t>
         </is>
@@ -2065,7 +2080,7 @@
       <c r="N25" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O25" s="0" t="inlineStr">
+      <c r="P25" s="0" t="inlineStr">
         <is>
           <t>重叠攻击-粘液减速</t>
         </is>
@@ -2102,7 +2117,7 @@
       <c r="N26" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O26" s="0" t="inlineStr">
+      <c r="P26" s="0" t="inlineStr">
         <is>
           <t>重叠攻击-中毒</t>
         </is>
@@ -2135,7 +2150,7 @@
       <c r="N27" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="O27" s="0" t="inlineStr">
+      <c r="P27" s="0" t="inlineStr">
         <is>
           <t>加血</t>
         </is>
@@ -2168,7 +2183,7 @@
       <c r="N28" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="O28" s="0" t="inlineStr">
+      <c r="P28" s="0" t="inlineStr">
         <is>
           <t>加护甲</t>
         </is>
@@ -2195,7 +2210,7 @@
       <c r="N29" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="O29" s="0" t="inlineStr">
+      <c r="P29" s="0" t="inlineStr">
         <is>
           <t>引诱敌人到当前线路</t>
         </is>
@@ -2238,7 +2253,12 @@
       <c r="N30" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O30" s="0" t="inlineStr">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="P30" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-火球</t>
         </is>
@@ -2281,7 +2301,12 @@
       <c r="N31" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O31" s="0" t="inlineStr">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="P31" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-水球</t>
         </is>
@@ -2324,7 +2349,7 @@
       <c r="N32" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O32" s="0" t="inlineStr">
+      <c r="P32" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-冰球</t>
         </is>
@@ -2356,7 +2381,7 @@
       <c r="N33" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O33" s="0" t="inlineStr">
+      <c r="P33" s="0" t="inlineStr">
         <is>
           <t>下落攻击-雷击</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1081,67 +1081,72 @@
           <t>prefab_name</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>visual_name</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>attack_search_type</t>
         </is>
       </c>
-      <c r="F1" s="0" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>collider_size</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>collider_area_type</t>
         </is>
       </c>
-      <c r="H1" s="0" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>collider_area_size</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>effect_hit</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>effect_damage</t>
         </is>
       </c>
-      <c r="K1" s="0" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>speed_move</t>
         </is>
       </c>
-      <c r="L1" s="0" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>sound_start</t>
         </is>
       </c>
-      <c r="M1" s="0" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>sound_miss</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>sound_hit</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>start_pos_offset</t>
         </is>
       </c>
-      <c r="P1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1163,67 +1168,72 @@
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" s="0" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="0" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L2" s="0" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="M2" s="0" t="inlineStr">
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="N2" s="0" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P2" s="0" t="inlineStr">
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1245,67 +1255,72 @@
           <t>预制名字</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>视觉名字(DSP Instancing 批量渲染分桶key,空=不走批量渲染,与prefab_name独立)</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>攻击buff（id:创建概率&amp;id:创建概率）</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>攻击搜索敌人类型（用于检测弹道是否打到）</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>碰撞检测大小（用于点到点）</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>碰撞范围搜索敌人类型（用于范围弹道检测）</t>
         </is>
       </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>碰撞范围检测（用于范围）</t>
         </is>
       </c>
-      <c r="I3" s="0" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>打击之后的特效(用&amp;分隔)</t>
         </is>
       </c>
-      <c r="J3" s="0" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>受伤特效（默认不填，0为关闭）</t>
         </is>
       </c>
-      <c r="K3" s="0" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>移动速度</t>
         </is>
       </c>
-      <c r="L3" s="0" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>音效-起始</t>
         </is>
       </c>
-      <c r="M3" s="0" t="inlineStr">
+      <c r="N3" s="0" t="inlineStr">
         <is>
           <t>音效-miss</t>
         </is>
       </c>
-      <c r="N3" s="0" t="inlineStr">
+      <c r="O3" s="0" t="inlineStr">
         <is>
           <t>音效-击中</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" s="0" t="inlineStr">
         <is>
           <t>攻击起始位置偏移(x,y,z,空=0,叠加在生物攻击起始位置之上)</t>
         </is>
       </c>
-      <c r="P3" s="0" t="inlineStr">
+      <c r="Q3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1320,23 +1335,23 @@
           <t>AttackModeMelee</t>
         </is>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="G4" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="I4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="0" t="n"/>
-      <c r="K4" s="0" t="n">
+      <c r="J4" s="0" t="n"/>
+      <c r="L4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N4" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O4" s="0" t="n">
         <v>200002</v>
       </c>
-      <c r="P4" s="0" t="inlineStr">
+      <c r="Q4" s="0" t="inlineStr">
         <is>
           <t>普通近战攻击</t>
         </is>
@@ -1351,27 +1366,27 @@
           <t>AttackModeMeleeArea</t>
         </is>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="G5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="H5" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>0.5,1,1</t>
         </is>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="J5" s="0" t="n">
         <v>400001</v>
       </c>
-      <c r="M5" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N5" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O5" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="P5" s="0" t="inlineStr">
+      <c r="Q5" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-前方镰刀打击</t>
         </is>
@@ -1386,25 +1401,25 @@
           <t>AttackModeMeleeArea</t>
         </is>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="G6" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="H6" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="I6" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="J6" s="0" t="n">
         <v>700001</v>
       </c>
-      <c r="M6" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N6" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O6" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P6" s="0" t="inlineStr">
+      <c r="Q6" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-捶地攻击</t>
         </is>
@@ -1419,22 +1434,22 @@
           <t>AttackModeMeleeArea</t>
         </is>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="H7" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="I7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="J7" s="0" t="n">
         <v>800001</v>
       </c>
-      <c r="M7" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N7" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O7" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="P7" s="0" t="inlineStr">
+      <c r="Q7" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地火锥</t>
         </is>
@@ -1449,22 +1464,22 @@
           <t>AttackModeMeleeArea</t>
         </is>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="H8" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="I8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="J8" s="0" t="n">
         <v>800002</v>
       </c>
-      <c r="M8" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N8" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O8" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="P8" s="0" t="inlineStr">
+      <c r="Q8" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地冰锥</t>
         </is>
@@ -1479,27 +1494,27 @@
           <t>AttackModeMeleeArea</t>
         </is>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="G9" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="H9" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="H9" s="0" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>3,1,0.25</t>
         </is>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="J9" s="0" t="n">
         <v>400002</v>
       </c>
-      <c r="M9" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N9" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O9" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="P9" s="0" t="inlineStr">
+      <c r="Q9" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-向前挥砍攻击前方6格</t>
         </is>
@@ -1519,23 +1534,23 @@
           <t>AttackMode_RangedNormal</t>
         </is>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="G10" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I10" s="0" t="n"/>
-      <c r="K10" s="0" t="n">
+      <c r="J10" s="0" t="n"/>
+      <c r="L10" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>310001</v>
       </c>
-      <c r="M10" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N10" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O10" s="0" t="n">
         <v>420011</v>
       </c>
-      <c r="P10" s="0" t="inlineStr">
+      <c r="Q10" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击</t>
         </is>
@@ -1555,25 +1570,25 @@
           <t>AttackMode_RangedFireBall</t>
         </is>
       </c>
-      <c r="D11" s="0" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>1000500001:0.5</t>
         </is>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="G11" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I11" s="0" t="n"/>
-      <c r="K11" s="0" t="n">
+      <c r="J11" s="0" t="n"/>
+      <c r="L11" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N11" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O11" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="P11" s="0" t="inlineStr">
+      <c r="Q11" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击</t>
         </is>
@@ -1593,25 +1608,25 @@
           <t>AttackMode_RangedWaterBall</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>1000600001:0.5</t>
         </is>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="G12" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I12" s="0" t="n"/>
-      <c r="K12" s="0" t="n">
+      <c r="J12" s="0" t="n"/>
+      <c r="L12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N12" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O12" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="P12" s="0" t="inlineStr">
+      <c r="Q12" s="0" t="inlineStr">
         <is>
           <t>远程攻击-水球直线攻击</t>
         </is>
@@ -1631,25 +1646,25 @@
           <t>AttackMode_RangedIceBall</t>
         </is>
       </c>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>1000700001:0.5</t>
         </is>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="G13" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I13" s="0" t="n"/>
-      <c r="K13" s="0" t="n">
+      <c r="J13" s="0" t="n"/>
+      <c r="L13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M13" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N13" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O13" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="P13" s="0" t="inlineStr">
+      <c r="Q13" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击</t>
         </is>
@@ -1669,28 +1684,28 @@
           <t>AttackMode_RangedFireBall</t>
         </is>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="G14" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="H14" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="I14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="K14" s="0" t="n">
+      <c r="J14" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="L14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M14" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N14" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O14" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P14" s="0" t="inlineStr">
+      <c r="Q14" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击-范围伤害</t>
         </is>
@@ -1710,29 +1725,29 @@
           <t>AttackMode_RangedIceBall</t>
         </is>
       </c>
-      <c r="D15" s="0" t="n"/>
-      <c r="F15" s="0" t="n">
+      <c r="E15" s="0" t="n"/>
+      <c r="G15" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="H15" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="I15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="0" t="n">
+      <c r="J15" s="0" t="n">
         <v>200001</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="L15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N15" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O15" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P15" s="0" t="inlineStr">
+      <c r="Q15" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击-范围伤害</t>
         </is>
@@ -1752,26 +1767,26 @@
           <t>AttackMode_RangedLove</t>
         </is>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="G16" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="H16" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="I16" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="0" t="n"/>
-      <c r="K16" s="0" t="n">
+      <c r="J16" s="0" t="n"/>
+      <c r="L16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M16" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N16" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O16" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="P16" s="0" t="inlineStr">
+      <c r="Q16" s="0" t="inlineStr">
         <is>
           <t>远程攻击-跟踪-爱心</t>
         </is>
@@ -1791,25 +1806,25 @@
           <t>AttackMode_RangedNormal</t>
         </is>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="F17" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="G17" s="0" t="n">
         <v>0.25</v>
       </c>
-      <c r="G17" s="0" t="n"/>
       <c r="H17" s="0" t="n"/>
       <c r="I17" s="0" t="n"/>
-      <c r="K17" s="0" t="n">
+      <c r="J17" s="0" t="n"/>
+      <c r="L17" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M17" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N17" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O17" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P17" s="0" t="inlineStr">
+      <c r="Q17" s="0" t="inlineStr">
         <is>
           <t>远程攻击-抛物线-石头</t>
         </is>
@@ -1829,20 +1844,20 @@
           <t>AttackMode_RangedNormal</t>
         </is>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="G18" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I18" s="0" t="n"/>
-      <c r="K18" s="0" t="n">
+      <c r="J18" s="0" t="n"/>
+      <c r="L18" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M18" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N18" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O18" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P18" s="0" t="inlineStr">
+      <c r="Q18" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂弓箭</t>
         </is>
@@ -1862,20 +1877,20 @@
           <t>AttackMode_RangedFireBall</t>
         </is>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="G19" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I19" s="0" t="n"/>
-      <c r="K19" s="0" t="n">
+      <c r="J19" s="0" t="n"/>
+      <c r="L19" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M19" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N19" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O19" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P19" s="0" t="inlineStr">
+      <c r="Q19" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂火球</t>
         </is>
@@ -1895,20 +1910,20 @@
           <t>AttackMode_RangedIceBall</t>
         </is>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="G20" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I20" s="0" t="n"/>
-      <c r="K20" s="0" t="n">
+      <c r="J20" s="0" t="n"/>
+      <c r="L20" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N20" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O20" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P20" s="0" t="inlineStr">
+      <c r="Q20" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂冰球</t>
         </is>
@@ -1928,20 +1943,20 @@
           <t>AttackMode_RangedNormal</t>
         </is>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="G21" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I21" s="0" t="n"/>
-      <c r="K21" s="0" t="n">
+      <c r="J21" s="0" t="n"/>
+      <c r="L21" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M21" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N21" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O21" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P21" s="0" t="inlineStr">
+      <c r="Q21" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透</t>
         </is>
@@ -1961,20 +1976,20 @@
           <t>AttackMode_RangedFireBall</t>
         </is>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="G22" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I22" s="0" t="n"/>
-      <c r="K22" s="0" t="n">
+      <c r="J22" s="0" t="n"/>
+      <c r="L22" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M22" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N22" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O22" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P22" s="0" t="inlineStr">
+      <c r="Q22" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透火锥</t>
         </is>
@@ -1994,20 +2009,20 @@
           <t>AttackMode_RangedIceBall</t>
         </is>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="G23" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I23" s="0" t="n"/>
-      <c r="K23" s="0" t="n">
+      <c r="J23" s="0" t="n"/>
+      <c r="L23" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M23" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N23" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O23" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P23" s="0" t="inlineStr">
+      <c r="Q23" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透冰锥</t>
         </is>
@@ -2022,28 +2037,28 @@
           <t>AttackModeExplosion</t>
         </is>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="G24" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="H24" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="I24" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="I24" s="0" t="n">
+      <c r="J24" s="0" t="n">
         <v>300001</v>
       </c>
-      <c r="K24" s="0" t="n">
+      <c r="L24" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N24" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O24" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P24" s="0" t="inlineStr">
+      <c r="Q24" s="0" t="inlineStr">
         <is>
           <t>爆炸范围攻击-火焰</t>
         </is>
@@ -2058,29 +2073,29 @@
           <t>AttackModeOverlap</t>
         </is>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="G25" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="H25" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="I25" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="I25" s="0" t="n"/>
-      <c r="J25" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="J25" s="0" t="n"/>
       <c r="K25" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="0" t="n">
-        <v>100001</v>
+      <c r="L25" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="N25" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O25" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P25" s="0" t="inlineStr">
+      <c r="Q25" s="0" t="inlineStr">
         <is>
           <t>重叠攻击-粘液减速</t>
         </is>
@@ -2095,29 +2110,29 @@
           <t>AttackModeOverlap</t>
         </is>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="G26" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="H26" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="I26" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="I26" s="0" t="n"/>
-      <c r="J26" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="J26" s="0" t="n"/>
       <c r="K26" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="0" t="n">
-        <v>100001</v>
+      <c r="L26" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="N26" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O26" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P26" s="0" t="inlineStr">
+      <c r="Q26" s="0" t="inlineStr">
         <is>
           <t>重叠攻击-中毒</t>
         </is>
@@ -2132,25 +2147,25 @@
           <t>AttackModeRegainHP</t>
         </is>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="G27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="H27" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="I27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="0" t="n">
+      <c r="J27" s="0" t="n">
         <v>500001</v>
       </c>
-      <c r="M27" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N27" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O27" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="P27" s="0" t="inlineStr">
+      <c r="Q27" s="0" t="inlineStr">
         <is>
           <t>加血</t>
         </is>
@@ -2165,25 +2180,25 @@
           <t>AttackModeRegainDR</t>
         </is>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="G28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="H28" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="I28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="0" t="n">
+      <c r="J28" s="0" t="n">
         <v>500002</v>
       </c>
-      <c r="M28" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N28" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O28" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="P28" s="0" t="inlineStr">
+      <c r="Q28" s="0" t="inlineStr">
         <is>
           <t>加护甲</t>
         </is>
@@ -2198,19 +2213,19 @@
           <t>AttackModeLure</t>
         </is>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="I29" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="0" t="n">
+      <c r="J29" s="0" t="n">
         <v>600001</v>
       </c>
-      <c r="M29" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N29" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O29" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="P29" s="0" t="inlineStr">
+      <c r="Q29" s="0" t="inlineStr">
         <is>
           <t>引诱敌人到当前线路</t>
         </is>
@@ -2230,35 +2245,35 @@
           <t>AttackMode_Fallupon_Meteorite_1</t>
         </is>
       </c>
-      <c r="D30" s="0" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>1000500001:0.5</t>
         </is>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="H30" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="I30" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="I30" s="0" t="n">
+      <c r="J30" s="0" t="n">
         <v>800001</v>
       </c>
-      <c r="K30" s="0" t="n">
+      <c r="L30" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="M30" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N30" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O30" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" s="0" t="inlineStr">
         <is>
           <t>0,6,0</t>
         </is>
       </c>
-      <c r="P30" s="0" t="inlineStr">
+      <c r="Q30" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-火球</t>
         </is>
@@ -2278,35 +2293,35 @@
           <t>AttackMode_Fallupon_Water_1</t>
         </is>
       </c>
-      <c r="D31" s="0" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>1000600001:0.5</t>
         </is>
       </c>
-      <c r="G31" s="0" t="n">
+      <c r="H31" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H31" s="0" t="n">
+      <c r="I31" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="I31" s="0" t="n">
+      <c r="J31" s="0" t="n">
         <v>800001</v>
       </c>
-      <c r="K31" s="0" t="n">
+      <c r="L31" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="M31" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N31" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O31" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" s="0" t="inlineStr">
         <is>
           <t>0,6,0</t>
         </is>
       </c>
-      <c r="P31" s="0" t="inlineStr">
+      <c r="Q31" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-水球</t>
         </is>
@@ -2326,30 +2341,30 @@
           <t>AttackMode_Fallupon_Ice_1</t>
         </is>
       </c>
-      <c r="D32" s="0" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>1000700001:0.5</t>
         </is>
       </c>
-      <c r="G32" s="0" t="n">
+      <c r="H32" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="I32" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="I32" s="0" t="n">
+      <c r="J32" s="0" t="n">
         <v>800001</v>
       </c>
-      <c r="K32" s="0" t="n">
+      <c r="L32" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="M32" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N32" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O32" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P32" s="0" t="inlineStr">
+      <c r="Q32" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-冰球</t>
         </is>
@@ -2364,24 +2379,24 @@
           <t>AttackModeFalluponChain</t>
         </is>
       </c>
-      <c r="G33" s="0" t="n">
+      <c r="H33" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="I33" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="I33" s="0" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>900001&amp;900002</t>
         </is>
       </c>
-      <c r="M33" s="0" t="n">
-        <v>100001</v>
-      </c>
       <c r="N33" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O33" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="P33" s="0" t="inlineStr">
+      <c r="Q33" s="0" t="inlineStr">
         <is>
           <t>下落攻击-雷击</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1156,7 +1156,12 @@
           <t>child_attack_mode_id</t>
         </is>
       </c>
-      <c r="S1" s="0" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>damage_add_rate</t>
+        </is>
+      </c>
+      <c r="T1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1253,7 +1258,12 @@
           <t>long</t>
         </is>
       </c>
-      <c r="S2" s="0" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1350,7 +1360,12 @@
           <t>子弹道攻击模块id(仅分裂弹AttackModeRangedSplit使用:本行退化为发射器,由它按分裂道路逐条发射该id的子弹道;0/空=不使用)</t>
         </is>
       </c>
-      <c r="S3" s="0" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>伤害加成比例(最终伤害=攻击者ATK×该比例;0或空=无加成按1倍)</t>
+        </is>
+      </c>
+      <c r="T3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1381,7 +1396,7 @@
       <c r="O4" s="0" t="n">
         <v>200002</v>
       </c>
-      <c r="S4" s="0" t="inlineStr">
+      <c r="T4" s="0" t="inlineStr">
         <is>
           <t>普通近战攻击</t>
         </is>
@@ -1416,7 +1431,7 @@
       <c r="O5" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="S5" s="0" t="inlineStr">
+      <c r="T5" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-前方镰刀打击</t>
         </is>
@@ -1449,7 +1464,7 @@
       <c r="O6" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S6" s="0" t="inlineStr">
+      <c r="T6" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-捶地攻击</t>
         </is>
@@ -1479,7 +1494,7 @@
       <c r="O7" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="S7" s="0" t="inlineStr">
+      <c r="T7" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地火锥</t>
         </is>
@@ -1509,7 +1524,7 @@
       <c r="O8" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="S8" s="0" t="inlineStr">
+      <c r="T8" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地冰锥</t>
         </is>
@@ -1544,7 +1559,7 @@
       <c r="O9" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="S9" s="0" t="inlineStr">
+      <c r="T9" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-向前挥砍攻击前方6格</t>
         </is>
@@ -1586,7 +1601,7 @@
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="S10" s="0" t="inlineStr">
+      <c r="T10" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击</t>
         </is>
@@ -1602,7 +1617,7 @@
         </is>
       </c>
       <c r="C11" s="0" t="n"/>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedFireBall</t>
         </is>
@@ -1625,7 +1640,7 @@
       <c r="O11" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="S11" s="0" t="inlineStr">
+      <c r="T11" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击</t>
         </is>
@@ -1663,7 +1678,7 @@
       <c r="O12" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="S12" s="0" t="inlineStr">
+      <c r="T12" s="0" t="inlineStr">
         <is>
           <t>远程攻击-水球直线攻击</t>
         </is>
@@ -1679,7 +1694,7 @@
         </is>
       </c>
       <c r="C13" s="0" t="n"/>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedIceBall</t>
         </is>
@@ -1702,7 +1717,7 @@
       <c r="O13" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="S13" s="0" t="inlineStr">
+      <c r="T13" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击</t>
         </is>
@@ -1718,7 +1733,7 @@
         </is>
       </c>
       <c r="C14" s="0" t="n"/>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedFireBall</t>
         </is>
@@ -1744,7 +1759,7 @@
       <c r="O14" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S14" s="0" t="inlineStr">
+      <c r="T14" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击-范围伤害</t>
         </is>
@@ -1760,7 +1775,7 @@
         </is>
       </c>
       <c r="C15" s="0" t="n"/>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedIceBall</t>
         </is>
@@ -1787,7 +1802,7 @@
       <c r="O15" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S15" s="0" t="inlineStr">
+      <c r="T15" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击-范围伤害</t>
         </is>
@@ -1826,7 +1841,7 @@
       <c r="O16" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="S16" s="0" t="inlineStr">
+      <c r="T16" s="0" t="inlineStr">
         <is>
           <t>远程攻击-跟踪-爱心</t>
         </is>
@@ -1864,7 +1879,7 @@
       <c r="O17" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S17" s="0" t="inlineStr">
+      <c r="T17" s="0" t="inlineStr">
         <is>
           <t>远程攻击-抛物线-石头</t>
         </is>
@@ -1888,7 +1903,7 @@
       <c r="R18" s="0" t="n">
         <v>204101</v>
       </c>
-      <c r="S18" s="0" t="inlineStr">
+      <c r="T18" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂弓箭</t>
         </is>
@@ -1912,7 +1927,7 @@
       <c r="R19" s="0" t="n">
         <v>204102</v>
       </c>
-      <c r="S19" s="0" t="inlineStr">
+      <c r="T19" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂火球</t>
         </is>
@@ -1936,7 +1951,7 @@
       <c r="R20" s="0" t="n">
         <v>204103</v>
       </c>
-      <c r="S20" s="0" t="inlineStr">
+      <c r="T20" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂冰球</t>
         </is>
@@ -1968,7 +1983,7 @@
       <c r="O21" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S21" s="0" t="inlineStr">
+      <c r="T21" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂弓箭-子弹道</t>
         </is>
@@ -1984,7 +1999,7 @@
         </is>
       </c>
       <c r="C22" s="0" t="n"/>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedFireBall</t>
         </is>
@@ -2001,7 +2016,7 @@
       <c r="O22" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S22" s="0" t="inlineStr">
+      <c r="T22" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂火球-子弹道</t>
         </is>
@@ -2017,7 +2032,7 @@
         </is>
       </c>
       <c r="C23" s="0" t="n"/>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedIceBall</t>
         </is>
@@ -2034,7 +2049,7 @@
       <c r="O23" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S23" s="0" t="inlineStr">
+      <c r="T23" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂冰球-子弹道</t>
         </is>
@@ -2067,7 +2082,7 @@
       <c r="O24" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S24" s="0" t="inlineStr">
+      <c r="T24" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透</t>
         </is>
@@ -2083,7 +2098,7 @@
         </is>
       </c>
       <c r="C25" s="0" t="n"/>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedFireBall</t>
         </is>
@@ -2101,7 +2116,7 @@
       <c r="O25" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S25" s="0" t="inlineStr">
+      <c r="T25" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透火锥</t>
         </is>
@@ -2117,7 +2132,7 @@
         </is>
       </c>
       <c r="C26" s="0" t="n"/>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedIceBall</t>
         </is>
@@ -2135,7 +2150,7 @@
       <c r="O26" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S26" s="0" t="inlineStr">
+      <c r="T26" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透冰锥</t>
         </is>
@@ -2177,7 +2192,7 @@
           <t>type:2&amp;color:1,1,1</t>
         </is>
       </c>
-      <c r="S27" s="0" t="inlineStr">
+      <c r="T27" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
@@ -2213,7 +2228,10 @@
       <c r="O28" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S28" s="0" t="inlineStr">
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" s="0" t="inlineStr">
         <is>
           <t>爆炸范围攻击-火焰</t>
         </is>
@@ -2250,7 +2268,7 @@
       <c r="O29" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S29" s="0" t="inlineStr">
+      <c r="T29" s="0" t="inlineStr">
         <is>
           <t>重叠攻击-粘液减速</t>
         </is>
@@ -2287,7 +2305,7 @@
       <c r="O30" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S30" s="0" t="inlineStr">
+      <c r="T30" s="0" t="inlineStr">
         <is>
           <t>重叠攻击-中毒</t>
         </is>
@@ -2320,7 +2338,7 @@
       <c r="O31" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="S31" s="0" t="inlineStr">
+      <c r="T31" s="0" t="inlineStr">
         <is>
           <t>加血</t>
         </is>
@@ -2353,7 +2371,7 @@
       <c r="O32" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="S32" s="0" t="inlineStr">
+      <c r="T32" s="0" t="inlineStr">
         <is>
           <t>加护甲</t>
         </is>
@@ -2380,7 +2398,7 @@
       <c r="O33" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="S33" s="0" t="inlineStr">
+      <c r="T33" s="0" t="inlineStr">
         <is>
           <t>引诱敌人到当前线路</t>
         </is>
@@ -2428,7 +2446,7 @@
           <t>0,6,0</t>
         </is>
       </c>
-      <c r="S34" s="0" t="inlineStr">
+      <c r="T34" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-火球</t>
         </is>
@@ -2476,7 +2494,7 @@
           <t>0,6,0</t>
         </is>
       </c>
-      <c r="S35" s="0" t="inlineStr">
+      <c r="T35" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-水球</t>
         </is>
@@ -2519,7 +2537,7 @@
       <c r="O36" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S36" s="0" t="inlineStr">
+      <c r="T36" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-冰球</t>
         </is>
@@ -2551,7 +2569,7 @@
       <c r="O37" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S37" s="0" t="inlineStr">
+      <c r="T37" s="0" t="inlineStr">
         <is>
           <t>下落攻击-雷击</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1156,12 +1156,17 @@
           <t>child_attack_mode_id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="0" t="inlineStr">
         <is>
           <t>damage_add_rate</t>
         </is>
       </c>
-      <c r="T1" s="0" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>hit_max</t>
+        </is>
+      </c>
+      <c r="U1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1258,12 +1263,17 @@
           <t>long</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="T2" s="0" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="U2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1360,12 +1370,17 @@
           <t>子弹道攻击模块id(仅分裂弹AttackModeRangedSplit使用:本行退化为发射器,由它按分裂道路逐条发射该id的子弹道;0/空=不使用)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="0" t="inlineStr">
         <is>
           <t>伤害加成比例(最终伤害=攻击者ATK×该比例;0或空=无加成按1倍)</t>
         </is>
       </c>
-      <c r="T3" s="0" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>单次命中目标数上限(&gt;0时按距落点近者优先截断,0/空=不限制;目前仅AttackModeInstantArea系使用)</t>
+        </is>
+      </c>
+      <c r="U3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1396,7 +1411,7 @@
       <c r="O4" s="0" t="n">
         <v>200002</v>
       </c>
-      <c r="T4" s="0" t="inlineStr">
+      <c r="U4" s="0" t="inlineStr">
         <is>
           <t>普通近战攻击</t>
         </is>
@@ -1431,7 +1446,7 @@
       <c r="O5" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="T5" s="0" t="inlineStr">
+      <c r="U5" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-前方镰刀打击</t>
         </is>
@@ -1464,7 +1479,7 @@
       <c r="O6" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T6" s="0" t="inlineStr">
+      <c r="U6" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-捶地攻击</t>
         </is>
@@ -1494,7 +1509,7 @@
       <c r="O7" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="T7" s="0" t="inlineStr">
+      <c r="U7" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地火锥</t>
         </is>
@@ -1524,7 +1539,7 @@
       <c r="O8" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="T8" s="0" t="inlineStr">
+      <c r="U8" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地冰锥</t>
         </is>
@@ -1559,7 +1574,7 @@
       <c r="O9" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="T9" s="0" t="inlineStr">
+      <c r="U9" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-向前挥砍攻击前方6格</t>
         </is>
@@ -1601,7 +1616,7 @@
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="T10" s="0" t="inlineStr">
+      <c r="U10" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击</t>
         </is>
@@ -1640,7 +1655,7 @@
       <c r="O11" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="T11" s="0" t="inlineStr">
+      <c r="U11" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击</t>
         </is>
@@ -1678,7 +1693,7 @@
       <c r="O12" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="T12" s="0" t="inlineStr">
+      <c r="U12" s="0" t="inlineStr">
         <is>
           <t>远程攻击-水球直线攻击</t>
         </is>
@@ -1717,7 +1732,7 @@
       <c r="O13" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="T13" s="0" t="inlineStr">
+      <c r="U13" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击</t>
         </is>
@@ -1759,7 +1774,7 @@
       <c r="O14" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T14" s="0" t="inlineStr">
+      <c r="U14" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击-范围伤害</t>
         </is>
@@ -1802,7 +1817,7 @@
       <c r="O15" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T15" s="0" t="inlineStr">
+      <c r="U15" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击-范围伤害</t>
         </is>
@@ -1841,7 +1856,7 @@
       <c r="O16" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="T16" s="0" t="inlineStr">
+      <c r="U16" s="0" t="inlineStr">
         <is>
           <t>远程攻击-跟踪-爱心</t>
         </is>
@@ -1879,7 +1894,7 @@
       <c r="O17" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T17" s="0" t="inlineStr">
+      <c r="U17" s="0" t="inlineStr">
         <is>
           <t>远程攻击-抛物线-石头</t>
         </is>
@@ -1903,7 +1918,7 @@
       <c r="R18" s="0" t="n">
         <v>204101</v>
       </c>
-      <c r="T18" s="0" t="inlineStr">
+      <c r="U18" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂弓箭</t>
         </is>
@@ -1927,7 +1942,7 @@
       <c r="R19" s="0" t="n">
         <v>204102</v>
       </c>
-      <c r="T19" s="0" t="inlineStr">
+      <c r="U19" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂火球</t>
         </is>
@@ -1951,7 +1966,7 @@
       <c r="R20" s="0" t="n">
         <v>204103</v>
       </c>
-      <c r="T20" s="0" t="inlineStr">
+      <c r="U20" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂冰球</t>
         </is>
@@ -1983,7 +1998,7 @@
       <c r="O21" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T21" s="0" t="inlineStr">
+      <c r="U21" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂弓箭-子弹道</t>
         </is>
@@ -2016,7 +2031,7 @@
       <c r="O22" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T22" s="0" t="inlineStr">
+      <c r="U22" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂火球-子弹道</t>
         </is>
@@ -2049,7 +2064,7 @@
       <c r="O23" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T23" s="0" t="inlineStr">
+      <c r="U23" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂冰球-子弹道</t>
         </is>
@@ -2082,7 +2097,7 @@
       <c r="O24" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T24" s="0" t="inlineStr">
+      <c r="U24" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透</t>
         </is>
@@ -2116,7 +2131,7 @@
       <c r="O25" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T25" s="0" t="inlineStr">
+      <c r="U25" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透火锥</t>
         </is>
@@ -2150,7 +2165,7 @@
       <c r="O26" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T26" s="0" t="inlineStr">
+      <c r="U26" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透冰锥</t>
         </is>
@@ -2192,7 +2207,7 @@
           <t>type:2&amp;color:1,1,1</t>
         </is>
       </c>
-      <c r="T27" s="0" t="inlineStr">
+      <c r="U27" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
@@ -2228,10 +2243,10 @@
       <c r="O28" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S28" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="T28" s="0" t="inlineStr">
+      <c r="U28" s="0" t="inlineStr">
         <is>
           <t>爆炸范围攻击-火焰</t>
         </is>
@@ -2268,7 +2283,7 @@
       <c r="O29" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T29" s="0" t="inlineStr">
+      <c r="U29" s="0" t="inlineStr">
         <is>
           <t>重叠攻击-粘液减速</t>
         </is>
@@ -2305,7 +2320,7 @@
       <c r="O30" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T30" s="0" t="inlineStr">
+      <c r="U30" s="0" t="inlineStr">
         <is>
           <t>重叠攻击-中毒</t>
         </is>
@@ -2338,7 +2353,7 @@
       <c r="O31" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="T31" s="0" t="inlineStr">
+      <c r="U31" s="0" t="inlineStr">
         <is>
           <t>加血</t>
         </is>
@@ -2371,7 +2386,7 @@
       <c r="O32" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="T32" s="0" t="inlineStr">
+      <c r="U32" s="0" t="inlineStr">
         <is>
           <t>加护甲</t>
         </is>
@@ -2398,7 +2413,7 @@
       <c r="O33" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="T33" s="0" t="inlineStr">
+      <c r="U33" s="0" t="inlineStr">
         <is>
           <t>引诱敌人到当前线路</t>
         </is>
@@ -2446,7 +2461,7 @@
           <t>0,6,0</t>
         </is>
       </c>
-      <c r="T34" s="0" t="inlineStr">
+      <c r="U34" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-火球</t>
         </is>
@@ -2494,7 +2509,7 @@
           <t>0,6,0</t>
         </is>
       </c>
-      <c r="T35" s="0" t="inlineStr">
+      <c r="U35" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-水球</t>
         </is>
@@ -2537,7 +2552,7 @@
       <c r="O36" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T36" s="0" t="inlineStr">
+      <c r="U36" s="0" t="inlineStr">
         <is>
           <t>下落范围攻击-冰球</t>
         </is>
@@ -2569,14 +2584,147 @@
       <c r="O37" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T37" s="0" t="inlineStr">
+      <c r="U37" s="0" t="inlineStr">
         <is>
           <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="1"/>
-    <row r="39" ht="15" customHeight="1" s="1"/>
+    <row r="38" ht="15" customHeight="1" s="1">
+      <c r="A38" t="n">
+        <v>300031</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>11</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="1">
+      <c r="A39" t="n">
+        <v>300032</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>11</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>300033</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>11</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>300034</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>11</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>300035</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>11</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
     <row r="71" ht="12" customHeight="1" s="1"/>
     <row r="72" ht="12" customHeight="1" s="1"/>
     <row r="73" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -2255,329 +2255,490 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>400001</v>
+        <v>300061</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlap</t>
-        </is>
+          <t>AttackModeRangedArcBounce</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Axe_1</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="I29" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J29" s="0" t="n"/>
-      <c r="K29" s="0" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L29" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="O29" s="0" t="n">
-        <v>420008</v>
+        <v>420001</v>
+      </c>
+      <c r="Q29" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="R29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U29" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>400002</v>
+        <v>300081</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlap</t>
-        </is>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="I30" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J30" s="0" t="n"/>
-      <c r="K30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="O30" s="0" t="n">
-        <v>420008</v>
+        <v>420001</v>
+      </c>
+      <c r="Q30" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="R30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U30" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-中毒</t>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>500001</v>
+        <v>300082</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
-        </is>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="I31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="0" t="n">
-        <v>500001</v>
+        <v>0</v>
+      </c>
+      <c r="L31" s="0" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M31" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="N31" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="O31" s="0" t="n">
-        <v>470001</v>
+        <v>420001</v>
+      </c>
+      <c r="Q31" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="R31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U31" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>500002</v>
+        <v>300083</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
-        </is>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H32" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="I32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="0" t="n">
-        <v>500002</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="N32" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>470001</v>
+        <v>420001</v>
+      </c>
+      <c r="Q32" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="R32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U32" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>600001</v>
+        <v>300084</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
-      </c>
-      <c r="I33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="0" t="n">
-        <v>600001</v>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="0" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M33" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="N33" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>6</v>
+        <v>420001</v>
+      </c>
+      <c r="Q33" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="R33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U33" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>700001</v>
+        <v>300085</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Meteorite_1</t>
-        </is>
-      </c>
-      <c r="E34" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>0.6</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="I34" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J34" s="0" t="n">
-        <v>800001</v>
+        <v>0</v>
       </c>
       <c r="L34" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="M34" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="N34" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="O34" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="P34" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
+        <v>420001</v>
+      </c>
+      <c r="Q34" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="R34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U34" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球</t>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>700002</v>
+        <v>300091</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Water_1</t>
-        </is>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t>1000600001:0.5</t>
-        </is>
+          <t>AttackModeShockwaveRing</t>
+        </is>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="I35" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J35" s="0" t="n">
-        <v>800001</v>
+        <v>0</v>
+      </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>0.5,0.5</t>
+        </is>
       </c>
       <c r="L35" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M35" s="0" t="n">
+        <v>420001</v>
       </c>
       <c r="N35" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="O35" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="P35" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U35" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球</t>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
-      <c r="A36" s="0" t="n">
-        <v>700003</v>
-      </c>
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
-        </is>
-      </c>
-      <c r="E36" s="0" t="inlineStr">
-        <is>
-          <t>1000700001:0.5</t>
-        </is>
-      </c>
-      <c r="H36" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="I36" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J36" s="0" t="n">
-        <v>800001</v>
-      </c>
-      <c r="L36" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N36" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="O36" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="U36" s="0" t="inlineStr">
-        <is>
-          <t>下落范围攻击-冰球</t>
+      <c r="A36" t="n">
+        <v>300101</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>420003</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>800001</v>
+        <v>400001</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
-        </is>
+          <t>AttackModeOverlap</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>0.5</v>
       </c>
       <c r="H37" s="0" t="n">
         <v>11</v>
       </c>
       <c r="I37" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J37" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="J37" s="0" t="n"/>
+      <c r="K37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="N37" s="0" t="n">
         <v>100001</v>
@@ -2587,199 +2748,613 @@
       </c>
       <c r="U37" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>300031</v>
+        <v>400002</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
-        </is>
+          <t>AttackModeOverlap</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>0.5</v>
       </c>
       <c r="H38" s="0" t="n">
         <v>11</v>
       </c>
       <c r="I38" s="0" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
+      </c>
+      <c r="J38" s="0" t="n"/>
+      <c r="K38" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="L38" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="O38" s="0" t="n"/>
-      <c r="T38" s="0" t="n">
-        <v>1</v>
+      <c r="N38" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O38" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="U38" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>300032</v>
+        <v>500001</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
-        </is>
+          <t>AttackModeRegainHP</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H39" s="0" t="n">
         <v>11</v>
       </c>
       <c r="I39" s="0" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="O39" s="0" t="n"/>
-      <c r="T39" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="N39" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O39" s="0" t="n">
+        <v>470001</v>
       </c>
       <c r="U39" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300033</v>
+        <v>500002</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
-        </is>
+          <t>AttackModeRegainDR</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H40" s="0" t="n">
         <v>11</v>
       </c>
       <c r="I40" s="0" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="O40" s="0" t="n"/>
-      <c r="T40" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>500002</v>
+      </c>
+      <c r="N40" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O40" s="0" t="n">
+        <v>470001</v>
       </c>
       <c r="U40" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300034</v>
+        <v>600001</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
-        </is>
-      </c>
-      <c r="H41" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="I41" s="0" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="O41" s="0" t="n"/>
-      <c r="T41" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>600001</v>
+      </c>
+      <c r="N41" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O41" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="U41" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300035</v>
+        <v>700001</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Meteorite_1</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H42" s="0" t="n">
         <v>11</v>
       </c>
       <c r="I42" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="J42" s="0" t="n">
+        <v>800001</v>
       </c>
       <c r="L42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="O42" s="0" t="n"/>
-      <c r="T42" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="N42" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O42" s="0" t="n">
+        <v>420008</v>
+      </c>
+      <c r="P42" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
       </c>
       <c r="U42" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落范围攻击-火球</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
+        <v>700002</v>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Water_1</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>1000600001:0.5</t>
+        </is>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J43" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="L43" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N43" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O43" s="0" t="n">
+        <v>420008</v>
+      </c>
+      <c r="P43" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="U43" s="0" t="inlineStr">
+        <is>
+          <t>下落范围攻击-水球</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="n">
+        <v>700003</v>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="L44" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N44" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O44" s="0" t="n">
+        <v>420008</v>
+      </c>
+      <c r="U44" s="0" t="inlineStr">
+        <is>
+          <t>下落范围攻击-冰球</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeFalluponChain</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="N45" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O45" s="0" t="n">
+        <v>420008</v>
+      </c>
+      <c r="U45" s="0" t="inlineStr">
+        <is>
+          <t>下落攻击-雷击</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="n">
+        <v>300031</v>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I46" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="O46" s="0" t="n"/>
+      <c r="T46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="n">
+        <v>300032</v>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I47" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="O47" s="0" t="n"/>
+      <c r="T47" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="n">
+        <v>300033</v>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I48" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="O48" s="0" t="n"/>
+      <c r="T48" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="n">
+        <v>300034</v>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="O49" s="0" t="n"/>
+      <c r="T49" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="n">
+        <v>300035</v>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="O50" s="0" t="n"/>
+      <c r="T50" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="n">
         <v>300041</v>
       </c>
-      <c r="B43" s="0" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>AttackModeRangedPiercingRoad</t>
         </is>
       </c>
-      <c r="D43" s="0" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_Minecart_1</t>
         </is>
       </c>
-      <c r="G43" s="0" t="n">
+      <c r="G51" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="L43" s="0" t="n">
+      <c r="L51" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="N43" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="O43" s="0" t="n">
+      <c r="N51" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O51" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q43" s="0" t="inlineStr">
+      <c r="Q51" s="0" t="inlineStr">
         <is>
           <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
         </is>
       </c>
-      <c r="U43" s="0" t="inlineStr">
+      <c r="U51" s="0" t="inlineStr">
         <is>
           <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="n">
+        <v>300051</v>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr"/>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr"/>
+      <c r="F52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="0" t="inlineStr"/>
+      <c r="J52" s="0" t="inlineStr"/>
+      <c r="K52" s="0" t="inlineStr"/>
+      <c r="L52" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="M52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="O52" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="P52" s="0" t="inlineStr"/>
+      <c r="Q52" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="R52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="0" t="inlineStr">
+        <is>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="Q53" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="R53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力50%伤害,每只书对同一敌人0.5秒冷却)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -3376,7 +3376,7 @@
       </c>
       <c r="V53" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力50%伤害,每只书对同一敌人0.5秒冷却)</t>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1842,68 +1842,77 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>202001</v>
+        <v>201003</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedTracking</t>
-        </is>
-      </c>
-      <c r="C16" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedLove</t>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H16" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I16" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="J16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="0" t="n"/>
+      <c r="K16" s="0" t="n">
+        <v>100001</v>
+      </c>
       <c r="M16" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <v>9</v>
       </c>
       <c r="O16" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P16" s="0" t="n">
-        <v>6</v>
+        <v>420008</v>
       </c>
       <c r="V16" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-跟踪-爱心</t>
+          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="1">
       <c r="A17" s="0" t="n">
-        <v>203001</v>
+        <v>201004</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArc</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
-        </is>
-      </c>
-      <c r="G17" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>1000100001:0.5</t>
+        </is>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I17" s="0" t="n"/>
-      <c r="J17" s="0" t="n"/>
-      <c r="K17" s="0" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <v>200001</v>
+      </c>
       <c r="M17" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9</v>
       </c>
       <c r="O17" s="0" t="n">
         <v>100001</v>
@@ -1913,61 +1922,90 @@
       </c>
       <c r="V17" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-石头</t>
+          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="1">
       <c r="A18" s="0" t="n">
-        <v>204001</v>
+        <v>202001</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplit</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="n"/>
-      <c r="H18" s="0" t="n"/>
+          <t>AttackModeRangedTracking</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedLove</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="K18" s="0" t="n"/>
-      <c r="M18" s="0" t="n"/>
-      <c r="O18" s="0" t="n"/>
-      <c r="P18" s="0" t="n"/>
-      <c r="S18" s="0" t="n">
-        <v>204101</v>
+      <c r="M18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P18" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="V18" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭</t>
+          <t>远程攻击-跟踪-爱心</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>204002</v>
+        <v>203001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplit</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="n"/>
-      <c r="H19" s="0" t="n"/>
+          <t>AttackModeRangedArc</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I19" s="0" t="n"/>
+      <c r="J19" s="0" t="n"/>
       <c r="K19" s="0" t="n"/>
-      <c r="M19" s="0" t="n"/>
-      <c r="O19" s="0" t="n"/>
-      <c r="P19" s="0" t="n"/>
-      <c r="S19" s="0" t="n">
-        <v>204102</v>
+      <c r="M19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P19" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="V19" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂火球</t>
+          <t>远程攻击-抛物线-石头</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>204003</v>
+        <v>204001</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
@@ -1981,92 +2019,74 @@
       <c r="O20" s="0" t="n"/>
       <c r="P20" s="0" t="n"/>
       <c r="S20" s="0" t="n">
-        <v>204103</v>
+        <v>204101</v>
       </c>
       <c r="V20" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂冰球</t>
+          <t>远程攻击-分裂弓箭</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>204101</v>
+        <v>204002</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplitChild</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
-        </is>
-      </c>
-      <c r="H21" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P21" s="0" t="n">
-        <v>420008</v>
+          <t>AttackModeRangedSplit</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="n"/>
+      <c r="H21" s="0" t="n"/>
+      <c r="K21" s="0" t="n"/>
+      <c r="M21" s="0" t="n"/>
+      <c r="O21" s="0" t="n"/>
+      <c r="P21" s="0" t="n"/>
+      <c r="S21" s="0" t="n">
+        <v>204102</v>
       </c>
       <c r="V21" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭-子弹道</t>
+          <t>远程攻击-分裂火球</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>204102</v>
+        <v>204003</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplitChild</t>
+          <t>AttackModeRangedSplit</t>
         </is>
       </c>
       <c r="C22" s="0" t="n"/>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="H22" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P22" s="0" t="n">
-        <v>420008</v>
+      <c r="H22" s="0" t="n"/>
+      <c r="K22" s="0" t="n"/>
+      <c r="M22" s="0" t="n"/>
+      <c r="O22" s="0" t="n"/>
+      <c r="P22" s="0" t="n"/>
+      <c r="S22" s="0" t="n">
+        <v>204103</v>
       </c>
       <c r="V22" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂火球-子弹道</t>
+          <t>远程攻击-分裂冰球</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>204103</v>
+        <v>204101</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
           <t>AttackModeRangedSplitChild</t>
         </is>
       </c>
-      <c r="C23" s="0" t="n"/>
-      <c r="D23" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
         </is>
       </c>
       <c r="H23" s="0" t="n">
@@ -2083,28 +2103,28 @@
       </c>
       <c r="V23" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂冰球-子弹道</t>
+          <t>远程攻击-分裂弓箭-子弹道</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>205001</v>
+        <v>204102</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
+          <t>AttackModeRangedSplitChild</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="n"/>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="H24" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K24" s="0" t="n"/>
       <c r="M24" s="0" t="n">
         <v>1</v>
       </c>
@@ -2116,29 +2136,28 @@
       </c>
       <c r="V24" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透</t>
+          <t>远程攻击-分裂火球-子弹道</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>205002</v>
+        <v>204103</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
+          <t>AttackModeRangedSplitChild</t>
         </is>
       </c>
       <c r="C25" s="0" t="n"/>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="H25" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K25" s="0" t="n"/>
       <c r="M25" s="0" t="n">
         <v>1</v>
       </c>
@@ -2150,23 +2169,22 @@
       </c>
       <c r="V25" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透火锥</t>
+          <t>远程攻击-分裂冰球-子弹道</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>205003</v>
+        <v>205001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
           <t>AttackModeRangedPiercing</t>
         </is>
       </c>
-      <c r="C26" s="0" t="n"/>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
         </is>
       </c>
       <c r="H26" s="0" t="n">
@@ -2184,23 +2202,23 @@
       </c>
       <c r="V26" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透冰锥</t>
+          <t>远程攻击-穿透</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>210001</v>
+        <v>205002</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
+          <t>AttackModeRangedPiercing</t>
         </is>
       </c>
       <c r="C27" s="0" t="n"/>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="H27" s="0" t="n">
@@ -2210,49 +2228,39 @@
       <c r="M27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="2" t="n">
-        <v>310001</v>
-      </c>
       <c r="O27" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P27" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R27" s="0" t="inlineStr">
-        <is>
-          <t>type:2&amp;color:1,1,1</t>
-        </is>
+        <v>420008</v>
       </c>
       <c r="V27" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击-VFX轨迹(白)</t>
+          <t>远程攻击-穿透火锥</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>300001</v>
+        <v>205003</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
+          <t>AttackModeRangedPiercing</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="n"/>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="H28" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I28" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J28" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K28" s="0" t="n">
-        <v>300001</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="K28" s="0" t="n"/>
       <c r="M28" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="0" t="n">
         <v>100001</v>
@@ -2260,155 +2268,123 @@
       <c r="P28" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="T28" s="0" t="n">
-        <v>50</v>
-      </c>
       <c r="V28" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰</t>
+          <t>远程攻击-穿透冰锥</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>300061</v>
+        <v>210001</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcBounce</t>
-        </is>
-      </c>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="n"/>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Axe_1</t>
-        </is>
-      </c>
-      <c r="G29" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeVisual_RangedNormal</t>
+        </is>
       </c>
       <c r="H29" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="K29" s="0" t="n"/>
       <c r="M29" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="N29" s="0" t="n">
-        <v>400003</v>
+        <v>1</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O29" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P29" s="0" t="n">
-        <v>420001</v>
+        <v>420011</v>
       </c>
       <c r="R29" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="0" t="n">
-        <v>0</v>
+          <t>type:2&amp;color:1,1,1</t>
+        </is>
       </c>
       <c r="V29" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
+          <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>300081</v>
+        <v>300001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Pingpang_1</t>
-        </is>
-      </c>
-      <c r="G30" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeExplosion</t>
+        </is>
       </c>
       <c r="H30" s="0" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="I30" s="0" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>300001</v>
       </c>
       <c r="M30" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" s="0" t="n">
-        <v>400003</v>
+        <v>0</v>
       </c>
       <c r="O30" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P30" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R30" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S30" s="0" t="n">
-        <v>0</v>
+        <v>420008</v>
       </c>
       <c r="T30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="0" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V30" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
+          <t>爆炸范围攻击-火焰</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>300082</v>
+        <v>300061</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
+          <t>AttackModeRangedArcBounce</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Pingpang_1</t>
+          <t>AttackModeVisual_Axe_1</t>
         </is>
       </c>
       <c r="G31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I31" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M31" s="0" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="N31" s="0" t="n">
         <v>400003</v>
@@ -2435,13 +2411,13 @@
       </c>
       <c r="V31" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>300083</v>
+        <v>300081</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
@@ -2463,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" s="0" t="n">
         <v>400003</v>
@@ -2490,13 +2466,13 @@
       </c>
       <c r="V32" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>300084</v>
+        <v>300082</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
@@ -2518,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="0" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="N33" s="0" t="n">
         <v>400003</v>
@@ -2545,13 +2521,13 @@
       </c>
       <c r="V33" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>300085</v>
+        <v>300083</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
@@ -2573,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N34" s="0" t="n">
         <v>400003</v>
@@ -2600,44 +2576,49 @@
       </c>
       <c r="V34" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>300091</v>
+        <v>300084</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShockwaveRing</t>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
         </is>
       </c>
       <c r="G35" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I35" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="0" t="inlineStr">
-        <is>
-          <t>0.5,0.5</t>
-        </is>
-      </c>
       <c r="M35" s="0" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N35" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O35" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P35" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="O35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="0" t="n">
-        <v>0</v>
+      <c r="R35" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
       </c>
       <c r="S35" s="0" t="n">
         <v>0</v>
@@ -2650,351 +2631,360 @@
       </c>
       <c r="V35" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>300101</v>
+        <v>300085</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcGround</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="inlineStr"/>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_FireBottle_1</t>
-        </is>
-      </c>
-      <c r="F36" s="0" t="inlineStr"/>
-      <c r="G36" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H36" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I36" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J36" s="0" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="K36" s="0" t="inlineStr"/>
-      <c r="L36" s="0" t="inlineStr"/>
-      <c r="M36" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>AttackModeVisual_Pingpang_1</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="N36" s="0" t="n">
         <v>400003</v>
       </c>
-      <c r="O36" s="0" t="inlineStr"/>
-      <c r="P36" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q36" s="0" t="inlineStr"/>
-      <c r="R36" s="0" t="inlineStr"/>
-      <c r="S36" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U36" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="O36" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P36" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R36" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="V36" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>400001</v>
+        <v>300091</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlap</t>
-        </is>
+          <t>AttackModeShockwaveRing</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H37" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I37" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J37" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K37" s="0" t="n"/>
-      <c r="L37" s="0" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t>0.5,0.5</t>
+        </is>
       </c>
       <c r="M37" s="0" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="N37" s="0" t="n">
+        <v>420001</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P37" s="0" t="n">
-        <v>420008</v>
+        <v>0</v>
+      </c>
+      <c r="S37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="V37" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>400002</v>
+        <v>300101</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlap</t>
-        </is>
-      </c>
-      <c r="H38" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I38" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J38" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K38" s="0" t="n"/>
-      <c r="L38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P38" s="0" t="n">
-        <v>420008</v>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr"/>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="inlineStr"/>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="inlineStr"/>
+      <c r="L38" s="0" t="inlineStr"/>
+      <c r="M38" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N38" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O38" s="0" t="inlineStr"/>
+      <c r="P38" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" s="0" t="inlineStr"/>
+      <c r="R38" s="0" t="inlineStr"/>
+      <c r="S38" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U38" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="V38" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-中毒</t>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>500001</v>
+        <v>400001</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeOverlap</t>
         </is>
       </c>
       <c r="H39" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I39" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="0" t="n">
-        <v>500001</v>
+        <v>0.5</v>
+      </c>
+      <c r="K39" s="0" t="n"/>
+      <c r="L39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O39" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P39" s="0" t="n">
-        <v>470001</v>
+        <v>420008</v>
       </c>
       <c r="V39" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>500002</v>
+        <v>400002</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
+          <t>AttackModeOverlap</t>
         </is>
       </c>
       <c r="H40" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I40" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J40" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" s="0" t="n">
-        <v>500002</v>
+        <v>0.5</v>
+      </c>
+      <c r="K40" s="0" t="n"/>
+      <c r="L40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O40" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P40" s="0" t="n">
-        <v>470001</v>
+        <v>420008</v>
       </c>
       <c r="V40" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>600001</v>
+        <v>500001</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
+          <t>AttackModeRegainHP</t>
+        </is>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J41" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" s="0" t="n">
-        <v>600001</v>
+        <v>500001</v>
       </c>
       <c r="O41" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P41" s="0" t="n">
-        <v>6</v>
+        <v>470001</v>
       </c>
       <c r="V41" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>700001</v>
+        <v>500002</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Meteorite_1</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
+          <t>AttackModeRegainDR</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="I42" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K42" s="0" t="n">
-        <v>800001</v>
-      </c>
-      <c r="M42" s="0" t="n">
-        <v>3</v>
+        <v>500002</v>
       </c>
       <c r="O42" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P42" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q42" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
+        <v>470001</v>
       </c>
       <c r="V42" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球</t>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>700002</v>
+        <v>600001</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Water_1</t>
-        </is>
-      </c>
-      <c r="F43" s="0" t="inlineStr">
-        <is>
-          <t>1000600001:0.5</t>
-        </is>
-      </c>
-      <c r="I43" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J43" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K43" s="0" t="n">
-        <v>800001</v>
-      </c>
-      <c r="M43" s="0" t="n">
-        <v>3</v>
+        <v>600001</v>
       </c>
       <c r="O43" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P43" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q43" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="V43" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>700003</v>
+        <v>700001</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
@@ -3003,12 +2993,12 @@
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackMode_Fallupon_Meteorite_1</t>
         </is>
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I44" s="0" t="n">
@@ -3029,19 +3019,34 @@
       <c r="P44" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q44" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
       <c r="V44" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落范围攻击-火球</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>800001</v>
+        <v>700002</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Water_1</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I45" s="0" t="n">
@@ -3050,10 +3055,11 @@
       <c r="J45" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K45" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K45" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="M45" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="O45" s="0" t="n">
         <v>100001</v>
@@ -3061,77 +3067,95 @@
       <c r="P45" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q45" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
       <c r="V45" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>下落范围攻击-水球</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>300031</v>
+        <v>700003</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
+        </is>
+      </c>
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I46" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J46" s="0" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
+      </c>
+      <c r="K46" s="0" t="n">
+        <v>800001</v>
       </c>
       <c r="M46" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P46" s="0" t="n"/>
-      <c r="U46" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="O46" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P46" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="V46" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>300032</v>
+        <v>800001</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I47" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M47" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P47" s="0" t="n"/>
-      <c r="U47" s="0" t="n">
-        <v>2</v>
+        <v>1.5</v>
+      </c>
+      <c r="K47" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O47" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P47" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="V47" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>300033</v>
+        <v>300031</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
@@ -3142,7 +3166,7 @@
         <v>11</v>
       </c>
       <c r="J48" s="0" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="M48" s="0" t="n">
         <v>0</v>
@@ -3152,17 +3176,17 @@
       </c>
       <c r="P48" s="0" t="n"/>
       <c r="U48" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V48" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300034</v>
+        <v>300032</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
@@ -3173,7 +3197,7 @@
         <v>11</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="M49" s="0" t="n">
         <v>0</v>
@@ -3183,17 +3207,17 @@
       </c>
       <c r="P49" s="0" t="n"/>
       <c r="U49" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V49" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300035</v>
+        <v>300033</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
@@ -3204,7 +3228,7 @@
         <v>11</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M50" s="0" t="n">
         <v>0</v>
@@ -3214,167 +3238,229 @@
       </c>
       <c r="P50" s="0" t="n"/>
       <c r="U50" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V50" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300041</v>
+        <v>300034</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D51" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E51" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H51" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>0.8</v>
       </c>
       <c r="M51" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N51" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O51" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P51" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R51" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P51" s="0" t="n"/>
+      <c r="U51" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="V51" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300051</v>
+        <v>300035</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C52" s="0" t="inlineStr"/>
-      <c r="D52" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F52" s="0" t="inlineStr"/>
-      <c r="G52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
       </c>
       <c r="I52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="0" t="inlineStr"/>
-      <c r="K52" s="0" t="inlineStr"/>
-      <c r="L52" s="0" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="M52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="P52" s="0" t="n"/>
+      <c r="U52" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="N52" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O52" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P52" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="Q52" s="0" t="inlineStr"/>
-      <c r="R52" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="V52" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300071</v>
+        <v>300041</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
+          <t>AttackModeRangedPiercingRoad</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
-      <c r="G53" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H53" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I53" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="M53" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N53" s="0" t="n">
-        <v>0</v>
+        <v>310001</v>
+      </c>
+      <c r="O53" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P53" s="0" t="n">
         <v>420001</v>
       </c>
       <c r="R53" s="0" t="inlineStr">
         <is>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
+      </c>
+      <c r="V53" s="0" t="inlineStr">
+        <is>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="n">
+        <v>300051</v>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr"/>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr"/>
+      <c r="G54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="0" t="inlineStr"/>
+      <c r="K54" s="0" t="inlineStr"/>
+      <c r="L54" s="0" t="inlineStr"/>
+      <c r="M54" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N54" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O54" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P54" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="Q54" s="0" t="inlineStr"/>
+      <c r="R54" s="0" t="inlineStr">
+        <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
         </is>
       </c>
-      <c r="S53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="0" t="inlineStr">
+      <c r="S54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="0" t="inlineStr">
+        <is>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R55" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="0" t="inlineStr">
         <is>
           <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V55"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1564,12 +1564,15 @@
     </row>
     <row r="9" ht="14.25" customHeight="1" s="1">
       <c r="A9" s="0" t="n">
-        <v>102001</v>
+        <v>101005</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
           <t>AttackModeMeleeArea</t>
         </is>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H9" s="0" t="n">
         <v>3</v>
@@ -1579,11 +1582,19 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>3,1,0.25</t>
-        </is>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>400002</v>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>400001</t>
+        </is>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O9" s="0" t="n">
         <v>100001</v>
@@ -1591,57 +1602,59 @@
       <c r="P9" s="0" t="n">
         <v>200007</v>
       </c>
+      <c r="S9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="V9" s="0" t="inlineStr">
         <is>
-          <t>BOSS技能-向前挥砍攻击前方6格</t>
+          <t>普通近战范围-前方挥砍(攻击前方2单位)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" s="1">
       <c r="A10" s="0" t="n">
-        <v>200001</v>
+        <v>102001</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="n"/>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeMeleeArea</t>
         </is>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K10" s="0" t="n"/>
-      <c r="M10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>310001</v>
+        <v>3</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>3,1,0.25</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>400002</v>
       </c>
       <c r="O10" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P10" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R10" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
+        <v>200007</v>
       </c>
       <c r="V10" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击</t>
+          <t>BOSS技能-向前挥砍攻击前方6格</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>200002</v>
+        <v>200001</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
@@ -1651,12 +1664,7 @@
       <c r="C11" s="0" t="n"/>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H11" s="0" t="n">
@@ -1666,35 +1674,44 @@
       <c r="M11" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N11" s="2" t="n">
+        <v>310001</v>
+      </c>
       <c r="O11" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P11" s="0" t="n">
-        <v>420003</v>
+        <v>420011</v>
+      </c>
+      <c r="R11" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="V11" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击</t>
+          <t>远程攻击-攻击</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>200003</v>
+        <v>200002</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedWaterBall</t>
+      <c r="C12" s="0" t="n"/>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H12" s="0" t="n">
@@ -1712,28 +1729,27 @@
       </c>
       <c r="V12" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-水球直线攻击</t>
+          <t>远程攻击-火球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="1">
       <c r="A13" s="0" t="n">
-        <v>200004</v>
+        <v>200003</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="C13" s="0" t="n"/>
-      <c r="D13" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedWaterBall</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="H13" s="0" t="n">
@@ -1751,37 +1767,34 @@
       </c>
       <c r="V13" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击</t>
+          <t>远程攻击-水球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>201001</v>
+        <v>200004</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArea</t>
+          <t>AttackModeRanged</t>
         </is>
       </c>
       <c r="C14" s="0" t="n"/>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="H14" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I14" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <v>100001</v>
-      </c>
+      <c r="K14" s="0" t="n"/>
       <c r="M14" s="0" t="n">
         <v>1</v>
       </c>
@@ -1789,17 +1802,17 @@
         <v>100001</v>
       </c>
       <c r="P14" s="0" t="n">
-        <v>420008</v>
+        <v>420003</v>
       </c>
       <c r="V14" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击-范围伤害</t>
+          <t>远程攻击-冰球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>201002</v>
+        <v>201001</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
@@ -1809,10 +1822,9 @@
       <c r="C15" s="0" t="n"/>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
-        </is>
-      </c>
-      <c r="F15" s="0" t="n"/>
+          <t>AttackModeVisual_RangedFireBall</t>
+        </is>
+      </c>
       <c r="H15" s="0" t="n">
         <v>0.1</v>
       </c>
@@ -1823,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M15" s="0" t="n">
         <v>1</v>
@@ -1836,40 +1848,40 @@
       </c>
       <c r="V15" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击-范围伤害</t>
+          <t>远程攻击-火球直线攻击-范围伤害</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>201003</v>
+        <v>201002</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
+          <t>AttackModeRangedArea</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="n"/>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F16" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
-      </c>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="n"/>
       <c r="H16" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="I16" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" s="0" t="n">
-        <v>100001</v>
+        <v>200001</v>
       </c>
       <c r="M16" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N16" s="0" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O16" s="0" t="n">
         <v>100001</v>
@@ -1879,13 +1891,13 @@
       </c>
       <c r="V16" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-冰球直线攻击-范围伤害</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="1">
       <c r="A17" s="0" t="n">
-        <v>201004</v>
+        <v>201003</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
@@ -1894,24 +1906,24 @@
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>1000100001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H17" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M17" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="0" t="n">
         <v>9</v>
       </c>
       <c r="O17" s="0" t="n">
@@ -1922,71 +1934,76 @@
       </c>
       <c r="V17" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="1">
       <c r="A18" s="0" t="n">
-        <v>202001</v>
+        <v>201004</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedTracking</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedLove</t>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>1000100001:0.5</t>
         </is>
       </c>
       <c r="H18" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I18" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="J18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="0" t="n"/>
+      <c r="K18" s="0" t="n">
+        <v>200001</v>
+      </c>
       <c r="M18" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="N18" s="0" t="n">
+        <v>9</v>
       </c>
       <c r="O18" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P18" s="0" t="n">
-        <v>6</v>
+        <v>420008</v>
       </c>
       <c r="V18" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-跟踪-爱心</t>
+          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>203001</v>
+        <v>202001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArc</t>
+          <t>AttackModeRangedTracking</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_RangedNormal</t>
-        </is>
-      </c>
-      <c r="G19" s="0" t="n">
-        <v>11</v>
+          <t>AttackMode_RangedLove</t>
+        </is>
       </c>
       <c r="H19" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I19" s="0" t="n"/>
-      <c r="J19" s="0" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="K19" s="0" t="n"/>
       <c r="M19" s="0" t="n">
         <v>1</v>
@@ -1995,41 +2012,55 @@
         <v>100001</v>
       </c>
       <c r="P19" s="0" t="n">
-        <v>420008</v>
+        <v>6</v>
       </c>
       <c r="V19" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-石头</t>
+          <t>远程攻击-跟踪-爱心</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>204001</v>
+        <v>203001</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplit</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="n"/>
-      <c r="H20" s="0" t="n"/>
+          <t>AttackModeRangedArc</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I20" s="0" t="n"/>
+      <c r="J20" s="0" t="n"/>
       <c r="K20" s="0" t="n"/>
-      <c r="M20" s="0" t="n"/>
-      <c r="O20" s="0" t="n"/>
-      <c r="P20" s="0" t="n"/>
-      <c r="S20" s="0" t="n">
-        <v>204101</v>
+      <c r="M20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P20" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="V20" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭</t>
+          <t>远程攻击-抛物线-石头</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>204002</v>
+        <v>204001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
@@ -2043,17 +2074,17 @@
       <c r="O21" s="0" t="n"/>
       <c r="P21" s="0" t="n"/>
       <c r="S21" s="0" t="n">
-        <v>204102</v>
+        <v>204101</v>
       </c>
       <c r="V21" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂火球</t>
+          <t>远程攻击-分裂弓箭</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>204003</v>
+        <v>204002</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
@@ -2067,59 +2098,50 @@
       <c r="O22" s="0" t="n"/>
       <c r="P22" s="0" t="n"/>
       <c r="S22" s="0" t="n">
-        <v>204103</v>
+        <v>204102</v>
       </c>
       <c r="V22" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂冰球</t>
+          <t>远程攻击-分裂火球</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>204101</v>
+        <v>204003</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplitChild</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
-        </is>
-      </c>
-      <c r="H23" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P23" s="0" t="n">
-        <v>420008</v>
+          <t>AttackModeRangedSplit</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="n"/>
+      <c r="H23" s="0" t="n"/>
+      <c r="K23" s="0" t="n"/>
+      <c r="M23" s="0" t="n"/>
+      <c r="O23" s="0" t="n"/>
+      <c r="P23" s="0" t="n"/>
+      <c r="S23" s="0" t="n">
+        <v>204103</v>
       </c>
       <c r="V23" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭-子弹道</t>
+          <t>远程攻击-分裂冰球</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>204102</v>
+        <v>204101</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
           <t>AttackModeRangedSplitChild</t>
         </is>
       </c>
-      <c r="C24" s="0" t="n"/>
-      <c r="D24" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
         </is>
       </c>
       <c r="H24" s="0" t="n">
@@ -2136,13 +2158,13 @@
       </c>
       <c r="V24" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂火球-子弹道</t>
+          <t>远程攻击-分裂弓箭-子弹道</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>204103</v>
+        <v>204102</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
@@ -2152,7 +2174,7 @@
       <c r="C25" s="0" t="n"/>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="H25" s="0" t="n">
@@ -2169,28 +2191,28 @@
       </c>
       <c r="V25" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂冰球-子弹道</t>
+          <t>远程攻击-分裂火球-子弹道</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>205001</v>
+        <v>204103</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
-        </is>
-      </c>
-      <c r="C26" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
+          <t>AttackModeRangedSplitChild</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n"/>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="H26" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K26" s="0" t="n"/>
       <c r="M26" s="0" t="n">
         <v>1</v>
       </c>
@@ -2202,23 +2224,22 @@
       </c>
       <c r="V26" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透</t>
+          <t>远程攻击-分裂冰球-子弹道</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>205002</v>
+        <v>205001</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
           <t>AttackModeRangedPiercing</t>
         </is>
       </c>
-      <c r="C27" s="0" t="n"/>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
         </is>
       </c>
       <c r="H27" s="0" t="n">
@@ -2236,13 +2257,13 @@
       </c>
       <c r="V27" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透火锥</t>
+          <t>远程攻击-穿透</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>205003</v>
+        <v>205002</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
@@ -2252,7 +2273,7 @@
       <c r="C28" s="0" t="n"/>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="H28" s="0" t="n">
@@ -2270,23 +2291,23 @@
       </c>
       <c r="V28" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透冰锥</t>
+          <t>远程攻击-穿透火锥</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>210001</v>
+        <v>205003</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
+          <t>AttackModeRangedPiercing</t>
         </is>
       </c>
       <c r="C29" s="0" t="n"/>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="H29" s="0" t="n">
@@ -2296,150 +2317,129 @@
       <c r="M29" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="2" t="n">
-        <v>310001</v>
-      </c>
       <c r="O29" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P29" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R29" s="0" t="inlineStr">
-        <is>
-          <t>type:2&amp;color:1,1,1</t>
-        </is>
+        <v>420008</v>
       </c>
       <c r="V29" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击-VFX轨迹(白)</t>
+          <t>远程攻击-穿透冰锥</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>300001</v>
+        <v>210001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="n"/>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H30" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I30" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J30" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K30" s="0" t="n">
-        <v>300001</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="K30" s="0" t="n"/>
       <c r="M30" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O30" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P30" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="T30" s="0" t="n">
-        <v>50</v>
+        <v>420011</v>
+      </c>
+      <c r="R30" s="0" t="inlineStr">
+        <is>
+          <t>type:2&amp;color:1,1,1</t>
+        </is>
       </c>
       <c r="V30" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰</t>
+          <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>300061</v>
+        <v>300001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcBounce</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Axe_1</t>
-        </is>
-      </c>
-      <c r="G31" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeExplosion</t>
+        </is>
       </c>
       <c r="H31" s="0" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>300001</v>
       </c>
       <c r="M31" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="N31" s="0" t="n">
-        <v>400003</v>
+        <v>0</v>
       </c>
       <c r="O31" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P31" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R31" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S31" s="0" t="n">
-        <v>0</v>
+        <v>420008</v>
       </c>
       <c r="T31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="0" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V31" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
+          <t>爆炸范围攻击-火焰</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>300081</v>
+        <v>300061</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
+          <t>AttackModeRangedArcBounce</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Pingpang_1</t>
+          <t>AttackModeVisual_Axe_1</t>
         </is>
       </c>
       <c r="G32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="0" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I32" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M32" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N32" s="0" t="n">
         <v>400003</v>
@@ -2466,13 +2466,13 @@
       </c>
       <c r="V32" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>300082</v>
+        <v>300081</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="0" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N33" s="0" t="n">
         <v>400003</v>
@@ -2521,13 +2521,13 @@
       </c>
       <c r="V33" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>300083</v>
+        <v>300082</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="0" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N34" s="0" t="n">
         <v>400003</v>
@@ -2576,13 +2576,13 @@
       </c>
       <c r="V34" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>300084</v>
+        <v>300083</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N35" s="0" t="n">
         <v>400003</v>
@@ -2631,13 +2631,13 @@
       </c>
       <c r="V35" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>300085</v>
+        <v>300084</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="0" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N36" s="0" t="n">
         <v>400003</v>
@@ -2686,44 +2686,49 @@
       </c>
       <c r="V36" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>300091</v>
+        <v>300085</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShockwaveRing</t>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
         </is>
       </c>
       <c r="G37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="0" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I37" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="0" t="inlineStr">
-        <is>
-          <t>0.5,0.5</t>
-        </is>
-      </c>
       <c r="M37" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N37" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O37" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P37" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="O37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="0" t="n">
-        <v>0</v>
+      <c r="R37" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
       </c>
       <c r="S37" s="0" t="n">
         <v>0</v>
@@ -2736,129 +2741,147 @@
       </c>
       <c r="V37" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>300101</v>
+        <v>300091</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcGround</t>
-        </is>
-      </c>
-      <c r="C38" s="0" t="inlineStr"/>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_FireBottle_1</t>
-        </is>
-      </c>
-      <c r="F38" s="0" t="inlineStr"/>
-      <c r="G38" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H38" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I38" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>AttackModeShockwaveRing</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="K38" s="0" t="inlineStr"/>
-      <c r="L38" s="0" t="inlineStr"/>
-      <c r="M38" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>0.5,0.5</t>
+        </is>
+      </c>
+      <c r="M38" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="N38" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O38" s="0" t="inlineStr"/>
-      <c r="P38" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q38" s="0" t="inlineStr"/>
-      <c r="R38" s="0" t="inlineStr"/>
-      <c r="S38" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U38" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>420001</v>
+      </c>
+      <c r="O38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="V38" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>400001</v>
+        <v>300101</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlap</t>
-        </is>
-      </c>
-      <c r="H39" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I39" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J39" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K39" s="0" t="n"/>
-      <c r="L39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P39" s="0" t="n">
-        <v>420008</v>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr"/>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr"/>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="inlineStr"/>
+      <c r="L39" s="0" t="inlineStr"/>
+      <c r="M39" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N39" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O39" s="0" t="inlineStr"/>
+      <c r="P39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" s="0" t="inlineStr"/>
+      <c r="R39" s="0" t="inlineStr"/>
+      <c r="S39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="V39" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>400002</v>
+        <v>400001</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlap</t>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>1000200001:1</t>
         </is>
       </c>
       <c r="H40" s="0" t="n">
@@ -2885,50 +2908,59 @@
       </c>
       <c r="V40" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-中毒</t>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>500001</v>
+        <v>400002</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F41" s="0" t="inlineStr">
+        <is>
+          <t>1000400001:1</t>
         </is>
       </c>
       <c r="H41" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I41" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="0" t="n">
-        <v>500001</v>
+        <v>0.5</v>
+      </c>
+      <c r="K41" s="0" t="n"/>
+      <c r="L41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O41" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P41" s="0" t="n">
-        <v>470001</v>
+        <v>420008</v>
       </c>
       <c r="V41" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
+          <t>AttackModeRegainHP</t>
         </is>
       </c>
       <c r="H42" s="0" t="n">
@@ -2941,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="O42" s="0" t="n">
         <v>100001</v>
@@ -2951,88 +2983,73 @@
       </c>
       <c r="V42" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
+          <t>AttackModeRegainDR</t>
+        </is>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J43" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="O43" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P43" s="0" t="n">
-        <v>6</v>
+        <v>470001</v>
       </c>
       <c r="V43" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Meteorite_1</t>
-        </is>
-      </c>
-      <c r="F44" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
-      </c>
-      <c r="I44" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J44" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K44" s="0" t="n">
-        <v>800001</v>
-      </c>
-      <c r="M44" s="0" t="n">
-        <v>3</v>
+        <v>600001</v>
       </c>
       <c r="O44" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P44" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q44" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="V44" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>700002</v>
+        <v>700001</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
@@ -3041,12 +3058,12 @@
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_Fallupon_Water_1</t>
+          <t>AttackMode_Fallupon_Meteorite_1</t>
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I45" s="0" t="n">
@@ -3074,13 +3091,13 @@
       </c>
       <c r="V45" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球</t>
+          <t>下落范围攻击-火球</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>700003</v>
+        <v>700002</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
@@ -3089,12 +3106,12 @@
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackMode_Fallupon_Water_1</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I46" s="0" t="n">
@@ -3115,19 +3132,34 @@
       <c r="P46" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q46" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
       <c r="V46" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落范围攻击-水球</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>800001</v>
+        <v>700003</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
+        </is>
+      </c>
+      <c r="F47" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I47" s="0" t="n">
@@ -3136,10 +3168,11 @@
       <c r="J47" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K47" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K47" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="M47" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="O47" s="0" t="n">
         <v>100001</v>
@@ -3149,44 +3182,45 @@
       </c>
       <c r="V47" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>300031</v>
+        <v>800001</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I48" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J48" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P48" s="0" t="n"/>
-      <c r="U48" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="K48" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O48" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P48" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="V48" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300032</v>
+        <v>300031</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
@@ -3197,7 +3231,7 @@
         <v>11</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M49" s="0" t="n">
         <v>0</v>
@@ -3207,17 +3241,17 @@
       </c>
       <c r="P49" s="0" t="n"/>
       <c r="U49" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V49" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300033</v>
+        <v>300032</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
@@ -3228,7 +3262,7 @@
         <v>11</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M50" s="0" t="n">
         <v>0</v>
@@ -3238,17 +3272,17 @@
       </c>
       <c r="P50" s="0" t="n"/>
       <c r="U50" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V50" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300034</v>
+        <v>300033</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
@@ -3259,7 +3293,7 @@
         <v>11</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M51" s="0" t="n">
         <v>0</v>
@@ -3269,17 +3303,17 @@
       </c>
       <c r="P51" s="0" t="n"/>
       <c r="U51" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V51" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300035</v>
+        <v>300034</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
@@ -3290,7 +3324,7 @@
         <v>11</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M52" s="0" t="n">
         <v>0</v>
@@ -3300,92 +3334,72 @@
       </c>
       <c r="P52" s="0" t="n"/>
       <c r="U52" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V52" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300041</v>
+        <v>300035</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D53" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E53" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H53" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="M53" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N53" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O53" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P53" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R53" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P53" s="0" t="n"/>
+      <c r="U53" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="V53" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300051</v>
+        <v>300041</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C54" s="0" t="inlineStr"/>
+          <t>AttackModeRangedPiercingRoad</t>
+        </is>
+      </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F54" s="0" t="inlineStr"/>
-      <c r="G54" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H54" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="0" t="inlineStr"/>
-      <c r="K54" s="0" t="inlineStr"/>
-      <c r="L54" s="0" t="inlineStr"/>
       <c r="M54" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N54" s="0" t="n">
-        <v>400003</v>
+        <v>310001</v>
       </c>
       <c r="O54" s="0" t="n">
         <v>100001</v>
@@ -3393,43 +3407,35 @@
       <c r="P54" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q54" s="0" t="inlineStr"/>
       <c r="R54" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="0" t="n">
-        <v>0</v>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="V54" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300071</v>
+        <v>300051</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
-        </is>
-      </c>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr"/>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr"/>
       <c r="G55" s="0" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H55" s="0" t="n">
         <v>0.3</v>
@@ -3437,15 +3443,22 @@
       <c r="I55" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J55" s="0" t="inlineStr"/>
+      <c r="K55" s="0" t="inlineStr"/>
+      <c r="L55" s="0" t="inlineStr"/>
       <c r="M55" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N55" s="0" t="n">
-        <v>0</v>
+        <v>400003</v>
+      </c>
+      <c r="O55" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P55" s="0" t="n">
         <v>420001</v>
       </c>
+      <c r="Q55" s="0" t="inlineStr"/>
       <c r="R55" s="0" t="inlineStr">
         <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
@@ -3461,6 +3474,58 @@
         <v>0</v>
       </c>
       <c r="V55" s="0" t="inlineStr">
+        <is>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R56" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="0" t="inlineStr">
         <is>
           <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1175,6 +1175,11 @@
       </c>
       <c r="V1" s="0" t="inlineStr">
         <is>
+          <t>other_data</t>
+        </is>
+      </c>
+      <c r="W1" s="0" t="inlineStr">
+        <is>
           <t>remark</t>
         </is>
       </c>
@@ -1290,6 +1295,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="W2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1394,10 +1404,15 @@
       </c>
       <c r="U3" s="0" t="inlineStr">
         <is>
-          <t>单次命中目标数上限(&gt;0时按距落点近者优先截断,0/空=不限制;目前仅AttackModeInstantArea系使用)</t>
+          <t>单次命中目标数上限(&gt;0时按距检测点近者优先截断+同生物去重,0/空=不限制;走CheckHitTargetArea的范围攻击与AttackModeInstantArea系通用)</t>
         </is>
       </c>
       <c r="V3" s="0" t="inlineStr">
+        <is>
+          <t>其它扩展参数(&amp;分隔项,:分键值,按key解析)。stuck_time:射空后弹体插地停留秒数(&gt;0启用,空/0=不插地落地即销毁); stuck_sink:插地下沉深度(默认0,正值向下沉)。插地目前仅AttackModeRangedArcTracking系(抛物线落点跟踪)使用; aim_up:瞄准点相对目标脚底上抬高度(默认0=瞄脚底),目前仅AttackModeRangedObliqueTracking(直线斜射跟踪)使用</t>
+        </is>
+      </c>
+      <c r="W3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1428,7 +1443,7 @@
       <c r="P4" s="0" t="n">
         <v>200002</v>
       </c>
-      <c r="V4" s="0" t="inlineStr">
+      <c r="W4" s="0" t="inlineStr">
         <is>
           <t>普通近战攻击</t>
         </is>
@@ -1455,7 +1470,7 @@
         </is>
       </c>
       <c r="K5" s="0" t="n">
-        <v>400001</v>
+        <v>400003</v>
       </c>
       <c r="O5" s="0" t="n">
         <v>100001</v>
@@ -1463,7 +1478,10 @@
       <c r="P5" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="V5" s="0" t="inlineStr">
+      <c r="U5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-前方镰刀打击</t>
         </is>
@@ -1496,7 +1514,7 @@
       <c r="P6" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V6" s="0" t="inlineStr">
+      <c r="W6" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-捶地攻击</t>
         </is>
@@ -1526,7 +1544,7 @@
       <c r="P7" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="V7" s="0" t="inlineStr">
+      <c r="W7" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地火锥</t>
         </is>
@@ -1556,7 +1574,7 @@
       <c r="P8" s="0" t="n">
         <v>420007</v>
       </c>
-      <c r="V8" s="0" t="inlineStr">
+      <c r="W8" s="0" t="inlineStr">
         <is>
           <t>普通近战-捶地冰锥</t>
         </is>
@@ -1609,11 +1627,11 @@
         <v>0</v>
       </c>
       <c r="U9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="0" t="inlineStr">
-        <is>
-          <t>普通近战范围-前方挥砍(攻击前方2单位)</t>
+        <v>3</v>
+      </c>
+      <c r="W9" s="0" t="inlineStr">
+        <is>
+          <t>普通近战范围-前方挥砍(攻击前方2单位,最多命中3个敌人)</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1664,7 @@
       <c r="P10" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="V10" s="0" t="inlineStr">
+      <c r="W10" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-向前挥砍攻击前方6格</t>
         </is>
@@ -1688,7 +1706,7 @@
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="V11" s="0" t="inlineStr">
+      <c r="W11" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击</t>
         </is>
@@ -1727,7 +1745,7 @@
       <c r="P12" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="V12" s="0" t="inlineStr">
+      <c r="W12" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击</t>
         </is>
@@ -1765,7 +1783,7 @@
       <c r="P13" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="V13" s="0" t="inlineStr">
+      <c r="W13" s="0" t="inlineStr">
         <is>
           <t>远程攻击-水球直线攻击</t>
         </is>
@@ -1804,7 +1822,7 @@
       <c r="P14" s="0" t="n">
         <v>420003</v>
       </c>
-      <c r="V14" s="0" t="inlineStr">
+      <c r="W14" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击</t>
         </is>
@@ -1816,7 +1834,7 @@
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArea</t>
+          <t>AttackModeRangedObliqueTracking</t>
         </is>
       </c>
       <c r="C15" s="0" t="n"/>
@@ -1825,6 +1843,11 @@
           <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>1000500002:0.1</t>
+        </is>
+      </c>
       <c r="H15" s="0" t="n">
         <v>0.1</v>
       </c>
@@ -1840,15 +1863,26 @@
       <c r="M15" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N15" s="0" t="n">
+        <v>9</v>
+      </c>
       <c r="O15" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P15" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="U15" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="V15" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击-范围伤害</t>
+          <t>aim_up:0.5</t>
+        </is>
+      </c>
+      <c r="W15" s="0" t="inlineStr">
+        <is>
+          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1892,7 @@
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArea</t>
+          <t>AttackModeRangedObliqueTracking</t>
         </is>
       </c>
       <c r="C16" s="0" t="n"/>
@@ -1867,7 +1901,11 @@
           <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
-      <c r="F16" s="0" t="n"/>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
+        </is>
+      </c>
       <c r="H16" s="0" t="n">
         <v>0.1</v>
       </c>
@@ -1883,15 +1921,26 @@
       <c r="M16" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N16" s="0" t="n">
+        <v>9</v>
+      </c>
       <c r="O16" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P16" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="U16" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="V16" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击-范围伤害</t>
+          <t>aim_up:0.5</t>
+        </is>
+      </c>
+      <c r="W16" s="0" t="inlineStr">
+        <is>
+          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1981,7 @@
       <c r="P17" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V17" s="0" t="inlineStr">
+      <c r="W17" s="0" t="inlineStr">
         <is>
           <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
         </is>
@@ -1975,7 +2024,7 @@
       <c r="P18" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V18" s="0" t="inlineStr">
+      <c r="W18" s="0" t="inlineStr">
         <is>
           <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
         </is>
@@ -2014,7 +2063,7 @@
       <c r="P19" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="V19" s="0" t="inlineStr">
+      <c r="W19" s="0" t="inlineStr">
         <is>
           <t>远程攻击-跟踪-爱心</t>
         </is>
@@ -2052,7 +2101,7 @@
       <c r="P20" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V20" s="0" t="inlineStr">
+      <c r="W20" s="0" t="inlineStr">
         <is>
           <t>远程攻击-抛物线-石头</t>
         </is>
@@ -2076,7 +2125,7 @@
       <c r="S21" s="0" t="n">
         <v>204101</v>
       </c>
-      <c r="V21" s="0" t="inlineStr">
+      <c r="W21" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂弓箭</t>
         </is>
@@ -2100,7 +2149,7 @@
       <c r="S22" s="0" t="n">
         <v>204102</v>
       </c>
-      <c r="V22" s="0" t="inlineStr">
+      <c r="W22" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂火球</t>
         </is>
@@ -2124,7 +2173,7 @@
       <c r="S23" s="0" t="n">
         <v>204103</v>
       </c>
-      <c r="V23" s="0" t="inlineStr">
+      <c r="W23" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂冰球</t>
         </is>
@@ -2156,7 +2205,7 @@
       <c r="P24" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V24" s="0" t="inlineStr">
+      <c r="W24" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂弓箭-子弹道</t>
         </is>
@@ -2189,7 +2238,7 @@
       <c r="P25" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V25" s="0" t="inlineStr">
+      <c r="W25" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂火球-子弹道</t>
         </is>
@@ -2222,7 +2271,7 @@
       <c r="P26" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V26" s="0" t="inlineStr">
+      <c r="W26" s="0" t="inlineStr">
         <is>
           <t>远程攻击-分裂冰球-子弹道</t>
         </is>
@@ -2255,7 +2304,7 @@
       <c r="P27" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V27" s="0" t="inlineStr">
+      <c r="W27" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透</t>
         </is>
@@ -2289,7 +2338,7 @@
       <c r="P28" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V28" s="0" t="inlineStr">
+      <c r="W28" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透火锥</t>
         </is>
@@ -2323,7 +2372,7 @@
       <c r="P29" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V29" s="0" t="inlineStr">
+      <c r="W29" s="0" t="inlineStr">
         <is>
           <t>远程攻击-穿透冰锥</t>
         </is>
@@ -2331,14 +2380,13 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>210001</v>
+        <v>206001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="n"/>
+          <t>AttackModeRangedArcTracking</t>
+        </is>
+      </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
@@ -2347,11 +2395,18 @@
       <c r="H30" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K30" s="0" t="n"/>
+      <c r="I30" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
       <c r="M30" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="N30" s="0" t="n">
         <v>310001</v>
       </c>
       <c r="O30" s="0" t="n">
@@ -2362,139 +2417,131 @@
       </c>
       <c r="R30" s="0" t="inlineStr">
         <is>
-          <t>type:2&amp;color:1,1,1</t>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
       <c r="V30" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击-VFX轨迹(白)</t>
+          <t>stuck_time:3&amp;stuck_sink:0.1</t>
+        </is>
+      </c>
+      <c r="W30" s="0" t="inlineStr">
+        <is>
+          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>300001</v>
+        <v>210001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="n"/>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H31" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I31" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J31" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K31" s="0" t="n">
-        <v>300001</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="K31" s="0" t="n"/>
       <c r="M31" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O31" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P31" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="T31" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="V31" s="0" t="inlineStr">
-        <is>
-          <t>爆炸范围攻击-火焰</t>
+        <v>420011</v>
+      </c>
+      <c r="R31" s="0" t="inlineStr">
+        <is>
+          <t>type:2&amp;color:1,1,1</t>
+        </is>
+      </c>
+      <c r="W31" s="0" t="inlineStr">
+        <is>
+          <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>300061</v>
+        <v>300001</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcBounce</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Axe_1</t>
-        </is>
-      </c>
-      <c r="G32" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeExplosion</t>
+        </is>
       </c>
       <c r="H32" s="0" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>300001</v>
       </c>
       <c r="M32" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="N32" s="0" t="n">
-        <v>400003</v>
+        <v>0</v>
       </c>
       <c r="O32" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P32" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R32" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S32" s="0" t="n">
-        <v>0</v>
+        <v>420008</v>
       </c>
       <c r="T32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="0" t="inlineStr">
-        <is>
-          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
+        <v>50</v>
+      </c>
+      <c r="W32" s="0" t="inlineStr">
+        <is>
+          <t>爆炸范围攻击-火焰</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>300081</v>
+        <v>300061</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
+          <t>AttackModeRangedArcBounce</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Pingpang_1</t>
+          <t>AttackModeVisual_Axe_1</t>
         </is>
       </c>
       <c r="G33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I33" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M33" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N33" s="0" t="n">
         <v>400003</v>
@@ -2519,15 +2566,15 @@
       <c r="U33" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="0" t="inlineStr">
-        <is>
-          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
+      <c r="W33" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>300082</v>
+        <v>300081</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
@@ -2549,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="0" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N34" s="0" t="n">
         <v>400003</v>
@@ -2574,15 +2621,15 @@
       <c r="U34" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="0" t="inlineStr">
-        <is>
-          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
+      <c r="W34" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>300083</v>
+        <v>300082</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
@@ -2604,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="0" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N35" s="0" t="n">
         <v>400003</v>
@@ -2629,15 +2676,15 @@
       <c r="U35" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="0" t="inlineStr">
-        <is>
-          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
+      <c r="W35" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>300084</v>
+        <v>300083</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
@@ -2659,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N36" s="0" t="n">
         <v>400003</v>
@@ -2684,15 +2731,15 @@
       <c r="U36" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="0" t="inlineStr">
-        <is>
-          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
+      <c r="W36" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>300085</v>
+        <v>300084</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
@@ -2714,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="0" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N37" s="0" t="n">
         <v>400003</v>
@@ -2739,46 +2786,51 @@
       <c r="U37" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="0" t="inlineStr">
-        <is>
-          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
+      <c r="W37" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>300091</v>
+        <v>300085</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShockwaveRing</t>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
         </is>
       </c>
       <c r="G38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="0" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I38" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="0" t="inlineStr">
-        <is>
-          <t>0.5,0.5</t>
-        </is>
-      </c>
       <c r="M38" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N38" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O38" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P38" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="O38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="0" t="n">
-        <v>0</v>
+      <c r="R38" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
       </c>
       <c r="S38" s="0" t="n">
         <v>0</v>
@@ -2789,132 +2841,140 @@
       <c r="U38" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="0" t="inlineStr">
-        <is>
-          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
+      <c r="W38" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>300101</v>
+        <v>300091</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcGround</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="inlineStr"/>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_FireBottle_1</t>
-        </is>
-      </c>
-      <c r="F39" s="0" t="inlineStr"/>
-      <c r="G39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I39" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>AttackModeShockwaveRing</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="K39" s="0" t="inlineStr"/>
-      <c r="L39" s="0" t="inlineStr"/>
-      <c r="M39" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>0.5,0.5</t>
+        </is>
+      </c>
+      <c r="M39" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="N39" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O39" s="0" t="inlineStr"/>
-      <c r="P39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q39" s="0" t="inlineStr"/>
-      <c r="R39" s="0" t="inlineStr"/>
-      <c r="S39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V39" s="0" t="inlineStr">
-        <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+        <v>420001</v>
+      </c>
+      <c r="O39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="0" t="inlineStr">
+        <is>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>400001</v>
+        <v>300101</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlapNoDamage</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr">
-        <is>
-          <t>1000200001:1</t>
-        </is>
-      </c>
-      <c r="H40" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I40" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J40" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K40" s="0" t="n"/>
-      <c r="L40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P40" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="V40" s="0" t="inlineStr">
-        <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr"/>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="inlineStr"/>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K40" s="0" t="inlineStr"/>
+      <c r="L40" s="0" t="inlineStr"/>
+      <c r="M40" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N40" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O40" s="0" t="inlineStr"/>
+      <c r="P40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q40" s="0" t="inlineStr"/>
+      <c r="R40" s="0" t="inlineStr"/>
+      <c r="S40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W40" s="0" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>400002</v>
+        <v>400001</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
@@ -2923,7 +2983,7 @@
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t>1000400001:1</t>
+          <t>1000200001:1</t>
         </is>
       </c>
       <c r="H41" s="0" t="n">
@@ -2942,58 +3002,69 @@
       <c r="M41" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="N41" s="0" t="n"/>
       <c r="O41" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P41" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="V41" s="0" t="inlineStr">
-        <is>
-          <t>重叠攻击-中毒</t>
+        <v>630005</v>
+      </c>
+      <c r="W41" s="0" t="inlineStr">
+        <is>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>500001</v>
+        <v>400002</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t>1000400001:1</t>
         </is>
       </c>
       <c r="H42" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I42" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" s="0" t="n">
-        <v>500001</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K42" s="0" t="n"/>
+      <c r="L42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="0" t="n"/>
       <c r="O42" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P42" s="0" t="n">
-        <v>470001</v>
-      </c>
-      <c r="V42" s="0" t="inlineStr">
-        <is>
-          <t>加血</t>
+        <v>630005</v>
+      </c>
+      <c r="W42" s="0" t="inlineStr">
+        <is>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
+          <t>AttackModeRegainHP</t>
         </is>
       </c>
       <c r="H43" s="0" t="n">
@@ -3006,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="O43" s="0" t="n">
         <v>100001</v>
@@ -3014,90 +3085,75 @@
       <c r="P43" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="V43" s="0" t="inlineStr">
-        <is>
-          <t>加护甲</t>
+      <c r="W43" s="0" t="inlineStr">
+        <is>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
+          <t>AttackModeRegainDR</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="O44" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P44" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="V44" s="0" t="inlineStr">
-        <is>
-          <t>引诱敌人到当前线路</t>
+        <v>470001</v>
+      </c>
+      <c r="W44" s="0" t="inlineStr">
+        <is>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Meteorite_1</t>
-        </is>
-      </c>
-      <c r="F45" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
-      </c>
-      <c r="I45" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J45" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K45" s="0" t="n">
-        <v>800001</v>
-      </c>
-      <c r="M45" s="0" t="n">
-        <v>3</v>
+        <v>600001</v>
       </c>
       <c r="O45" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P45" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q45" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V45" s="0" t="inlineStr">
-        <is>
-          <t>下落范围攻击-火球</t>
+        <v>6</v>
+      </c>
+      <c r="W45" s="0" t="inlineStr">
+        <is>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>700002</v>
+        <v>700001</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
@@ -3106,12 +3162,12 @@
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_Fallupon_Water_1</t>
+          <t>AttackMode_Fallupon_Meteorite_1</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I46" s="0" t="n">
@@ -3137,15 +3193,15 @@
           <t>0,6,0</t>
         </is>
       </c>
-      <c r="V46" s="0" t="inlineStr">
-        <is>
-          <t>下落范围攻击-水球</t>
+      <c r="W46" s="0" t="inlineStr">
+        <is>
+          <t>下落范围攻击-火球</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>700003</v>
+        <v>700002</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
@@ -3154,12 +3210,12 @@
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackMode_Fallupon_Water_1</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I47" s="0" t="n">
@@ -3180,19 +3236,34 @@
       <c r="P47" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V47" s="0" t="inlineStr">
-        <is>
-          <t>下落范围攻击-冰球</t>
+      <c r="Q47" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="W47" s="0" t="inlineStr">
+        <is>
+          <t>下落范围攻击-水球</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>800001</v>
+        <v>700003</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I48" s="0" t="n">
@@ -3201,10 +3272,11 @@
       <c r="J48" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K48" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K48" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="O48" s="0" t="n">
         <v>100001</v>
@@ -3212,46 +3284,47 @@
       <c r="P48" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="V48" s="0" t="inlineStr">
-        <is>
-          <t>下落攻击-雷击</t>
+      <c r="W48" s="0" t="inlineStr">
+        <is>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300031</v>
+        <v>800001</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I49" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P49" s="0" t="n"/>
-      <c r="U49" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V49" s="0" t="inlineStr">
-        <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        <v>1.5</v>
+      </c>
+      <c r="K49" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O49" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P49" s="0" t="n">
+        <v>420008</v>
+      </c>
+      <c r="W49" s="0" t="inlineStr">
+        <is>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300032</v>
+        <v>300031</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
@@ -3262,7 +3335,7 @@
         <v>11</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M50" s="0" t="n">
         <v>0</v>
@@ -3272,17 +3345,17 @@
       </c>
       <c r="P50" s="0" t="n"/>
       <c r="U50" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="V50" s="0" t="inlineStr">
-        <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        <v>1</v>
+      </c>
+      <c r="W50" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300033</v>
+        <v>300032</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
@@ -3293,7 +3366,7 @@
         <v>11</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M51" s="0" t="n">
         <v>0</v>
@@ -3303,17 +3376,17 @@
       </c>
       <c r="P51" s="0" t="n"/>
       <c r="U51" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="V51" s="0" t="inlineStr">
-        <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        <v>2</v>
+      </c>
+      <c r="W51" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300034</v>
+        <v>300033</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
@@ -3324,7 +3397,7 @@
         <v>11</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M52" s="0" t="n">
         <v>0</v>
@@ -3334,17 +3407,17 @@
       </c>
       <c r="P52" s="0" t="n"/>
       <c r="U52" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="V52" s="0" t="inlineStr">
-        <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        <v>3</v>
+      </c>
+      <c r="W52" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300035</v>
+        <v>300034</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
@@ -3355,7 +3428,7 @@
         <v>11</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M53" s="0" t="n">
         <v>0</v>
@@ -3365,92 +3438,72 @@
       </c>
       <c r="P53" s="0" t="n"/>
       <c r="U53" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="V53" s="0" t="inlineStr">
-        <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+        <v>4</v>
+      </c>
+      <c r="W53" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300041</v>
+        <v>300035</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D54" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E54" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H54" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="M54" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N54" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O54" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P54" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R54" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
-      </c>
-      <c r="V54" s="0" t="inlineStr">
-        <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+        <v>420003</v>
+      </c>
+      <c r="P54" s="0" t="n"/>
+      <c r="U54" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="W54" s="0" t="inlineStr">
+        <is>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300051</v>
+        <v>300041</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C55" s="0" t="inlineStr"/>
+          <t>AttackModeRangedPiercingRoad</t>
+        </is>
+      </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F55" s="0" t="inlineStr"/>
-      <c r="G55" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H55" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="0" t="inlineStr"/>
-      <c r="K55" s="0" t="inlineStr"/>
-      <c r="L55" s="0" t="inlineStr"/>
       <c r="M55" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N55" s="0" t="n">
-        <v>400003</v>
+        <v>310001</v>
       </c>
       <c r="O55" s="0" t="n">
         <v>100001</v>
@@ -3458,43 +3511,35 @@
       <c r="P55" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q55" s="0" t="inlineStr"/>
       <c r="R55" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="0" t="inlineStr">
-        <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
+      </c>
+      <c r="W55" s="0" t="inlineStr">
+        <is>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300071</v>
+        <v>300051</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
-        </is>
-      </c>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr"/>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr"/>
       <c r="G56" s="0" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H56" s="0" t="n">
         <v>0.3</v>
@@ -3502,15 +3547,22 @@
       <c r="I56" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J56" s="0" t="inlineStr"/>
+      <c r="K56" s="0" t="inlineStr"/>
+      <c r="L56" s="0" t="inlineStr"/>
       <c r="M56" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N56" s="0" t="n">
-        <v>0</v>
+        <v>400003</v>
+      </c>
+      <c r="O56" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P56" s="0" t="n">
         <v>420001</v>
       </c>
+      <c r="Q56" s="0" t="inlineStr"/>
       <c r="R56" s="0" t="inlineStr">
         <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
@@ -3525,7 +3577,59 @@
       <c r="U56" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="0" t="inlineStr">
+      <c r="W56" s="0" t="inlineStr">
+        <is>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R57" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="0" t="inlineStr">
         <is>
           <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -2933,7 +2933,9 @@
           <t>1.2</t>
         </is>
       </c>
-      <c r="K40" s="0" t="inlineStr"/>
+      <c r="K40" s="0" t="n">
+        <v>1800001</v>
+      </c>
       <c r="L40" s="0" t="inlineStr"/>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3337,6 +3339,9 @@
       <c r="J50" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="K50" t="n">
+        <v>900003</v>
+      </c>
       <c r="M50" s="0" t="n">
         <v>0</v>
       </c>
@@ -3368,6 +3373,9 @@
       <c r="J51" s="0" t="n">
         <v>0.4</v>
       </c>
+      <c r="K51" t="n">
+        <v>900003</v>
+      </c>
       <c r="M51" s="0" t="n">
         <v>0</v>
       </c>
@@ -3399,6 +3407,9 @@
       <c r="J52" s="0" t="n">
         <v>0.6</v>
       </c>
+      <c r="K52" t="n">
+        <v>900003</v>
+      </c>
       <c r="M52" s="0" t="n">
         <v>0</v>
       </c>
@@ -3430,6 +3441,9 @@
       <c r="J53" s="0" t="n">
         <v>0.8</v>
       </c>
+      <c r="K53" t="n">
+        <v>900003</v>
+      </c>
       <c r="M53" s="0" t="n">
         <v>0</v>
       </c>
@@ -3460,6 +3474,9 @@
       </c>
       <c r="J54" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>900003</v>
       </c>
       <c r="M54" s="0" t="n">
         <v>0</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="AttackModeInfo" sheetId="1" state="visible" r:id="rId1"/>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14.25" customHeight="1" s="1">
       <c r="A11" s="0" t="n">
         <v>200001</v>
       </c>
@@ -1864,13 +1864,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="0" t="n">
-        <v>9</v>
+        <v>100003</v>
       </c>
       <c r="O15" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P15" s="0" t="n">
-        <v>420008</v>
+        <v>420006</v>
       </c>
       <c r="U15" s="0" t="n">
         <v>3</v>
@@ -1922,13 +1922,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="0" t="n">
-        <v>9</v>
+        <v>100003</v>
       </c>
       <c r="O16" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P16" s="0" t="n">
-        <v>420008</v>
+        <v>420006</v>
       </c>
       <c r="U16" s="0" t="n">
         <v>3</v>
@@ -1973,13 +1973,13 @@
         <v>1.5</v>
       </c>
       <c r="N17" s="0" t="n">
-        <v>9</v>
+        <v>100003</v>
       </c>
       <c r="O17" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P17" s="0" t="n">
-        <v>420008</v>
+        <v>420006</v>
       </c>
       <c r="W17" s="0" t="inlineStr">
         <is>
@@ -2016,13 +2016,13 @@
         <v>1.5</v>
       </c>
       <c r="N18" s="0" t="n">
-        <v>9</v>
+        <v>100003</v>
       </c>
       <c r="O18" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P18" s="0" t="n">
-        <v>420008</v>
+        <v>420006</v>
       </c>
       <c r="W18" s="0" t="inlineStr">
         <is>
@@ -2039,9 +2039,10 @@
           <t>AttackModeRangedTracking</t>
         </is>
       </c>
-      <c r="C19" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedLove</t>
+      <c r="C19" s="0" t="n"/>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedLove</t>
         </is>
       </c>
       <c r="H19" s="0" t="n">
@@ -2056,6 +2057,9 @@
       <c r="K19" s="0" t="n"/>
       <c r="M19" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>100003</v>
       </c>
       <c r="O19" s="0" t="n">
         <v>100001</v>
@@ -2431,7 +2435,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="14.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
         <v>210001</v>
       </c>
@@ -3139,13 +3143,13 @@
         <v>0</v>
       </c>
       <c r="K45" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="O45" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P45" s="0" t="n">
-        <v>6</v>
+        <v>470001</v>
       </c>
       <c r="W45" s="0" t="inlineStr">
         <is>
@@ -3339,7 +3343,7 @@
       <c r="J50" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K50" s="0" t="n">
         <v>900003</v>
       </c>
       <c r="M50" s="0" t="n">
@@ -3373,7 +3377,7 @@
       <c r="J51" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51" s="0" t="n">
         <v>900003</v>
       </c>
       <c r="M51" s="0" t="n">
@@ -3407,7 +3411,7 @@
       <c r="J52" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K52" s="0" t="n">
         <v>900003</v>
       </c>
       <c r="M52" s="0" t="n">
@@ -3441,7 +3445,7 @@
       <c r="J53" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K53" s="0" t="n">
         <v>900003</v>
       </c>
       <c r="M53" s="0" t="n">
@@ -3475,7 +3479,7 @@
       <c r="J54" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K54" s="0" t="n">
         <v>900003</v>
       </c>
       <c r="M54" s="0" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1514,6 +1514,9 @@
       <c r="P6" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="U6" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="W6" s="0" t="inlineStr">
         <is>
           <t>普通近战范围-捶地攻击</t>
@@ -1544,9 +1547,12 @@
       <c r="P7" s="0" t="n">
         <v>420007</v>
       </c>
+      <c r="U7" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="W7" s="0" t="inlineStr">
         <is>
-          <t>普通近战-捶地火锥</t>
+          <t>普通近战-捶地火锥(最多命中5个敌人)</t>
         </is>
       </c>
     </row>
@@ -1574,9 +1580,12 @@
       <c r="P8" s="0" t="n">
         <v>420007</v>
       </c>
+      <c r="U8" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="W8" s="0" t="inlineStr">
         <is>
-          <t>普通近战-捶地冰锥</t>
+          <t>普通近战-捶地冰锥(最多命中5个敌人)</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2067,7 @@
       <c r="M19" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="0" t="n">
         <v>100003</v>
       </c>
       <c r="O19" s="0" t="n">
@@ -2079,12 +2088,13 @@
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArc</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
+          <t>AttackModeRangedArcArea</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="G20" s="0" t="n">
@@ -2093,21 +2103,40 @@
       <c r="H20" s="0" t="n">
         <v>0.25</v>
       </c>
-      <c r="I20" s="0" t="n"/>
-      <c r="J20" s="0" t="n"/>
-      <c r="K20" s="0" t="n"/>
+      <c r="I20" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="n">
+        <v>1900001</v>
+      </c>
       <c r="M20" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N20" t="n">
+        <v>100002</v>
+      </c>
       <c r="O20" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P20" s="0" t="n">
-        <v>420008</v>
+        <v>420011</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="U20" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-石头</t>
+          <t>远程攻击-抛物线-落点范围(落点AOE,hit_max=5,近者优先;DSP石头+残影拖尾;击中特效1900001;出手sound_knife_miss_2,命中sound_hit_11)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
         </is>
@@ -2117,7 +2117,7 @@
       <c r="M20" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="0" t="n">
         <v>100002</v>
       </c>
       <c r="O20" s="0" t="n">
@@ -2126,7 +2126,7 @@
       <c r="P20" s="0" t="n">
         <v>420011</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" s="0" t="inlineStr">
         <is>
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
@@ -2153,6 +2153,9 @@
       <c r="H21" s="0" t="n"/>
       <c r="K21" s="0" t="n"/>
       <c r="M21" s="0" t="n"/>
+      <c r="N21" s="0" t="n">
+        <v>310001</v>
+      </c>
       <c r="O21" s="0" t="n"/>
       <c r="P21" s="0" t="n"/>
       <c r="S21" s="0" t="n">
@@ -2170,21 +2173,50 @@
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplit</t>
+          <t>AttackModeRangedChain</t>
         </is>
       </c>
       <c r="C22" s="0" t="n"/>
-      <c r="H22" s="0" t="n"/>
-      <c r="K22" s="0" t="n"/>
-      <c r="M22" s="0" t="n"/>
-      <c r="O22" s="0" t="n"/>
-      <c r="P22" s="0" t="n"/>
-      <c r="S22" s="0" t="n">
-        <v>204102</v>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>1000500002:0.1</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <v>100003</v>
+      </c>
+      <c r="O22" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P22" s="0" t="n">
+        <v>420006</v>
+      </c>
+      <c r="S22" s="0" t="n"/>
+      <c r="U22" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="W22" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂火球</t>
+          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
         </is>
       </c>
     </row>
@@ -2194,21 +2226,50 @@
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplit</t>
+          <t>AttackModeRangedChain</t>
         </is>
       </c>
       <c r="C23" s="0" t="n"/>
-      <c r="H23" s="0" t="n"/>
-      <c r="K23" s="0" t="n"/>
-      <c r="M23" s="0" t="n"/>
-      <c r="O23" s="0" t="n"/>
-      <c r="P23" s="0" t="n"/>
-      <c r="S23" s="0" t="n">
-        <v>204103</v>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="0" t="n">
+        <v>100003</v>
+      </c>
+      <c r="O23" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P23" s="0" t="n">
+        <v>420006</v>
+      </c>
+      <c r="S23" s="0" t="n"/>
+      <c r="U23" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="W23" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂冰球</t>
+          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
         </is>
       </c>
     </row>
@@ -2246,22 +2307,22 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>204102</v>
+        <v>205001</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplitChild</t>
-        </is>
-      </c>
-      <c r="C25" s="0" t="n"/>
-      <c r="D25" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeRangedPiercing</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
         </is>
       </c>
       <c r="H25" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="K25" s="0" t="n"/>
       <c r="M25" s="0" t="n">
         <v>1</v>
       </c>
@@ -2273,28 +2334,29 @@
       </c>
       <c r="W25" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂火球-子弹道</t>
+          <t>远程攻击-穿透</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>204103</v>
+        <v>205002</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplitChild</t>
+          <t>AttackModeRangedPiercing</t>
         </is>
       </c>
       <c r="C26" s="0" t="n"/>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="H26" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="K26" s="0" t="n"/>
       <c r="M26" s="0" t="n">
         <v>1</v>
       </c>
@@ -2306,22 +2368,23 @@
       </c>
       <c r="W26" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂冰球-子弹道</t>
+          <t>远程攻击-穿透火锥</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>205001</v>
+        <v>205003</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
           <t>AttackModeRangedPiercing</t>
         </is>
       </c>
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
+      <c r="C27" s="0" t="n"/>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="H27" s="0" t="n">
@@ -2339,57 +2402,76 @@
       </c>
       <c r="W27" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透</t>
+          <t>远程攻击-穿透冰锥</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>205002</v>
+        <v>206001</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="n"/>
+          <t>AttackModeRangedArcTracking</t>
+        </is>
+      </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H28" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K28" s="0" t="n"/>
+      <c r="I28" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
       <c r="M28" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N28" s="0" t="n">
+        <v>310001</v>
+      </c>
       <c r="O28" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P28" s="0" t="n">
-        <v>420008</v>
+        <v>420011</v>
+      </c>
+      <c r="R28" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="V28" s="0" t="inlineStr">
+        <is>
+          <t>stuck_time:3&amp;stuck_sink:0.1</t>
+        </is>
       </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透火锥</t>
+          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>205003</v>
+        <v>210001</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
+          <t>AttackModeRanged</t>
         </is>
       </c>
       <c r="C29" s="0" t="n"/>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H29" s="0" t="n">
@@ -2399,182 +2481,189 @@
       <c r="M29" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N29" s="2" t="n">
+        <v>310001</v>
+      </c>
       <c r="O29" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P29" s="0" t="n">
-        <v>420008</v>
+        <v>420011</v>
+      </c>
+      <c r="R29" s="0" t="inlineStr">
+        <is>
+          <t>type:2&amp;color:1,1,1</t>
+        </is>
       </c>
       <c r="W29" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透冰锥</t>
+          <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>206001</v>
+        <v>300001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcTracking</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeExplosion</t>
         </is>
       </c>
       <c r="H30" s="0" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="I30" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="J30" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="J30" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>300002</v>
       </c>
       <c r="M30" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="0" t="n">
-        <v>310001</v>
+        <v>0</v>
       </c>
       <c r="O30" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P30" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R30" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="V30" s="0" t="inlineStr">
-        <is>
-          <t>stuck_time:3&amp;stuck_sink:0.1</t>
-        </is>
+        <v>420008</v>
+      </c>
+      <c r="T30" s="0" t="n">
+        <v>50</v>
       </c>
       <c r="W30" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
+          <t>爆炸范围攻击-火焰</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
-        <v>210001</v>
+        <v>300002</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="n"/>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeExplosion</t>
         </is>
       </c>
       <c r="H31" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K31" s="0" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>300002</v>
+      </c>
       <c r="M31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P31" s="0" t="n">
+        <v>420008</v>
+      </c>
+      <c r="T31" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O31" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P31" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R31" s="0" t="inlineStr">
-        <is>
-          <t>type:2&amp;color:1,1,1</t>
-        </is>
-      </c>
       <c r="W31" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击-VFX轨迹(白)</t>
+          <t>爆炸范围攻击-火焰(敢死队)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>300001</v>
+        <v>300061</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
-        </is>
+          <t>AttackModeRangedArcBounce</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Axe_1</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H32" s="0" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J32" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K32" s="0" t="n">
-        <v>300001</v>
+        <v>0</v>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="M32" s="0" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="N32" s="0" t="n">
+        <v>400003</v>
       </c>
       <c r="O32" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P32" s="0" t="n">
-        <v>420008</v>
+        <v>420001</v>
+      </c>
+      <c r="R32" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S32" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T32" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="U32" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W32" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰</t>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>300061</v>
+        <v>300081</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcBounce</t>
+          <t>AttackModeRangedRebound</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Axe_1</t>
+          <t>AttackModeVisual_Pingpang_1</t>
         </is>
       </c>
       <c r="G33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I33" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="M33" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N33" s="0" t="n">
         <v>400003</v>
@@ -2601,13 +2690,13 @@
       </c>
       <c r="W33" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>300081</v>
+        <v>300082</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
@@ -2629,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="0" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N34" s="0" t="n">
         <v>400003</v>
@@ -2656,13 +2745,13 @@
       </c>
       <c r="W34" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>300082</v>
+        <v>300083</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
@@ -2684,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="0" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N35" s="0" t="n">
         <v>400003</v>
@@ -2711,13 +2800,13 @@
       </c>
       <c r="W35" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>300083</v>
+        <v>300084</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
@@ -2739,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="0" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N36" s="0" t="n">
         <v>400003</v>
@@ -2766,13 +2855,13 @@
       </c>
       <c r="W36" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>300084</v>
+        <v>300085</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
@@ -2794,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="0" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N37" s="0" t="n">
         <v>400003</v>
@@ -2821,49 +2910,47 @@
       </c>
       <c r="W37" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>300085</v>
+        <v>300091</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
-        </is>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Pingpang_1</t>
+          <t>AttackModeShockwaveRing</t>
         </is>
       </c>
       <c r="G38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="0" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I38" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>0.5,0.5</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="n">
+        <v>1700001</v>
+      </c>
       <c r="M38" s="0" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N38" s="0" t="n">
-        <v>400003</v>
+        <v>420001</v>
       </c>
       <c r="O38" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P38" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R38" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S38" s="0" t="n">
         <v>0</v>
@@ -2876,140 +2963,133 @@
       </c>
       <c r="W38" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>300091</v>
+        <v>300101</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShockwaveRing</t>
-        </is>
-      </c>
-      <c r="G39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr"/>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr"/>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>0.5,0.5</t>
-        </is>
-      </c>
-      <c r="M39" s="0" t="n">
-        <v>6</v>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="n">
+        <v>1800001</v>
+      </c>
+      <c r="L39" s="0" t="inlineStr"/>
+      <c r="M39" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N39" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="O39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="0" t="n">
-        <v>0</v>
+        <v>400003</v>
+      </c>
+      <c r="O39" s="0" t="inlineStr"/>
+      <c r="P39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" s="0" t="inlineStr"/>
+      <c r="R39" s="0" t="inlineStr"/>
+      <c r="S39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U39" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="W39" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300101</v>
+        <v>400001</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcGround</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="inlineStr"/>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_FireBottle_1</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr"/>
-      <c r="G40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I40" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J40" s="0" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="K40" s="0" t="n">
-        <v>1800001</v>
-      </c>
-      <c r="L40" s="0" t="inlineStr"/>
-      <c r="M40" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N40" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O40" s="0" t="inlineStr"/>
-      <c r="P40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q40" s="0" t="inlineStr"/>
-      <c r="R40" s="0" t="inlineStr"/>
-      <c r="S40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>1000200001:1</t>
+        </is>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K40" s="0" t="n"/>
+      <c r="L40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="0" t="n"/>
+      <c r="O40" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P40" s="0" t="n">
+        <v>630005</v>
       </c>
       <c r="W40" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>400001</v>
+        <v>400002</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
@@ -3018,7 +3098,7 @@
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t>1000200001:1</t>
+          <t>1000400001:1</t>
         </is>
       </c>
       <c r="H41" s="0" t="n">
@@ -3046,60 +3126,50 @@
       </c>
       <c r="W41" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>400002</v>
+        <v>500001</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlapNoDamage</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr">
-        <is>
-          <t>1000400001:1</t>
+          <t>AttackModeRegainHP</t>
         </is>
       </c>
       <c r="H42" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I42" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K42" s="0" t="n"/>
-      <c r="L42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="0" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K42" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="O42" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P42" s="0" t="n">
-        <v>630005</v>
+        <v>470001</v>
       </c>
       <c r="W42" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-中毒</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>500001</v>
+        <v>500002</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeRegainDR</t>
         </is>
       </c>
       <c r="H43" s="0" t="n">
@@ -3112,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="0" t="n">
-        <v>500001</v>
+        <v>500002</v>
       </c>
       <c r="O43" s="0" t="n">
         <v>100001</v>
@@ -3122,27 +3192,21 @@
       </c>
       <c r="W43" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>500002</v>
+        <v>600001</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
-        </is>
-      </c>
-      <c r="H44" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J44" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="0" t="n">
         <v>500002</v>
@@ -3155,40 +3219,61 @@
       </c>
       <c r="W44" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>600001</v>
+        <v>700001</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Meteorite_1</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>1000500001:0.5</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K45" s="0" t="n">
-        <v>500002</v>
+        <v>800001</v>
+      </c>
+      <c r="M45" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="O45" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P45" s="0" t="n">
-        <v>470001</v>
+        <v>420008</v>
+      </c>
+      <c r="Q45" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
       </c>
       <c r="W45" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>下落范围攻击-火球</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>700001</v>
+        <v>700002</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
@@ -3197,12 +3282,12 @@
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_Fallupon_Meteorite_1</t>
+          <t>AttackMode_Fallupon_Water_1</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>1000500001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I46" s="0" t="n">
@@ -3230,13 +3315,13 @@
       </c>
       <c r="W46" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球</t>
+          <t>下落范围攻击-水球</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>700002</v>
+        <v>700003</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
@@ -3245,12 +3330,12 @@
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_Fallupon_Water_1</t>
+          <t>AttackMode_Fallupon_Ice_1</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I47" s="0" t="n">
@@ -3271,34 +3356,19 @@
       <c r="P47" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="Q47" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
       <c r="W47" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>700003</v>
+        <v>800001</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
-        </is>
-      </c>
-      <c r="F48" s="0" t="inlineStr">
-        <is>
-          <t>1000700001:0.5</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I48" s="0" t="n">
@@ -3307,11 +3377,10 @@
       <c r="J48" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K48" s="0" t="n">
-        <v>800001</v>
-      </c>
-      <c r="M48" s="0" t="n">
-        <v>3</v>
+      <c r="K48" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
       </c>
       <c r="O48" s="0" t="n">
         <v>100001</v>
@@ -3321,45 +3390,47 @@
       </c>
       <c r="W48" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>800001</v>
+        <v>300031</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeInstantAreaThunder</t>
         </is>
       </c>
       <c r="I49" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K49" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
-      </c>
-      <c r="O49" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P49" s="0" t="n">
-        <v>420008</v>
+        <v>0.2</v>
+      </c>
+      <c r="K49" s="0" t="n">
+        <v>900003</v>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="P49" s="0" t="n"/>
+      <c r="U49" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300031</v>
+        <v>300032</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
@@ -3370,7 +3441,7 @@
         <v>11</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="K50" s="0" t="n">
         <v>900003</v>
@@ -3383,17 +3454,17 @@
       </c>
       <c r="P50" s="0" t="n"/>
       <c r="U50" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300032</v>
+        <v>300033</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
@@ -3404,7 +3475,7 @@
         <v>11</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K51" s="0" t="n">
         <v>900003</v>
@@ -3417,17 +3488,17 @@
       </c>
       <c r="P51" s="0" t="n"/>
       <c r="U51" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300033</v>
+        <v>300034</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
@@ -3438,7 +3509,7 @@
         <v>11</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K52" s="0" t="n">
         <v>900003</v>
@@ -3451,17 +3522,17 @@
       </c>
       <c r="P52" s="0" t="n"/>
       <c r="U52" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300034</v>
+        <v>300035</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
@@ -3472,7 +3543,7 @@
         <v>11</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>900003</v>
@@ -3485,75 +3556,92 @@
       </c>
       <c r="P53" s="0" t="n"/>
       <c r="U53" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300035</v>
+        <v>300041</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
-        </is>
-      </c>
-      <c r="I54" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J54" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" s="0" t="n">
-        <v>900003</v>
+          <t>AttackModeRangedPiercingRoad</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>0.3</v>
       </c>
       <c r="M54" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N54" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P54" s="0" t="n"/>
-      <c r="U54" s="0" t="n">
-        <v>5</v>
+        <v>310001</v>
+      </c>
+      <c r="O54" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P54" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R54" s="0" t="inlineStr">
+        <is>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300041</v>
+        <v>300051</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr"/>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E55" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr"/>
+      <c r="G55" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H55" s="0" t="n">
         <v>0.3</v>
       </c>
+      <c r="I55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="0" t="inlineStr"/>
+      <c r="K55" s="0" t="inlineStr"/>
+      <c r="L55" s="0" t="inlineStr"/>
       <c r="M55" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N55" s="0" t="n">
-        <v>310001</v>
+        <v>400003</v>
       </c>
       <c r="O55" s="0" t="n">
         <v>100001</v>
@@ -3561,35 +3649,43 @@
       <c r="P55" s="0" t="n">
         <v>420001</v>
       </c>
+      <c r="Q55" s="0" t="inlineStr"/>
       <c r="R55" s="0" t="inlineStr">
         <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300051</v>
+        <v>300071</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C56" s="0" t="inlineStr"/>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F56" s="0" t="inlineStr"/>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
       <c r="G56" s="0" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H56" s="0" t="n">
         <v>0.3</v>
@@ -3597,22 +3693,15 @@
       <c r="I56" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="0" t="inlineStr"/>
-      <c r="K56" s="0" t="inlineStr"/>
-      <c r="L56" s="0" t="inlineStr"/>
       <c r="M56" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N56" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O56" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P56" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q56" s="0" t="inlineStr"/>
       <c r="R56" s="0" t="inlineStr">
         <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
@@ -3628,58 +3717,6 @@
         <v>0</v>
       </c>
       <c r="W56" s="0" t="inlineStr">
-        <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="n">
-        <v>300071</v>
-      </c>
-      <c r="B57" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeOrbit</t>
-        </is>
-      </c>
-      <c r="D57" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
-      <c r="G57" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="H57" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R57" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" s="0" t="inlineStr">
         <is>
           <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1515,7 +1515,7 @@
         <v>420008</v>
       </c>
       <c r="U6" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W6" s="0" t="inlineStr">
         <is>
@@ -1529,7 +1529,12 @@
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>AttackModeMeleeArea</t>
+          <t>AttackModeInstantArea</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="I7" s="0" t="n">
@@ -1548,11 +1553,16 @@
         <v>420007</v>
       </c>
       <c r="U7" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="V7" s="0" t="inlineStr">
+        <is>
+          <t>dr_damage_rate:2&amp;hp_damage_rate:0.5&amp;hit_decay:1</t>
+        </is>
       </c>
       <c r="W7" s="0" t="inlineStr">
         <is>
-          <t>普通近战-捶地火锥(最多命中5个敌人)</t>
+          <t>远程瞬时-捶地火锥（目标脚下释放，最多命中5个全额，护甲双倍/血量半伤，10%烧伤）</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1572,12 @@
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>AttackModeMeleeArea</t>
+          <t>AttackModeInstantArea</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="I8" s="0" t="n">
@@ -1581,11 +1596,16 @@
         <v>420007</v>
       </c>
       <c r="U8" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="V8" s="0" t="inlineStr">
+        <is>
+          <t>dr_damage_rate:2&amp;hp_damage_rate:0.5&amp;hit_decay:1</t>
+        </is>
       </c>
       <c r="W8" s="0" t="inlineStr">
         <is>
-          <t>普通近战-捶地冰锥(最多命中5个敌人)</t>
+          <t>远程瞬时-捶地冰锥（目标脚下释放，最多命中5个全额，护甲双倍/血量半伤，10%冰缓）</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2152,7 @@
         </is>
       </c>
       <c r="U20" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
@@ -2314,9 +2334,10 @@
           <t>AttackModeRangedPiercing</t>
         </is>
       </c>
-      <c r="C25" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
+      <c r="C25" s="0" t="inlineStr"/>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H25" s="0" t="n">
@@ -2326,11 +2347,19 @@
       <c r="M25" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N25" s="0" t="n">
+        <v>310001</v>
+      </c>
       <c r="O25" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P25" s="0" t="n">
-        <v>420008</v>
+        <v>420011</v>
+      </c>
+      <c r="R25" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W25" s="0" t="inlineStr">
         <is>
@@ -2344,13 +2373,18 @@
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
+          <t>AttackModeRangedPiercingShrink</t>
         </is>
       </c>
       <c r="C26" s="0" t="n"/>
       <c r="D26" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedFireBall</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H26" s="0" t="n">
@@ -2360,15 +2394,18 @@
       <c r="M26" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N26" s="0" t="n">
+        <v>100003</v>
+      </c>
       <c r="O26" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P26" s="0" t="n">
-        <v>420008</v>
+        <v>420006</v>
       </c>
       <c r="W26" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透火锥</t>
+          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
         </is>
       </c>
     </row>
@@ -2378,13 +2415,18 @@
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
+          <t>AttackModeRangedPiercingShrink</t>
         </is>
       </c>
       <c r="C27" s="0" t="n"/>
       <c r="D27" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H27" s="0" t="n">
@@ -2394,81 +2436,78 @@
       <c r="M27" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N27" s="0" t="n">
+        <v>100003</v>
+      </c>
       <c r="O27" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P27" s="0" t="n">
-        <v>420008</v>
+        <v>420006</v>
       </c>
       <c r="W27" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透冰锥</t>
+          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>206001</v>
+        <v>205004</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcTracking</t>
-        </is>
-      </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
+          <t>AttackModeMelee</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H28" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="I28" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J28" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="0" t="n">
-        <v>310001</v>
+        <v>0</v>
       </c>
       <c r="O28" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P28" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R28" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="V28" s="0" t="inlineStr">
-        <is>
-          <t>stuck_time:3&amp;stuck_sink:0.1</t>
-        </is>
+        <v>200007</v>
+      </c>
+      <c r="S28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
+          <t>普通近战攻击-单体(兽人战士)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>210001</v>
+        <v>206001</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="n"/>
+          <t>AttackModeRangedArcTracking</t>
+        </is>
+      </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
@@ -2477,11 +2516,18 @@
       <c r="H29" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K29" s="0" t="n"/>
+      <c r="I29" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
       <c r="M29" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="N29" s="0" t="n">
         <v>310001</v>
       </c>
       <c r="O29" s="0" t="n">
@@ -2492,57 +2538,65 @@
       </c>
       <c r="R29" s="0" t="inlineStr">
         <is>
-          <t>type:2&amp;color:1,1,1</t>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="V29" s="0" t="inlineStr">
+        <is>
+          <t>stuck_time:3&amp;stuck_sink:0.1</t>
         </is>
       </c>
       <c r="W29" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击-VFX轨迹(白)</t>
+          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>300001</v>
+        <v>210001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="n"/>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H30" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I30" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J30" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K30" s="0" t="n">
-        <v>300002</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="K30" s="0" t="n"/>
       <c r="M30" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O30" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P30" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="T30" s="0" t="n">
-        <v>50</v>
+        <v>420011</v>
+      </c>
+      <c r="R30" s="0" t="inlineStr">
+        <is>
+          <t>type:2&amp;color:1,1,1</t>
+        </is>
       </c>
       <c r="W30" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰</t>
+          <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
-        <v>300002</v>
+        <v>300001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
@@ -2571,99 +2625,83 @@
         <v>420008</v>
       </c>
       <c r="T31" s="0" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="W31" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰(敢死队)</t>
+          <t>爆炸范围攻击-火焰</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>300061</v>
+        <v>300002</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcBounce</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Axe_1</t>
-        </is>
-      </c>
-      <c r="G32" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeExplosion</t>
+        </is>
       </c>
       <c r="H32" s="0" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>300002</v>
       </c>
       <c r="M32" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="N32" s="0" t="n">
-        <v>400003</v>
+        <v>0</v>
       </c>
       <c r="O32" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P32" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R32" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S32" s="0" t="n">
-        <v>0</v>
+        <v>420008</v>
       </c>
       <c r="T32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
+          <t>爆炸范围攻击-火焰(敢死队)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>300081</v>
+        <v>300061</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
+          <t>AttackModeRangedArcBounce</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Pingpang_1</t>
+          <t>AttackModeVisual_Axe_1</t>
         </is>
       </c>
       <c r="G33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I33" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M33" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N33" s="0" t="n">
         <v>400003</v>
@@ -2690,13 +2728,13 @@
       </c>
       <c r="W33" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>300082</v>
+        <v>300081</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
@@ -2718,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="0" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N34" s="0" t="n">
         <v>400003</v>
@@ -2745,13 +2783,13 @@
       </c>
       <c r="W34" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>300083</v>
+        <v>300082</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
@@ -2773,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="0" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N35" s="0" t="n">
         <v>400003</v>
@@ -2800,13 +2838,13 @@
       </c>
       <c r="W35" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>300084</v>
+        <v>300083</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
@@ -2828,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N36" s="0" t="n">
         <v>400003</v>
@@ -2855,13 +2893,13 @@
       </c>
       <c r="W36" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>300085</v>
+        <v>300084</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
@@ -2883,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="0" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N37" s="0" t="n">
         <v>400003</v>
@@ -2910,47 +2948,49 @@
       </c>
       <c r="W37" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>300091</v>
+        <v>300085</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShockwaveRing</t>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
         </is>
       </c>
       <c r="G38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="0" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I38" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="0" t="inlineStr">
-        <is>
-          <t>0.5,0.5</t>
-        </is>
-      </c>
-      <c r="K38" s="0" t="n">
-        <v>1700001</v>
-      </c>
       <c r="M38" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N38" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O38" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P38" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="O38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="0" t="n">
-        <v>0</v>
+      <c r="R38" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
       </c>
       <c r="S38" s="0" t="n">
         <v>0</v>
@@ -2963,133 +3003,143 @@
       </c>
       <c r="W38" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>300101</v>
+        <v>300091</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcGround</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="inlineStr"/>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_FireBottle_1</t>
-        </is>
-      </c>
-      <c r="F39" s="0" t="inlineStr"/>
-      <c r="G39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I39" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>AttackModeShockwaveRing</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.5,0.5</t>
         </is>
       </c>
       <c r="K39" s="0" t="n">
-        <v>1800001</v>
-      </c>
-      <c r="L39" s="0" t="inlineStr"/>
-      <c r="M39" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+        <v>1700001</v>
+      </c>
+      <c r="M39" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="N39" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O39" s="0" t="inlineStr"/>
-      <c r="P39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q39" s="0" t="inlineStr"/>
-      <c r="R39" s="0" t="inlineStr"/>
-      <c r="S39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U39" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>420001</v>
+      </c>
+      <c r="O39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W39" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>400001</v>
+        <v>300101</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlapNoDamage</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr">
-        <is>
-          <t>1000200001:1</t>
-        </is>
-      </c>
-      <c r="H40" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I40" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J40" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K40" s="0" t="n"/>
-      <c r="L40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="0" t="n"/>
-      <c r="O40" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P40" s="0" t="n">
-        <v>630005</v>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr"/>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="inlineStr"/>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K40" s="0" t="n">
+        <v>1800001</v>
+      </c>
+      <c r="L40" s="0" t="inlineStr"/>
+      <c r="M40" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N40" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O40" s="0" t="inlineStr"/>
+      <c r="P40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q40" s="0" t="inlineStr"/>
+      <c r="R40" s="0" t="inlineStr"/>
+      <c r="S40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U40" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="W40" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>400002</v>
+        <v>400001</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
@@ -3098,7 +3148,7 @@
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t>1000400001:1</t>
+          <t>1000200001:1</t>
         </is>
       </c>
       <c r="H41" s="0" t="n">
@@ -3126,50 +3176,60 @@
       </c>
       <c r="W41" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-中毒</t>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>500001</v>
+        <v>400002</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t>1000400001:1</t>
         </is>
       </c>
       <c r="H42" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I42" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" s="0" t="n">
-        <v>500001</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K42" s="0" t="n"/>
+      <c r="L42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="0" t="n"/>
       <c r="O42" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P42" s="0" t="n">
-        <v>470001</v>
+        <v>630005</v>
       </c>
       <c r="W42" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
+          <t>AttackModeRegainHP</t>
         </is>
       </c>
       <c r="H43" s="0" t="n">
@@ -3182,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="O43" s="0" t="n">
         <v>100001</v>
@@ -3192,21 +3252,27 @@
       </c>
       <c r="W43" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
+          <t>AttackModeRegainDR</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="0" t="n">
         <v>500002</v>
@@ -3219,61 +3285,40 @@
       </c>
       <c r="W44" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Meteorite_1</t>
-        </is>
-      </c>
-      <c r="F45" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
-      </c>
-      <c r="I45" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J45" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K45" s="0" t="n">
-        <v>800001</v>
-      </c>
-      <c r="M45" s="0" t="n">
-        <v>3</v>
+        <v>500002</v>
       </c>
       <c r="O45" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P45" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q45" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
+        <v>470001</v>
       </c>
       <c r="W45" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>700002</v>
+        <v>700001</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
@@ -3282,12 +3327,12 @@
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_Fallupon_Water_1</t>
+          <t>AttackMode_Fallupon_Meteorite_1</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I46" s="0" t="n">
@@ -3315,13 +3360,13 @@
       </c>
       <c r="W46" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球</t>
+          <t>下落范围攻击-火球</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>700003</v>
+        <v>700002</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
@@ -3330,12 +3375,12 @@
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackMode_Fallupon_Water_1</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I47" s="0" t="n">
@@ -3356,19 +3401,34 @@
       <c r="P47" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q47" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
       <c r="W47" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落范围攻击-水球</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>800001</v>
+        <v>700003</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I48" s="0" t="n">
@@ -3377,10 +3437,11 @@
       <c r="J48" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K48" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K48" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="O48" s="0" t="n">
         <v>100001</v>
@@ -3390,47 +3451,45 @@
       </c>
       <c r="W48" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300031</v>
+        <v>800001</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I49" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K49" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P49" s="0" t="n"/>
-      <c r="U49" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="K49" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O49" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P49" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300032</v>
+        <v>300031</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
@@ -3441,7 +3500,7 @@
         <v>11</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K50" s="0" t="n">
         <v>900003</v>
@@ -3454,17 +3513,17 @@
       </c>
       <c r="P50" s="0" t="n"/>
       <c r="U50" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300033</v>
+        <v>300032</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
@@ -3475,7 +3534,7 @@
         <v>11</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K51" s="0" t="n">
         <v>900003</v>
@@ -3488,17 +3547,17 @@
       </c>
       <c r="P51" s="0" t="n"/>
       <c r="U51" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300034</v>
+        <v>300033</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
@@ -3509,7 +3568,7 @@
         <v>11</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K52" s="0" t="n">
         <v>900003</v>
@@ -3522,17 +3581,17 @@
       </c>
       <c r="P52" s="0" t="n"/>
       <c r="U52" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300035</v>
+        <v>300034</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
@@ -3543,7 +3602,7 @@
         <v>11</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>900003</v>
@@ -3556,92 +3615,75 @@
       </c>
       <c r="P53" s="0" t="n"/>
       <c r="U53" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300041</v>
+        <v>300035</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D54" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E54" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H54" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M54" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N54" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O54" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P54" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R54" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P54" s="0" t="n"/>
+      <c r="U54" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300051</v>
+        <v>300041</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C55" s="0" t="inlineStr"/>
+          <t>AttackModeRangedPiercingRoad</t>
+        </is>
+      </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F55" s="0" t="inlineStr"/>
-      <c r="G55" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H55" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="0" t="inlineStr"/>
-      <c r="K55" s="0" t="inlineStr"/>
-      <c r="L55" s="0" t="inlineStr"/>
       <c r="M55" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N55" s="0" t="n">
-        <v>400003</v>
+        <v>310001</v>
       </c>
       <c r="O55" s="0" t="n">
         <v>100001</v>
@@ -3649,43 +3691,35 @@
       <c r="P55" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q55" s="0" t="inlineStr"/>
       <c r="R55" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="0" t="n">
-        <v>0</v>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300071</v>
+        <v>300051</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
-        </is>
-      </c>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr"/>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr"/>
       <c r="G56" s="0" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H56" s="0" t="n">
         <v>0.3</v>
@@ -3693,15 +3727,22 @@
       <c r="I56" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J56" s="0" t="inlineStr"/>
+      <c r="K56" s="0" t="inlineStr"/>
+      <c r="L56" s="0" t="inlineStr"/>
       <c r="M56" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N56" s="0" t="n">
-        <v>0</v>
+        <v>400003</v>
+      </c>
+      <c r="O56" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P56" s="0" t="n">
         <v>420001</v>
       </c>
+      <c r="Q56" s="0" t="inlineStr"/>
       <c r="R56" s="0" t="inlineStr">
         <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
@@ -3717,6 +3758,58 @@
         <v>0</v>
       </c>
       <c r="W56" s="0" t="inlineStr">
+        <is>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R57" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="0" t="inlineStr">
         <is>
           <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1789,9 +1789,10 @@
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedWaterBall</t>
+      <c r="C13" s="0" t="n"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedWaterBall</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>0.5,1,0.4</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="W9" s="0" t="inlineStr">
         <is>
-          <t>普通近战范围-前方挥砍(攻击前方2单位,最多命中3个敌人)</t>
+          <t>普通近战范围-前方挥砍(攻击前方1单位,只打本路,最多命中3个敌人)</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C13" s="0" t="n"/>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedWaterBall</t>
         </is>
@@ -2318,7 +2318,7 @@
         <v>100001</v>
       </c>
       <c r="P24" s="0" t="n">
-        <v>420008</v>
+        <v>200008</v>
       </c>
       <c r="W24" s="0" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>100001</v>
       </c>
       <c r="P25" s="0" t="n">
-        <v>420011</v>
+        <v>200008</v>
       </c>
       <c r="R25" s="0" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>100001</v>
       </c>
       <c r="P29" s="0" t="n">
-        <v>420011</v>
+        <v>200008</v>
       </c>
       <c r="R29" s="0" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="W40" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="0" t="n">
-        <v>500002</v>
+        <v>500003</v>
       </c>
       <c r="O44" s="0" t="n">
         <v>100001</v>
@@ -3813,6 +3813,46 @@
       <c r="W57" s="0" t="inlineStr">
         <is>
           <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="n">
+        <v>207001</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
+        </is>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="0" t="n">
+        <v>310001</v>
+      </c>
+      <c r="O58" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P58" s="0" t="n">
+        <v>200008</v>
+      </c>
+      <c r="R58" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="W58" s="0" t="inlineStr">
+        <is>
+          <t>远程攻击-攻击(人类弓手)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
+          <t>AttackModeFalluponAreaRandom</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="W46" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球</t>
+          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
+          <t>AttackModeFalluponAreaRandom</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="W47" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球</t>
+          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1768,6 +1768,9 @@
       <c r="M12" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N12" s="0" t="n">
+        <v>100003</v>
+      </c>
       <c r="O12" s="0" t="n">
         <v>100001</v>
       </c>
@@ -1806,6 +1809,9 @@
       <c r="K13" s="0" t="n"/>
       <c r="M13" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <v>100003</v>
       </c>
       <c r="O13" s="0" t="n">
         <v>100001</v>
@@ -3326,9 +3332,10 @@
           <t>AttackModeFalluponAreaRandom</t>
         </is>
       </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Meteorite_1</t>
+      <c r="C46" s="0" t="n"/>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall_2</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
@@ -3343,10 +3350,10 @@
         <v>1.5</v>
       </c>
       <c r="K46" s="0" t="n">
-        <v>800001</v>
+        <v>2000001</v>
       </c>
       <c r="M46" s="0" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O46" s="0" t="n">
         <v>100001</v>
@@ -3357,6 +3364,11 @@
       <c r="Q46" s="0" t="inlineStr">
         <is>
           <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V46" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
         </is>
       </c>
       <c r="W46" s="0" t="inlineStr">
@@ -3374,9 +3386,10 @@
           <t>AttackModeFalluponAreaRandom</t>
         </is>
       </c>
-      <c r="C47" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Water_1</t>
+      <c r="C47" s="0" t="n"/>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedWaterBall_2</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
@@ -3391,10 +3404,10 @@
         <v>1.5</v>
       </c>
       <c r="K47" s="0" t="n">
-        <v>800001</v>
+        <v>2000002</v>
       </c>
       <c r="M47" s="0" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O47" s="0" t="n">
         <v>100001</v>
@@ -3405,6 +3418,11 @@
       <c r="Q47" s="0" t="inlineStr">
         <is>
           <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V47" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
         </is>
       </c>
       <c r="W47" s="0" t="inlineStr">
@@ -3443,6 +3461,9 @@
       </c>
       <c r="M48" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="N48" s="0" t="n">
+        <v>100003</v>
       </c>
       <c r="O48" s="0" t="n">
         <v>100001</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W58"/>
+  <dimension ref="A1:W60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="10" ht="14.25" customHeight="1" s="1">
       <c r="A10" s="0" t="n">
-        <v>102001</v>
+        <v>101006</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
@@ -1681,11 +1681,11 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>3,1,0.25</t>
+          <t>0.5,1,1</t>
         </is>
       </c>
       <c r="K10" s="0" t="n">
-        <v>400002</v>
+        <v>400003</v>
       </c>
       <c r="O10" s="0" t="n">
         <v>100001</v>
@@ -1693,99 +1693,88 @@
       <c r="P10" s="0" t="n">
         <v>200007</v>
       </c>
+      <c r="U10" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="W10" s="0" t="inlineStr">
         <is>
-          <t>BOSS技能-向前挥砍攻击前方6格</t>
+          <t>普通近战范围-前方挥砍(大剑战士BOSS普攻,同战之魅魔)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" s="1">
       <c r="A11" s="0" t="n">
-        <v>200001</v>
+        <v>102001</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="n"/>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeMeleeArea</t>
         </is>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K11" s="0" t="n"/>
-      <c r="M11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>310001</v>
+        <v>3</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>3,1,0.25</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>400002</v>
       </c>
       <c r="O11" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P11" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R11" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
+        <v>200007</v>
       </c>
       <c r="W11" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击</t>
+          <t>BOSS技能-向前挥砍攻击前方6格</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="n">
-        <v>200002</v>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="n"/>
-      <c r="D12" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F12" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
-      </c>
-      <c r="H12" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K12" s="0" t="n"/>
-      <c r="M12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="0" t="n">
-        <v>100003</v>
-      </c>
-      <c r="O12" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P12" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="W12" s="0" t="inlineStr">
-        <is>
-          <t>远程攻击-火球直线攻击</t>
+      <c r="A12" t="n">
+        <v>102002</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AttackModeMeleeArea</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,1,1.25</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>400002</v>
+      </c>
+      <c r="O12" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P12" t="n">
+        <v>200007</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>BOSS技能-向前挥砍攻击前方6格上中下3排</t>
         </is>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="1">
       <c r="A13" s="0" t="n">
-        <v>200003</v>
+        <v>200001</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
@@ -1795,12 +1784,7 @@
       <c r="C13" s="0" t="n"/>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedWaterBall</t>
-        </is>
-      </c>
-      <c r="F13" s="0" t="inlineStr">
-        <is>
-          <t>1000600001:0.5</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H13" s="0" t="n">
@@ -1810,24 +1794,29 @@
       <c r="M13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="0" t="n">
-        <v>100003</v>
+      <c r="N13" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O13" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P13" s="0" t="n">
-        <v>420003</v>
+        <v>420011</v>
+      </c>
+      <c r="R13" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W13" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-水球直线攻击</t>
+          <t>远程攻击-攻击</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>200004</v>
+        <v>200002</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
@@ -1837,12 +1826,12 @@
       <c r="C14" s="0" t="n"/>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H14" s="0" t="n">
@@ -1852,6 +1841,9 @@
       <c r="M14" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N14" s="0" t="n">
+        <v>100003</v>
+      </c>
       <c r="O14" s="0" t="n">
         <v>100001</v>
       </c>
@@ -1860,42 +1852,34 @@
       </c>
       <c r="W14" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击</t>
+          <t>远程攻击-火球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>201001</v>
+        <v>200003</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedObliqueTracking</t>
+          <t>AttackModeRanged</t>
         </is>
       </c>
       <c r="C15" s="0" t="n"/>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedWaterBall</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>1000500002:0.1</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="H15" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I15" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="0" t="n">
-        <v>100001</v>
-      </c>
+      <c r="K15" s="0" t="n"/>
       <c r="M15" s="0" t="n">
         <v>1</v>
       </c>
@@ -1906,29 +1890,21 @@
         <v>100001</v>
       </c>
       <c r="P15" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="U15" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="0" t="inlineStr">
-        <is>
-          <t>aim_up:0.5</t>
-        </is>
+        <v>420003</v>
       </c>
       <c r="W15" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
+          <t>远程攻击-水球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>201002</v>
+        <v>200004</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedObliqueTracking</t>
+          <t>AttackModeRanged</t>
         </is>
       </c>
       <c r="C16" s="0" t="n"/>
@@ -1939,56 +1915,38 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="H16" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I16" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="0" t="n">
-        <v>200001</v>
-      </c>
+      <c r="K16" s="0" t="n"/>
       <c r="M16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="0" t="n">
-        <v>100003</v>
-      </c>
       <c r="O16" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P16" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="U16" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="0" t="inlineStr">
-        <is>
-          <t>aim_up:0.5</t>
-        </is>
+        <v>420003</v>
       </c>
       <c r="W16" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
+          <t>远程攻击-冰球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="1">
       <c r="A17" s="0" t="n">
-        <v>201003</v>
+        <v>201001</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
+          <t>AttackModeRangedObliqueTracking</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="n"/>
       <c r="D17" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedFireBall</t>
@@ -1996,17 +1954,23 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>1000500001:0.5</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H17" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="I17" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="M17" s="0" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N17" s="0" t="n">
         <v>100003</v>
@@ -2017,21 +1981,30 @@
       <c r="P17" s="0" t="n">
         <v>420006</v>
       </c>
+      <c r="U17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="0" t="inlineStr">
+        <is>
+          <t>aim_up:0.5</t>
+        </is>
+      </c>
       <c r="W17" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="1">
       <c r="A18" s="0" t="n">
-        <v>201004</v>
+        <v>201002</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
+          <t>AttackModeRangedObliqueTracking</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="n"/>
       <c r="D18" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedIceBall</t>
@@ -2039,17 +2012,23 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>1000100001:0.5</t>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H18" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="I18" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" s="0" t="n">
         <v>200001</v>
       </c>
       <c r="M18" s="0" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N18" s="0" t="n">
         <v>100003</v>
@@ -2060,39 +2039,47 @@
       <c r="P18" s="0" t="n">
         <v>420006</v>
       </c>
+      <c r="U18" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="0" t="inlineStr">
+        <is>
+          <t>aim_up:0.5</t>
+        </is>
+      </c>
       <c r="W18" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>202001</v>
+        <v>201003</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedTracking</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="n"/>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedLove</t>
+          <t>AttackModeVisual_RangedFireBall</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H19" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I19" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="0" t="n"/>
+      <c r="K19" s="0" t="n">
+        <v>100001</v>
+      </c>
       <c r="M19" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N19" s="0" t="n">
         <v>100003</v>
@@ -2101,121 +2088,123 @@
         <v>100001</v>
       </c>
       <c r="P19" s="0" t="n">
-        <v>6</v>
+        <v>420006</v>
       </c>
       <c r="W19" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-跟踪-爱心</t>
+          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>203001</v>
+        <v>201004</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcArea</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr"/>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
-      </c>
-      <c r="G20" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>1000100001:0.5</t>
+        </is>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I20" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J20" s="0" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+        <v>0.1</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>1900001</v>
+        <v>200001</v>
       </c>
       <c r="M20" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N20" s="0" t="n">
-        <v>100002</v>
+        <v>100003</v>
       </c>
       <c r="O20" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P20" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R20" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="U20" s="0" t="n">
-        <v>3</v>
+        <v>420006</v>
       </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点范围(落点AOE,hit_max=5,近者优先;DSP石头+残影拖尾;击中特效1900001;出手sound_knife_miss_2,命中sound_hit_11)</t>
+          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>204001</v>
+        <v>202001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplit</t>
+          <t>AttackModeRangedTracking</t>
         </is>
       </c>
       <c r="C21" s="0" t="n"/>
-      <c r="H21" s="0" t="n"/>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedLove</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="K21" s="0" t="n"/>
-      <c r="M21" s="0" t="n"/>
+      <c r="M21" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="N21" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O21" s="0" t="n"/>
-      <c r="P21" s="0" t="n"/>
-      <c r="S21" s="0" t="n">
-        <v>204101</v>
+        <v>100003</v>
+      </c>
+      <c r="O21" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P21" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="W21" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭</t>
+          <t>远程攻击-跟踪-爱心</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>204002</v>
+        <v>203001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedChain</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="n"/>
+          <t>AttackModeRangedArcArea</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr"/>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>1000500002:0.1</t>
-        </is>
+          <t>AttackModeVisual_RangedNormal</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
@@ -2223,217 +2212,212 @@
         </is>
       </c>
       <c r="K22" s="0" t="n">
-        <v>100001</v>
+        <v>1900001</v>
       </c>
       <c r="M22" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="0" t="n">
-        <v>100003</v>
+        <v>100002</v>
       </c>
       <c r="O22" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P22" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="S22" s="0" t="n"/>
+        <v>420011</v>
+      </c>
+      <c r="R22" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
       <c r="U22" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W22" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
+          <t>远程攻击-抛物线-落点范围(落点AOE,hit_max=5,近者优先;DSP石头+残影拖尾;击中特效1900001;出手sound_knife_miss_2,命中sound_hit_11)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>204003</v>
+        <v>204001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedChain</t>
+          <t>AttackModeRangedSplit</t>
         </is>
       </c>
       <c r="C23" s="0" t="n"/>
-      <c r="D23" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedIceBall</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="inlineStr">
-        <is>
-          <t>1000100002:0.1</t>
-        </is>
-      </c>
-      <c r="H23" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J23" s="0" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K23" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="M23" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="H23" s="0" t="n"/>
+      <c r="K23" s="0" t="n"/>
+      <c r="M23" s="0" t="n"/>
       <c r="N23" s="0" t="n">
-        <v>100003</v>
-      </c>
-      <c r="O23" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P23" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="S23" s="0" t="n"/>
-      <c r="U23" s="0" t="n">
-        <v>2</v>
+        <v>310001</v>
+      </c>
+      <c r="O23" s="0" t="n"/>
+      <c r="P23" s="0" t="n"/>
+      <c r="S23" s="0" t="n">
+        <v>204101</v>
       </c>
       <c r="W23" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
+          <t>远程攻击-分裂弓箭</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>204101</v>
+        <v>204002</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplitChild</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
+          <t>AttackModeRangedChain</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="n"/>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H24" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>100001</v>
+      </c>
       <c r="M24" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N24" s="0" t="n">
+        <v>100003</v>
+      </c>
       <c r="O24" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P24" s="0" t="n">
-        <v>200008</v>
+        <v>420006</v>
+      </c>
+      <c r="S24" s="0" t="n"/>
+      <c r="U24" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="W24" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭-子弹道</t>
+          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>205001</v>
+        <v>204003</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
-        </is>
-      </c>
-      <c r="C25" s="0" t="inlineStr"/>
+          <t>AttackModeRangedChain</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="n"/>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H25" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K25" s="0" t="n"/>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>200001</v>
+      </c>
       <c r="M25" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="0" t="n">
-        <v>310001</v>
+        <v>100003</v>
       </c>
       <c r="O25" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P25" s="0" t="n">
-        <v>200008</v>
-      </c>
-      <c r="R25" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
+        <v>420006</v>
+      </c>
+      <c r="S25" s="0" t="n"/>
+      <c r="U25" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="W25" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透</t>
+          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>205002</v>
+        <v>204101</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingShrink</t>
-        </is>
-      </c>
-      <c r="C26" s="0" t="n"/>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="inlineStr">
-        <is>
-          <t>1000500002:0.1</t>
+          <t>AttackModeRangedSplitChild</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
         </is>
       </c>
       <c r="H26" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K26" s="0" t="n"/>
       <c r="M26" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="0" t="n">
-        <v>100003</v>
-      </c>
       <c r="O26" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P26" s="0" t="n">
-        <v>420006</v>
+        <v>200008</v>
       </c>
       <c r="W26" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
+          <t>远程攻击-分裂弓箭-子弹道</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>205003</v>
+        <v>205001</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingShrink</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="n"/>
+          <t>AttackModeRangedPiercing</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr"/>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
-        </is>
-      </c>
-      <c r="F27" s="0" t="inlineStr">
-        <is>
-          <t>1000100002:0.1</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H27" s="0" t="n">
@@ -2444,381 +2428,360 @@
         <v>1</v>
       </c>
       <c r="N27" s="0" t="n">
-        <v>100003</v>
+        <v>310001</v>
       </c>
       <c r="O27" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P27" s="0" t="n">
-        <v>420006</v>
+        <v>200008</v>
+      </c>
+      <c r="R27" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W27" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
+          <t>远程攻击-穿透</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>205004</v>
+        <v>205002</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeMelee</t>
-        </is>
-      </c>
-      <c r="G28" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeRangedPiercingShrink</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="n"/>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>1000500002:0.1</t>
+        </is>
       </c>
       <c r="H28" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="K28" s="0" t="n"/>
       <c r="M28" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="0" t="n">
-        <v>0</v>
+        <v>100003</v>
       </c>
       <c r="O28" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P28" s="0" t="n">
-        <v>200007</v>
-      </c>
-      <c r="S28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="0" t="n">
-        <v>0</v>
+        <v>420006</v>
       </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
-          <t>普通近战攻击-单体(兽人战士)</t>
+          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>206001</v>
+        <v>205003</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcTracking</t>
-        </is>
-      </c>
+          <t>AttackModeRangedPiercingShrink</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="n"/>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H29" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I29" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J29" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
+      <c r="K29" s="0" t="n"/>
       <c r="M29" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="0" t="n">
-        <v>310001</v>
+        <v>100003</v>
       </c>
       <c r="O29" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P29" s="0" t="n">
-        <v>200008</v>
-      </c>
-      <c r="R29" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="V29" s="0" t="inlineStr">
-        <is>
-          <t>stuck_time:3&amp;stuck_sink:0.1</t>
-        </is>
+        <v>420006</v>
       </c>
       <c r="W29" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
+          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>210001</v>
+        <v>205004</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="n"/>
-      <c r="D30" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
+          <t>AttackModeMelee</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H30" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K30" s="0" t="n"/>
+      <c r="I30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="M30" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="2" t="n">
-        <v>310001</v>
+      <c r="N30" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O30" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P30" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R30" s="0" t="inlineStr">
-        <is>
-          <t>type:2&amp;color:1,1,1</t>
-        </is>
+        <v>200007</v>
+      </c>
+      <c r="S30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W30" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击-VFX轨迹(白)</t>
+          <t>普通近战攻击-单体(兽人战士)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
-        <v>300001</v>
+        <v>206001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
+          <t>AttackModeRangedArcTracking</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H31" s="0" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="I31" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="J31" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K31" s="0" t="n">
-        <v>300002</v>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="M31" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N31" s="0" t="n">
+        <v>310001</v>
       </c>
       <c r="O31" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P31" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="T31" s="0" t="n">
-        <v>50</v>
+        <v>200008</v>
+      </c>
+      <c r="R31" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="V31" s="0" t="inlineStr">
+        <is>
+          <t>stuck_time:3&amp;stuck_sink:0.1</t>
+        </is>
       </c>
       <c r="W31" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰</t>
+          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>300002</v>
+        <v>210001</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="n"/>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H32" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I32" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J32" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K32" s="0" t="n">
-        <v>300002</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="K32" s="0" t="n"/>
       <c r="M32" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O32" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P32" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="T32" s="0" t="n">
-        <v>1</v>
+        <v>420011</v>
+      </c>
+      <c r="R32" s="0" t="inlineStr">
+        <is>
+          <t>type:2&amp;color:1,1,1</t>
+        </is>
       </c>
       <c r="W32" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰(敢死队)</t>
+          <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>300061</v>
+        <v>300001</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcBounce</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Axe_1</t>
-        </is>
-      </c>
-      <c r="G33" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeExplosion</t>
+        </is>
       </c>
       <c r="H33" s="0" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K33" s="0" t="n">
+        <v>300002</v>
       </c>
       <c r="M33" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="N33" s="0" t="n">
-        <v>400003</v>
+        <v>0</v>
       </c>
       <c r="O33" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P33" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R33" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S33" s="0" t="n">
-        <v>0</v>
+        <v>420008</v>
       </c>
       <c r="T33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="0" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W33" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
+          <t>爆炸范围攻击-火焰</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>300081</v>
+        <v>300002</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Pingpang_1</t>
-        </is>
-      </c>
-      <c r="G34" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeExplosion</t>
+        </is>
       </c>
       <c r="H34" s="0" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="I34" s="0" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K34" s="0" t="n">
+        <v>300002</v>
       </c>
       <c r="M34" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" s="0" t="n">
-        <v>400003</v>
+        <v>0</v>
       </c>
       <c r="O34" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P34" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R34" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S34" s="0" t="n">
-        <v>0</v>
+        <v>420008</v>
       </c>
       <c r="T34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
+          <t>爆炸范围攻击-火焰(敢死队)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>300082</v>
+        <v>300061</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
+          <t>AttackModeRangedArcBounce</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Pingpang_1</t>
+          <t>AttackModeVisual_Axe_1</t>
         </is>
       </c>
       <c r="G35" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I35" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M35" s="0" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="N35" s="0" t="n">
         <v>400003</v>
@@ -2845,13 +2808,13 @@
       </c>
       <c r="W35" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>300083</v>
+        <v>300081</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
@@ -2873,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N36" s="0" t="n">
         <v>400003</v>
@@ -2900,13 +2863,13 @@
       </c>
       <c r="W36" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>300084</v>
+        <v>300082</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
@@ -2928,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="0" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="N37" s="0" t="n">
         <v>400003</v>
@@ -2955,13 +2918,13 @@
       </c>
       <c r="W37" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>300085</v>
+        <v>300083</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
@@ -2983,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N38" s="0" t="n">
         <v>400003</v>
@@ -3010,47 +2973,49 @@
       </c>
       <c r="W38" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>300091</v>
+        <v>300084</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShockwaveRing</t>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
         </is>
       </c>
       <c r="G39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="0" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I39" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="0" t="inlineStr">
-        <is>
-          <t>0.5,0.5</t>
-        </is>
-      </c>
-      <c r="K39" s="0" t="n">
-        <v>1700001</v>
-      </c>
       <c r="M39" s="0" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N39" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O39" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P39" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="O39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="0" t="n">
-        <v>0</v>
+      <c r="R39" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
       </c>
       <c r="S39" s="0" t="n">
         <v>0</v>
@@ -3063,253 +3028,301 @@
       </c>
       <c r="W39" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300101</v>
+        <v>300085</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcGround</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="inlineStr"/>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_FireBottle_1</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr"/>
-      <c r="G40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I40" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J40" s="0" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="K40" s="0" t="n">
-        <v>1800001</v>
-      </c>
-      <c r="L40" s="0" t="inlineStr"/>
-      <c r="M40" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>AttackModeVisual_Pingpang_1</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="N40" s="0" t="n">
         <v>400003</v>
       </c>
-      <c r="O40" s="0" t="inlineStr"/>
-      <c r="P40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q40" s="0" t="inlineStr"/>
-      <c r="R40" s="0" t="inlineStr"/>
-      <c r="S40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U40" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="O40" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P40" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R40" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W40" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>400001</v>
+        <v>300091</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlapNoDamage</t>
-        </is>
-      </c>
-      <c r="F41" s="0" t="inlineStr">
-        <is>
-          <t>1000200001:1</t>
-        </is>
+          <t>AttackModeShockwaveRing</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H41" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I41" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J41" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K41" s="0" t="n"/>
-      <c r="L41" s="0" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t>0.5,0.5</t>
+        </is>
+      </c>
+      <c r="K41" s="0" t="n">
+        <v>1700001</v>
       </c>
       <c r="M41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="0" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="N41" s="0" t="n">
+        <v>420001</v>
+      </c>
       <c r="O41" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P41" s="0" t="n">
-        <v>630005</v>
+        <v>0</v>
+      </c>
+      <c r="S41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W41" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>400002</v>
+        <v>300101</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlapNoDamage</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr">
-        <is>
-          <t>1000400001:1</t>
-        </is>
-      </c>
-      <c r="H42" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I42" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J42" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K42" s="0" t="n"/>
-      <c r="L42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="0" t="n"/>
-      <c r="O42" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P42" s="0" t="n">
-        <v>630005</v>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr"/>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="inlineStr"/>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K42" s="0" t="n">
+        <v>1800001</v>
+      </c>
+      <c r="L42" s="0" t="inlineStr"/>
+      <c r="M42" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N42" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O42" s="0" t="inlineStr"/>
+      <c r="P42" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q42" s="0" t="inlineStr"/>
+      <c r="R42" s="0" t="inlineStr"/>
+      <c r="S42" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T42" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U42" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="W42" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-中毒</t>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>500001</v>
+        <v>400001</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="inlineStr">
+        <is>
+          <t>1000200001:1</t>
         </is>
       </c>
       <c r="H43" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I43" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J43" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" s="0" t="n">
-        <v>500001</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K43" s="0" t="n"/>
+      <c r="L43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="0" t="n"/>
       <c r="O43" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P43" s="0" t="n">
-        <v>470001</v>
+        <v>630005</v>
       </c>
       <c r="W43" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>500002</v>
+        <v>400002</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="inlineStr">
+        <is>
+          <t>1000400001:1</t>
         </is>
       </c>
       <c r="H44" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I44" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" s="0" t="n">
-        <v>500003</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K44" s="0" t="n"/>
+      <c r="L44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="0" t="n"/>
       <c r="O44" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P44" s="0" t="n">
-        <v>470001</v>
+        <v>630005</v>
       </c>
       <c r="W44" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>600001</v>
+        <v>500001</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
+          <t>AttackModeRegainHP</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="O45" s="0" t="n">
         <v>100001</v>
@@ -3319,135 +3332,88 @@
       </c>
       <c r="W45" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>700001</v>
+        <v>500002</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C46" s="0" t="n"/>
-      <c r="D46" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall_2</t>
-        </is>
-      </c>
-      <c r="F46" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
+          <t>AttackModeRegainDR</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="I46" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J46" s="0" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K46" s="0" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="M46" s="0" t="n">
-        <v>1.5</v>
+        <v>500003</v>
       </c>
       <c r="O46" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P46" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q46" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V46" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
+        <v>470001</v>
       </c>
       <c r="W46" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>700002</v>
+        <v>600001</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C47" s="0" t="n"/>
-      <c r="D47" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedWaterBall_2</t>
-        </is>
-      </c>
-      <c r="F47" s="0" t="inlineStr">
-        <is>
-          <t>1000600001:0.5</t>
-        </is>
-      </c>
-      <c r="I47" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J47" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K47" s="0" t="n">
-        <v>2000002</v>
-      </c>
-      <c r="M47" s="0" t="n">
-        <v>1.5</v>
+        <v>500002</v>
       </c>
       <c r="O47" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P47" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q47" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V47" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
+        <v>470001</v>
       </c>
       <c r="W47" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>700003</v>
+        <v>700001</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="n"/>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall_2</t>
         </is>
       </c>
       <c r="F48" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I48" s="0" t="n">
@@ -3457,13 +3423,10 @@
         <v>1.5</v>
       </c>
       <c r="K48" s="0" t="n">
-        <v>800001</v>
+        <v>2000001</v>
       </c>
       <c r="M48" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N48" s="0" t="n">
-        <v>100003</v>
+        <v>1.5</v>
       </c>
       <c r="O48" s="0" t="n">
         <v>100001</v>
@@ -3471,19 +3434,40 @@
       <c r="P48" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q48" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V48" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W48" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>800001</v>
+        <v>700002</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="n"/>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedWaterBall_2</t>
+        </is>
+      </c>
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I49" s="0" t="n">
@@ -3492,10 +3476,11 @@
       <c r="J49" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K49" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K49" s="0" t="n">
+        <v>2000002</v>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>1.5</v>
       </c>
       <c r="O49" s="0" t="n">
         <v>100001</v>
@@ -3503,83 +3488,103 @@
       <c r="P49" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q49" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V49" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300031</v>
+        <v>700003</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I50" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="K50" s="0" t="n">
-        <v>900003</v>
+        <v>800001</v>
       </c>
       <c r="M50" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N50" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P50" s="0" t="n"/>
-      <c r="U50" s="0" t="n">
-        <v>1</v>
+        <v>100003</v>
+      </c>
+      <c r="O50" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P50" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300032</v>
+        <v>800001</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I51" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K51" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P51" s="0" t="n"/>
-      <c r="U51" s="0" t="n">
-        <v>2</v>
+        <v>1.5</v>
+      </c>
+      <c r="K51" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O51" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P51" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300033</v>
+        <v>300031</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
@@ -3590,7 +3595,7 @@
         <v>11</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="K52" s="0" t="n">
         <v>900003</v>
@@ -3603,17 +3608,17 @@
       </c>
       <c r="P52" s="0" t="n"/>
       <c r="U52" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300034</v>
+        <v>300032</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
@@ -3624,7 +3629,7 @@
         <v>11</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>900003</v>
@@ -3637,17 +3642,17 @@
       </c>
       <c r="P53" s="0" t="n"/>
       <c r="U53" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300035</v>
+        <v>300033</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
@@ -3658,7 +3663,7 @@
         <v>11</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K54" s="0" t="n">
         <v>900003</v>
@@ -3671,207 +3676,275 @@
       </c>
       <c r="P54" s="0" t="n"/>
       <c r="U54" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300041</v>
+        <v>300034</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D55" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E55" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H55" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K55" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M55" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N55" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O55" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P55" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R55" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P55" s="0" t="n"/>
+      <c r="U55" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300051</v>
+        <v>300035</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C56" s="0" t="inlineStr"/>
-      <c r="D56" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F56" s="0" t="inlineStr"/>
-      <c r="G56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
       </c>
       <c r="I56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="0" t="inlineStr"/>
-      <c r="K56" s="0" t="inlineStr"/>
-      <c r="L56" s="0" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>900003</v>
+      </c>
       <c r="M56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="P56" s="0" t="n"/>
+      <c r="U56" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="N56" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O56" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P56" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="Q56" s="0" t="inlineStr"/>
-      <c r="R56" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W56" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300071</v>
+        <v>300041</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
+          <t>AttackModeRangedPiercingRoad</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
-      <c r="G57" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H57" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I57" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="M57" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N57" s="0" t="n">
-        <v>0</v>
+        <v>310001</v>
+      </c>
+      <c r="O57" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P57" s="0" t="n">
         <v>420001</v>
       </c>
       <c r="R57" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="0" t="n">
-        <v>0</v>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
+        <v>300051</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr"/>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F58" s="0" t="inlineStr"/>
+      <c r="G58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="0" t="inlineStr"/>
+      <c r="K58" s="0" t="inlineStr"/>
+      <c r="L58" s="0" t="inlineStr"/>
+      <c r="M58" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N58" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O58" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P58" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="Q58" s="0" t="inlineStr"/>
+      <c r="R58" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="0" t="inlineStr">
+        <is>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H59" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R59" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="n">
         <v>207001</v>
       </c>
-      <c r="B58" s="0" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="D58" s="0" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
-      <c r="H58" s="0" t="n">
+      <c r="H60" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M58" s="0" t="n">
+      <c r="M60" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N58" s="0" t="n">
+      <c r="N60" s="0" t="n">
         <v>310001</v>
       </c>
-      <c r="O58" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P58" s="0" t="n">
+      <c r="O60" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P60" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R58" s="0" t="inlineStr">
+      <c r="R60" s="0" t="inlineStr">
         <is>
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="W58" s="0" t="inlineStr">
+      <c r="W60" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击(人类弓手)</t>
         </is>
